--- a/data/ZGYO (TRY).xlsx
+++ b/data/ZGYO (TRY).xlsx
@@ -403,1091 +403,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F108"/>
-  <cols>
-    <col min="1" max="1" customWidth="1" width="40" level="2" outlineLevel="2"/>
-    <col min="2" max="2" customWidth="1" width="20"/>
-    <col min="3" max="3" customWidth="1" width="20"/>
-    <col min="4" max="4" customWidth="1" width="20"/>
-    <col min="5" max="5" customWidth="1" width="20"/>
-    <col min="6" max="6" customWidth="1" width="20"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Kalem</v>
-      </c>
-      <c r="B1" t="str">
-        <v>2025/12</v>
-      </c>
-      <c r="C1" t="str">
-        <v>2025/9</v>
-      </c>
-      <c r="D1" t="str">
-        <v>2024/12</v>
-      </c>
-      <c r="E1" t="str">
-        <v>2023/12</v>
-      </c>
-      <c r="F1" t="str">
-        <v>2022/12</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>Dönen Varlıklar</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v xml:space="preserve">    Nakit ve Nakit Benzerleri</v>
-      </c>
-      <c r="B3">
-        <v>3712488</v>
-      </c>
-      <c r="C3">
-        <v>10272210.725904455</v>
-      </c>
-      <c r="D3">
-        <v>44711</v>
-      </c>
-      <c r="E3">
-        <v>10817930.112603275</v>
-      </c>
-      <c r="F3">
-        <v>239829.17760051318</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v xml:space="preserve">    Gayrimenkul Projeleri Kapsamında Açılan Nakit Hesapları</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v xml:space="preserve">    Finansal Yatırımlar</v>
-      </c>
-      <c r="B5">
-        <v>35348</v>
-      </c>
-      <c r="C5">
-        <v>3411.3722982163326</v>
-      </c>
-      <c r="D5">
-        <v>23270169</v>
-      </c>
-      <c r="E5">
-        <v>1145.820368137514</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v xml:space="preserve">    Teminata Verilen Finansal Varlıklar</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v xml:space="preserve">    Ticari Alacaklar</v>
-      </c>
-      <c r="B7">
-        <v>6841554</v>
-      </c>
-      <c r="C7">
-        <v>27626641.14046008</v>
-      </c>
-      <c r="D7">
-        <v>6411614</v>
-      </c>
-      <c r="E7">
-        <v>747351.421371339</v>
-      </c>
-      <c r="F7">
-        <v>190259.40227546758</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v xml:space="preserve">    Finans Sektörü Faaliyetlerinden Alacaklar</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v xml:space="preserve">    Türkiye Cumhuriyet Merkez Bankası Hesabı</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v xml:space="preserve">    Diğer Alacaklar</v>
-      </c>
-      <c r="B10">
-        <v>867896</v>
-      </c>
-      <c r="C10">
-        <v>832940.446083119</v>
-      </c>
-      <c r="D10">
-        <v>835110</v>
-      </c>
-      <c r="E10">
-        <v>1532815.4579385961</v>
-      </c>
-      <c r="F10">
-        <v>2371209.508068971</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v xml:space="preserve">    Müşteri Sözleşmelerinden Doğan Varlıklar</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v xml:space="preserve">    İmtiyaz Sözleşmelerine İlişkin Finansal Varlıklar</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v xml:space="preserve">    Türev Araçlar</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v xml:space="preserve">    Stoklar</v>
-      </c>
-      <c r="B14">
-        <v>19439775</v>
-      </c>
-      <c r="C14">
-        <v>18940392.944924895</v>
-      </c>
-      <c r="D14">
-        <v>21953075</v>
-      </c>
-      <c r="E14">
-        <v>29233568.635488622</v>
-      </c>
-      <c r="F14">
-        <v>10004301.644418838</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v xml:space="preserve">    Proje Halindeki Stoklar</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="str">
-        <v xml:space="preserve">    Canlı Varlıklar</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="str">
-        <v xml:space="preserve">    Peşin Ödenmiş Giderler</v>
-      </c>
-      <c r="B17">
-        <v>5566089</v>
-      </c>
-      <c r="C17">
-        <v>891125.7887664008</v>
-      </c>
-      <c r="D17">
-        <v>30343</v>
-      </c>
-      <c r="E17">
-        <v>34388734.4802478</v>
-      </c>
-      <c r="F17">
-        <v>7250987.132382202</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="str">
-        <v xml:space="preserve">    Ertelenmiş Sigortacılık Üretim Giderleri</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="str">
-        <v xml:space="preserve">    Cari Dönem Vergisiyle İlgili Varlıklar</v>
-      </c>
-      <c r="C19">
-        <v>141599.6045105458</v>
-      </c>
-      <c r="F19">
-        <v>2618.2725898515687</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="str">
-        <v xml:space="preserve">    Nakit Dışı Serbest Kullanılabilir Teminatlar</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="str">
-        <v xml:space="preserve">    Diğer Dönen Varlıklar</v>
-      </c>
-      <c r="B21">
-        <v>16082306</v>
-      </c>
-      <c r="C21">
-        <v>16777603.778900694</v>
-      </c>
-      <c r="D21">
-        <v>18022307</v>
-      </c>
-      <c r="E21">
-        <v>9948314.022769526</v>
-      </c>
-      <c r="F21">
-        <v>370135.4596848439</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="str">
-        <v xml:space="preserve">    Satış Amacıyla Elde Tutulan Duran Varlıklar</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="str">
-        <v xml:space="preserve">    Ortaklara Dağıtılmak Üzere Elde Tutulan Duran Varlıklar</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="str">
-        <v xml:space="preserve">    Toplam Dönen Varlıklar</v>
-      </c>
-      <c r="B24">
-        <v>52545456</v>
-      </c>
-      <c r="C24">
-        <v>75485925.80184841</v>
-      </c>
-      <c r="D24">
-        <v>70567329</v>
-      </c>
-      <c r="E24">
-        <v>86669859.95078729</v>
-      </c>
-      <c r="F24">
-        <v>20429340.597020686</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="str">
-        <v>Duran Varlıklar</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="str">
-        <v xml:space="preserve">    Finansal Yatırımlar</v>
-      </c>
-      <c r="B26">
-        <v>84504</v>
-      </c>
-      <c r="C26">
-        <v>84503.73037401773</v>
-      </c>
-      <c r="D26">
-        <v>84504</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="str">
-        <v xml:space="preserve">    İştirakler, İş Ortaklıkları ve Bağlı Ortaklıklardaki Yatırımlar</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="str">
-        <v xml:space="preserve">    Ticari Alacaklar</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="str">
-        <v xml:space="preserve">    Finans Sektörü Faaliyetlerinden Alacaklar</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="str">
-        <v xml:space="preserve">    Diğer Alacaklar</v>
-      </c>
-      <c r="B30">
-        <v>17275</v>
-      </c>
-      <c r="C30">
-        <v>17273.920358634125</v>
-      </c>
-      <c r="D30">
-        <v>17275</v>
-      </c>
-      <c r="E30">
-        <v>8069.789532611471</v>
-      </c>
-      <c r="F30">
-        <v>13295.899189836126</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="str">
-        <v xml:space="preserve">    Müşteri Sözleşmelerinden Doğan Varlıklar</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="str">
-        <v xml:space="preserve">    İmtiyaz Sözleşmelerine İlişkin Finansal Varlıklar</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="str">
-        <v xml:space="preserve">    Türev Araçlar</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="str">
-        <v xml:space="preserve">    Stoklar</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="str">
-        <v xml:space="preserve">    Özkaynak Yöntemiyle Değerlenen Yatırımlar</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="str">
-        <v xml:space="preserve">    Canlı Varlıklar</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="str">
-        <v xml:space="preserve">    Yatırım Amaçlı Gayrimenkuller</v>
-      </c>
-      <c r="B37">
-        <v>2945141000</v>
-      </c>
-      <c r="C37">
-        <v>2951302462.2596684</v>
-      </c>
-      <c r="D37">
-        <v>3479757815</v>
-      </c>
-      <c r="E37">
-        <v>1739090092.7240899</v>
-      </c>
-      <c r="F37">
-        <v>1276648.4263457689</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="str">
-        <v xml:space="preserve">    Proje Halindeki Yatırım Amaçlı Gayrimenkuller</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="str">
-        <v xml:space="preserve">    Maddi Duran Varlıklar</v>
-      </c>
-      <c r="B39">
-        <v>2642652</v>
-      </c>
-      <c r="C39">
-        <v>3039475.322337121</v>
-      </c>
-      <c r="D39">
-        <v>4764157</v>
-      </c>
-      <c r="E39">
-        <v>5928998.447971918</v>
-      </c>
-      <c r="F39">
-        <v>8146712.8994571185</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="str">
-        <v xml:space="preserve">    Kullanım Hakkı Varlıkları</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="str">
-        <v xml:space="preserve">    Maddi Olmayan Duran Varlıklar</v>
-      </c>
-      <c r="B41">
-        <v>9989</v>
-      </c>
-      <c r="C41">
-        <v>13326.16220502373</v>
-      </c>
-      <c r="D41">
-        <v>23228</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="str">
-        <v xml:space="preserve">    Peşin Ödenmiş Giderler</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="str">
-        <v xml:space="preserve">    Ertelenmiş Vergi Varlığı</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="str">
-        <v xml:space="preserve">    Cari Dönem Vergisiyle İlgili Duran Varlıklar</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="str">
-        <v xml:space="preserve">    Nakit Dışı Serbest Kullanılabilir Teminatlar</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="str">
-        <v xml:space="preserve">    Diğer Duran Varlıklar</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="str">
-        <v xml:space="preserve">    Toplam Duran Varlıklar</v>
-      </c>
-      <c r="B47">
-        <v>2947895420</v>
-      </c>
-      <c r="C47">
-        <v>2954457041.3949428</v>
-      </c>
-      <c r="D47">
-        <v>3484646979</v>
-      </c>
-      <c r="E47">
-        <v>1745027160.9615943</v>
-      </c>
-      <c r="F47">
-        <v>9436657.224992724</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="str">
-        <v xml:space="preserve">    Toplam Varlıklar</v>
-      </c>
-      <c r="B48">
-        <v>3000440876</v>
-      </c>
-      <c r="C48">
-        <v>3029942967.196791</v>
-      </c>
-      <c r="D48">
-        <v>3555214308</v>
-      </c>
-      <c r="E48">
-        <v>1831697020.9123816</v>
-      </c>
-      <c r="F48">
-        <v>29865997.82201341</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="str">
-        <v>Kısa Vadeli Yükümlülükler</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="str">
-        <v xml:space="preserve">    Finansal Borçlar</v>
-      </c>
-      <c r="B50">
-        <v>92105760</v>
-      </c>
-      <c r="C50">
-        <v>86039479.25732504</v>
-      </c>
-      <c r="D50">
-        <v>7370028</v>
-      </c>
-      <c r="E50">
-        <v>8595679.339496676</v>
-      </c>
-      <c r="F50">
-        <v>2789697.961157869</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="str">
-        <v xml:space="preserve">    Diğer Finansal Yükümlülükler</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="str">
-        <v xml:space="preserve">    Ticari Borçlar</v>
-      </c>
-      <c r="B52">
-        <v>16760831</v>
-      </c>
-      <c r="C52">
-        <v>14224482.242986796</v>
-      </c>
-      <c r="D52">
-        <v>178591</v>
-      </c>
-      <c r="E52">
-        <v>6747165.324882247</v>
-      </c>
-      <c r="F52">
-        <v>876145.5962485373</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="str">
-        <v xml:space="preserve">    Finans Sektörü Faaliyetlerinden Borçlar</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="str">
-        <v xml:space="preserve">    Çalışanlara Sağlanan Faydalar Kapsamında Borçlar</v>
-      </c>
-      <c r="B54">
-        <v>287589</v>
-      </c>
-      <c r="C54">
-        <v>308243.4194172047</v>
-      </c>
-      <c r="D54">
-        <v>113064</v>
-      </c>
-      <c r="F54">
-        <v>64482.13694679884</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="str">
-        <v xml:space="preserve">    Diğer Borçlar</v>
-      </c>
-      <c r="B55">
-        <v>0</v>
-      </c>
-      <c r="D55">
-        <v>120181653</v>
-      </c>
-      <c r="E55">
-        <v>42779081.348801084</v>
-      </c>
-      <c r="F55">
-        <v>17512880.25721218</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="str">
-        <v xml:space="preserve">    Müşteri Sözleşmelerinden Doğan Yükümlülükler</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="str">
-        <v xml:space="preserve">    Özkaynak Yöntemiyle Değerlenen Yatırımlardan Yükümlülükler</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="str">
-        <v xml:space="preserve">    Türev Araçlar</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="str">
-        <v xml:space="preserve">    Devlet Teşvik ve Yardımları</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="str">
-        <v xml:space="preserve">    Ertelenmiş Gelirler</v>
-      </c>
-      <c r="B60">
-        <v>29970542</v>
-      </c>
-      <c r="C60">
-        <v>32841219.54534601</v>
-      </c>
-      <c r="D60">
-        <v>28413634</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="str">
-        <v xml:space="preserve">    Dönem Karı Vergi Yükümlülüğü</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="str">
-        <v xml:space="preserve">    Kısa Vadeli Karşılıklar</v>
-      </c>
-      <c r="B62">
-        <v>200083</v>
-      </c>
-      <c r="C62">
-        <v>312457.28339401644</v>
-      </c>
-      <c r="D62">
-        <v>652909</v>
-      </c>
-      <c r="E62">
-        <v>693266.1954698535</v>
-      </c>
-      <c r="F62">
-        <v>358595.8589281366</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="str">
-        <v xml:space="preserve">    Diğer Kısa Vadeli Yükümlülükler</v>
-      </c>
-      <c r="B63">
-        <v>120065</v>
-      </c>
-      <c r="C63">
-        <v>136198.1780756826</v>
-      </c>
-      <c r="D63">
-        <v>4437126</v>
-      </c>
-      <c r="E63">
-        <v>95064.47912224327</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="str">
-        <v xml:space="preserve">    Satış Amaçlı Sınıflandırılan Varlık Gruplarına İlişkin Yükümlülükler</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="str">
-        <v xml:space="preserve">    Ortaklara Dağıtılmak Üzere Elde Tutulan Varlık Gruplarına İlişkin Yükümlülükler</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="str">
-        <v xml:space="preserve">    Toplam Kısa Vadeli Yükümlülükler</v>
-      </c>
-      <c r="B66">
-        <v>139444870</v>
-      </c>
-      <c r="C66">
-        <v>133862079.92654474</v>
-      </c>
-      <c r="D66">
-        <v>161347005</v>
-      </c>
-      <c r="E66">
-        <v>58910256.68777211</v>
-      </c>
-      <c r="F66">
-        <v>21601801.81049352</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="str">
-        <v>Uzun Vadeli Yükümlülükler</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="str">
-        <v xml:space="preserve">    Finansal Borçlar</v>
-      </c>
-      <c r="B68">
-        <v>97867021</v>
-      </c>
-      <c r="C68">
-        <v>107610911.61030167</v>
-      </c>
-      <c r="D68">
-        <v>25631774</v>
-      </c>
-      <c r="E68">
-        <v>41245920.47506845</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="str">
-        <v xml:space="preserve">    Diğer Finansal Yükümlülükler</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="str">
-        <v xml:space="preserve">    Ticari Borçlar</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="str">
-        <v xml:space="preserve">    Finans Sektörü Faaliyetlerinden Borçlar</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="str">
-        <v xml:space="preserve">    Çalışanlara Sağlanan Faydalar Kapsamında Borçlar</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="str">
-        <v xml:space="preserve">    Diğer Borçlar</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="str">
-        <v xml:space="preserve">    Müşteri Sözleşmelerinden Doğan Yükümlülükler</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="str">
-        <v xml:space="preserve">    Devlet Teşvik ve Yardımları</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="str">
-        <v xml:space="preserve">    Özkaynak Yöntemiyle Değerlenen Yatırımlardan Yükümlülükler</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="str">
-        <v xml:space="preserve">    Türev Araçlar</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="str">
-        <v xml:space="preserve">    Devlet Teşvik ve Yardımları</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="str">
-        <v xml:space="preserve">    Ertelenmiş Gelirler</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="str">
-        <v xml:space="preserve">    Uzun vadeli Karşılıklar</v>
-      </c>
-      <c r="B80">
-        <v>187143</v>
-      </c>
-      <c r="C80">
-        <v>177190.9974756624</v>
-      </c>
-      <c r="D80">
-        <v>43153</v>
-      </c>
-      <c r="E80">
-        <v>26265.16652609571</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="str">
-        <v xml:space="preserve">    Cari Dönem Vergisiyle İlgili Borçlar</v>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="str">
-        <v xml:space="preserve">    Ertelenmiş Vergi Yükümlülüğü</v>
-      </c>
-      <c r="B82">
-        <v>249186072</v>
-      </c>
-      <c r="C82">
-        <v>252474210.12270954</v>
-      </c>
-      <c r="D82">
-        <v>994951837</v>
-      </c>
-      <c r="E82">
-        <v>313467316.7436639</v>
-      </c>
-      <c r="F82">
-        <v>1704057.164049275</v>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="str">
-        <v xml:space="preserve">    Diğer Uzun Vadeli Yükümlülükler</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="str">
-        <v xml:space="preserve">    Toplam Uzun Vadeli Yükümlülükler</v>
-      </c>
-      <c r="B84">
-        <v>347240236</v>
-      </c>
-      <c r="C84">
-        <v>360262312.73048687</v>
-      </c>
-      <c r="D84">
-        <v>1020626764</v>
-      </c>
-      <c r="E84">
-        <v>354739502.38525844</v>
-      </c>
-      <c r="F84">
-        <v>1704057.164049275</v>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="str">
-        <v>Özkaynaklar</v>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="str">
-        <v xml:space="preserve">    Ana Ortaklığa Ait Özkaynaklar</v>
-      </c>
-      <c r="B86">
-        <v>2513755770</v>
-      </c>
-      <c r="C86">
-        <v>2535818574.5397596</v>
-      </c>
-      <c r="D86">
-        <v>2373240539</v>
-      </c>
-      <c r="E86">
-        <v>1418047261.8393512</v>
-      </c>
-      <c r="F86">
-        <v>6560138.847470613</v>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="str">
-        <v xml:space="preserve">    Ödenmiş Sermaye</v>
-      </c>
-      <c r="B87">
-        <v>168242225</v>
-      </c>
-      <c r="C87">
-        <v>168242225</v>
-      </c>
-      <c r="D87">
-        <v>168242225</v>
-      </c>
-      <c r="E87">
-        <v>168242225</v>
-      </c>
-      <c r="F87">
-        <v>50000</v>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="str">
-        <v xml:space="preserve">    Sermaye Düzeltme Farkları</v>
-      </c>
-      <c r="B88">
-        <v>160140016</v>
-      </c>
-      <c r="C88">
-        <v>160140015.28618562</v>
-      </c>
-      <c r="D88">
-        <v>160140016</v>
-      </c>
-      <c r="E88">
-        <v>160140015.28618562</v>
-      </c>
-      <c r="F88">
-        <v>531438.0930381739</v>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="str">
-        <v xml:space="preserve">    Birleşme Denkleştirme Hesabı</v>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="str">
-        <v xml:space="preserve">    Pay Sahiplerinin İlave Sermaye Katkıları</v>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="str">
-        <v xml:space="preserve">    Sermaye Avansı</v>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="str">
-        <v xml:space="preserve">    Geri Alınmış Paylar (-)</v>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="str">
-        <v xml:space="preserve">    Karşılıklı İştirak Sermaye Düzeltmesi (-)</v>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="str">
-        <v xml:space="preserve">    Paylara İlişkin Primler (İskontolar)</v>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="str">
-        <v xml:space="preserve">    Ortak Kontrole Tabi Teşebbüs veya İşletmeleri İçeren Birleşmelerin Etkisi</v>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="str">
-        <v xml:space="preserve">    Pay Bazlı Ödemeler (-)</v>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="str">
-        <v xml:space="preserve">    Kar veya Zararda Yeniden Sınıflandırılmayacak Birikmiş Diğer Kapsamlı Gelirler (Giderler)</v>
-      </c>
-      <c r="B97">
-        <v>-30888</v>
-      </c>
-      <c r="C97">
-        <v>-18607.580131384348</v>
-      </c>
-      <c r="D97">
-        <v>711</v>
-      </c>
-      <c r="E97">
-        <v>-2335.4699306846596</v>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="str">
-        <v xml:space="preserve">    Kar veya Zararda Yeniden Sınıflandırılacak Birikmiş Diğer Kapsamlı Gelirler (Giderler)</v>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="str">
-        <v xml:space="preserve">    Kardan Ayrılan Kısıtlanmış Yedekler</v>
-      </c>
-      <c r="B99">
-        <v>23469</v>
-      </c>
-      <c r="C99">
-        <v>23469.49005410992</v>
-      </c>
-      <c r="D99">
-        <v>23469</v>
-      </c>
-      <c r="E99">
-        <v>6313251.082465654</v>
-      </c>
-      <c r="F99">
-        <v>6313251.082465654</v>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="str">
-        <v xml:space="preserve">    Diğer Özkaynak Payları</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="str">
-        <v xml:space="preserve">    Diğer Yedekler</v>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="str">
-        <v xml:space="preserve">    Ödenen Kar Payı Avansları (Net) (-)</v>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="str">
-        <v xml:space="preserve">    Geçmiş Yıllar Kar/Zararları</v>
-      </c>
-      <c r="B103">
-        <v>2044834118</v>
-      </c>
-      <c r="C103">
-        <v>2044834117.8928611</v>
-      </c>
-      <c r="D103">
-        <v>1083354106</v>
-      </c>
-      <c r="E103">
-        <v>-334550.3280332143</v>
-      </c>
-      <c r="F103">
-        <v>-164964.73933987087</v>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="str">
-        <v xml:space="preserve">    Dönem Net Kar/Zararı</v>
-      </c>
-      <c r="B104">
-        <v>140546830</v>
-      </c>
-      <c r="C104">
-        <v>162597354.45079026</v>
-      </c>
-      <c r="D104">
-        <v>961480012</v>
-      </c>
-      <c r="E104">
-        <v>1083688656.2686636</v>
-      </c>
-      <c r="F104">
-        <v>-169585.58869334348</v>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="str">
-        <v xml:space="preserve">    Azınlık Payları</v>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="str">
-        <v xml:space="preserve">    Toplam Özkaynaklar</v>
-      </c>
-      <c r="B106">
-        <v>2513755770</v>
-      </c>
-      <c r="C106">
-        <v>2535818574.5397596</v>
-      </c>
-      <c r="D106">
-        <v>2373240539</v>
-      </c>
-      <c r="E106">
-        <v>1418047261.8393512</v>
-      </c>
-      <c r="F106">
-        <v>6560138.847470613</v>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="str">
-        <v xml:space="preserve">    Toplam Kaynaklar</v>
-      </c>
-      <c r="B107">
-        <v>3000440876</v>
-      </c>
-      <c r="C107">
-        <v>3029942967.196791</v>
-      </c>
-      <c r="D107">
-        <v>3555214308</v>
-      </c>
-      <c r="E107">
-        <v>1831697020.9123816</v>
-      </c>
-      <c r="F107">
-        <v>29865997.82201341</v>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="str">
-        <v xml:space="preserve">    Hedge Dahil Net Yabancı Para Pozisyonu</v>
-      </c>
-      <c r="B108">
-        <v>19</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F108"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G50"/>
+  <dimension ref="A1:H108"/>
   <cols>
     <col min="1" max="1" customWidth="1" width="40" level="2" outlineLevel="2"/>
     <col min="2" max="2" customWidth="1" width="20"/>
@@ -1496,6 +412,7 @@
     <col min="5" max="5" customWidth="1" width="20"/>
     <col min="6" max="6" customWidth="1" width="20"/>
     <col min="7" max="7" customWidth="1" width="20"/>
+    <col min="8" max="8" customWidth="1" width="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1503,627 +420,1301 @@
         <v>Kalem</v>
       </c>
       <c r="B1" t="str">
+        <v>2026/6</v>
+      </c>
+      <c r="C1" t="str">
+        <v>2026/3</v>
+      </c>
+      <c r="D1" t="str">
         <v>2025/12</v>
       </c>
-      <c r="C1" t="str">
+      <c r="E1" t="str">
         <v>2025/9</v>
       </c>
-      <c r="D1" t="str">
+      <c r="F1" t="str">
         <v>2024/12</v>
       </c>
-      <c r="E1" t="str">
-        <v>2024/9</v>
-      </c>
-      <c r="F1" t="str">
+      <c r="G1" t="str">
         <v>2023/12</v>
       </c>
-      <c r="G1" t="str">
+      <c r="H1" t="str">
         <v>2022/12</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v/>
+        <v>Dönen Varlıklar</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v xml:space="preserve">    Satış Gelirleri</v>
+        <v xml:space="preserve">    Nakit ve Nakit Benzerleri</v>
       </c>
       <c r="B3">
-        <v>11649948</v>
+        <v>19085804</v>
       </c>
       <c r="C3">
-        <v>8562942.061929425</v>
+        <v>87086041.1027972</v>
       </c>
       <c r="D3">
-        <v>6074812</v>
+        <v>4371768</v>
       </c>
       <c r="E3">
-        <v>3129733.1998057743</v>
+        <v>12096545.668747514</v>
       </c>
       <c r="F3">
-        <v>3985014.0124108316</v>
+        <v>52651.631457623655</v>
       </c>
       <c r="G3">
-        <v>1264168.5850137502</v>
+        <v>12739184.304155953</v>
+      </c>
+      <c r="H3">
+        <v>282422.61349124805</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v xml:space="preserve">    Toplam Hasılat</v>
+        <v xml:space="preserve">    Gayrimenkul Projeleri Kapsamında Açılan Nakit Hesapları</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v xml:space="preserve">    Yurt İçi Satışlar</v>
+        <v xml:space="preserve">    Finansal Yatırımlar</v>
       </c>
       <c r="B5">
-        <v>11649948</v>
+        <v>142439305</v>
+      </c>
+      <c r="C5">
+        <v>229839946.40675095</v>
       </c>
       <c r="D5">
-        <v>6074812</v>
+        <v>41625</v>
+      </c>
+      <c r="E5">
+        <v>4017.228802988816</v>
+      </c>
+      <c r="F5">
+        <v>27402929.08109008</v>
+      </c>
+      <c r="G5">
+        <v>1349.3169855251515</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v xml:space="preserve">    Yurt Dışı Satışlar</v>
+        <v xml:space="preserve">    Teminata Verilen Finansal Varlıklar</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v xml:space="preserve">    Satışların Maliyeti (-)</v>
+        <v xml:space="preserve">    Ticari Alacaklar</v>
+      </c>
+      <c r="B7">
+        <v>46357105</v>
+      </c>
+      <c r="C7">
+        <v>3807856.794372004</v>
+      </c>
+      <c r="D7">
+        <v>8056509</v>
+      </c>
+      <c r="E7">
+        <v>32533106.56750079</v>
       </c>
       <c r="F7">
-        <v>-1867788.424632189</v>
+        <v>7550310.603129884</v>
       </c>
       <c r="G7">
-        <v>-1029283.7579635426</v>
+        <v>880080.3293904172</v>
+      </c>
+      <c r="H7">
+        <v>224049.29279049186</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v xml:space="preserve">    Ticari Faaliyetlerden Brüt Kar (Zarar)</v>
-      </c>
-      <c r="B8">
-        <v>11649948</v>
-      </c>
-      <c r="C8">
-        <v>8562942.061929425</v>
-      </c>
-      <c r="D8">
-        <v>6074812</v>
-      </c>
-      <c r="E8">
-        <v>3129733.1998057743</v>
-      </c>
-      <c r="F8">
-        <v>2117225.5877786423</v>
-      </c>
-      <c r="G8">
-        <v>234884.8270502076</v>
+        <v xml:space="preserve">    Finans Sektörü Faaliyetlerinden Alacaklar</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v xml:space="preserve">    Faiz, Ücret, Prim, Komisyon ve Diğer Gelirler</v>
+        <v xml:space="preserve">    Türkiye Cumhuriyet Merkez Bankası Hesabı</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v xml:space="preserve">    Faiz, Ücret, Prim, Komisyon ve Diğer Giderler (-)</v>
+        <v xml:space="preserve">    Diğer Alacaklar</v>
+      </c>
+      <c r="B10">
+        <v>2719873</v>
+      </c>
+      <c r="C10">
+        <v>2876463.514410072</v>
+      </c>
+      <c r="D10">
+        <v>1022021</v>
+      </c>
+      <c r="E10">
+        <v>980869.8842190295</v>
+      </c>
+      <c r="F10">
+        <v>983424.7488666343</v>
+      </c>
+      <c r="G10">
+        <v>1805042.0385124823</v>
+      </c>
+      <c r="H10">
+        <v>2792334.081717263</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v xml:space="preserve">    Finans Sektörü Faaliyetlerinden Brüt Kar (Zarar)</v>
+        <v xml:space="preserve">    Müşteri Sözleşmelerinden Doğan Varlıklar</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v xml:space="preserve">    Canlı Varlıklar Gerçeğe Uygun Değer Farkları</v>
+        <v xml:space="preserve">    İmtiyaz Sözleşmelerine İlişkin Finansal Varlıklar</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v xml:space="preserve">    Brüt Kar (Zarar)</v>
-      </c>
-      <c r="B13">
-        <v>11649948</v>
-      </c>
-      <c r="C13">
-        <v>8562942.061929425</v>
-      </c>
-      <c r="D13">
-        <v>6074812</v>
-      </c>
-      <c r="E13">
-        <v>3129733.1998057743</v>
-      </c>
-      <c r="F13">
-        <v>2117225.5877786423</v>
-      </c>
-      <c r="G13">
-        <v>234884.8270502076</v>
-      </c>
-    </row>
-    <row r="14"/>
+        <v xml:space="preserve">    Türev Araçlar</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v xml:space="preserve">    Stoklar</v>
+      </c>
+      <c r="B14">
+        <v>22891982</v>
+      </c>
+      <c r="C14">
+        <v>22891837.053623985</v>
+      </c>
+      <c r="D14">
+        <v>22891982</v>
+      </c>
+      <c r="E14">
+        <v>22304188.879666317</v>
+      </c>
+      <c r="F14">
+        <v>25851920.428117722</v>
+      </c>
+      <c r="G14">
+        <v>34425422.87103605</v>
+      </c>
+      <c r="H14">
+        <v>11781056.186907895</v>
+      </c>
+    </row>
     <row r="15">
       <c r="A15" t="str">
-        <v xml:space="preserve">    Genel Yönetim Giderleri (-)</v>
-      </c>
-      <c r="B15">
-        <v>-17514946</v>
-      </c>
-      <c r="C15">
-        <v>-10028336.739791282</v>
-      </c>
-      <c r="D15">
-        <v>-11510472</v>
-      </c>
-      <c r="E15">
-        <v>-8191997.849252499</v>
-      </c>
-      <c r="F15">
-        <v>-5880243.686952441</v>
-      </c>
-      <c r="G15">
-        <v>-5326483.73018395</v>
+        <v xml:space="preserve">    Proje Halindeki Stoklar</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v xml:space="preserve">    Pazarlama, Satış ve Dağıtım Giderleri (-)</v>
+        <v xml:space="preserve">    Canlı Varlıklar</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v xml:space="preserve">    Araştırma ve Geliştirme Giderleri (-)</v>
+        <v xml:space="preserve">    Peşin Ödenmiş Giderler</v>
+      </c>
+      <c r="B17">
+        <v>172708819</v>
+      </c>
+      <c r="C17">
+        <v>27885260.008459326</v>
+      </c>
+      <c r="D17">
+        <v>6554541</v>
+      </c>
+      <c r="E17">
+        <v>1049388.888920237</v>
+      </c>
+      <c r="F17">
+        <v>35731.88820018954</v>
+      </c>
+      <c r="G17">
+        <v>40496141.31082021</v>
+      </c>
+      <c r="H17">
+        <v>8538755.612671582</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v xml:space="preserve">    Diğer Faaliyet Gelirleri</v>
-      </c>
-      <c r="B18">
-        <v>180669516</v>
-      </c>
-      <c r="C18">
-        <v>184377930.32751945</v>
-      </c>
-      <c r="D18">
-        <v>1714258679</v>
-      </c>
-      <c r="E18">
-        <v>1974310056.5786939</v>
-      </c>
-      <c r="F18">
-        <v>1467970842.074955</v>
-      </c>
-      <c r="G18">
-        <v>82128.60545791483</v>
+        <v xml:space="preserve">    Ertelenmiş Sigortacılık Üretim Giderleri</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v xml:space="preserve">    Diğer Faaliyet Giderleri (-)</v>
+        <v xml:space="preserve">    Cari Dönem Vergisiyle İlgili Varlıklar</v>
       </c>
       <c r="B19">
-        <v>-774325438</v>
-      </c>
-      <c r="C19">
-        <v>-756983922.0466853</v>
-      </c>
-      <c r="D19">
-        <v>-90038483</v>
+        <v>3004687</v>
       </c>
       <c r="E19">
-        <v>-49514895.95588349</v>
-      </c>
-      <c r="F19">
-        <v>-80593786.37966037</v>
-      </c>
-      <c r="G19">
-        <v>-928808.4604362055</v>
+        <v>166747.5608068377</v>
+      </c>
+      <c r="H19">
+        <v>3083.2753339550136</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v xml:space="preserve">    Diğer Kazançlar (Kayıplar)</v>
+        <v xml:space="preserve">    Nakit Dışı Serbest Kullanılabilir Teminatlar</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v xml:space="preserve">    Faaliyet Karı (Zararı)</v>
+        <v xml:space="preserve">    Diğer Dönen Varlıklar</v>
       </c>
       <c r="B21">
-        <v>-599520920</v>
+        <v>18361091</v>
       </c>
       <c r="C21">
-        <v>-574071386.3970279</v>
+        <v>17803438.634850033</v>
       </c>
       <c r="D21">
-        <v>1618784536</v>
+        <v>18938278</v>
       </c>
       <c r="E21">
-        <v>1919732895.9733636</v>
+        <v>19757290.396294273</v>
       </c>
       <c r="F21">
-        <v>1383614037.5961208</v>
+        <v>21223051.736265145</v>
       </c>
       <c r="G21">
-        <v>-5938278.758112033</v>
-      </c>
-    </row>
-    <row r="22"/>
+        <v>11715125.216424828</v>
+      </c>
+      <c r="H21">
+        <v>435871.16845350177</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v xml:space="preserve">    Satış Amacıyla Elde Tutulan Duran Varlıklar</v>
+      </c>
+    </row>
     <row r="23">
       <c r="A23" t="str">
-        <v xml:space="preserve">    Ödenecek Kar Paylarının Defter Değeri ile Dağıtılan Nakit Dışı Varlıkların Değeri Arasındaki Fark</v>
+        <v xml:space="preserve">    Ortaklara Dağıtılmak Üzere Elde Tutulan Duran Varlıklar</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v xml:space="preserve">    İtfa Edilmiş Maliyetinden Ölçülen Finansal Varlıkların Finansal Tablo Dışı Bırakılmasından Kaynaklanan Kazançlar (Kayıplar)</v>
+        <v xml:space="preserve">    Toplam Dönen Varlıklar</v>
+      </c>
+      <c r="B24">
+        <v>427568666</v>
+      </c>
+      <c r="C24">
+        <v>392190843.51526356</v>
+      </c>
+      <c r="D24">
+        <v>61876724</v>
+      </c>
+      <c r="E24">
+        <v>88892155.074958</v>
+      </c>
+      <c r="F24">
+        <v>83100020.11712728</v>
+      </c>
+      <c r="G24">
+        <v>102062345.38732547</v>
+      </c>
+      <c r="H24">
+        <v>24057572.231365934</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v xml:space="preserve">    Yatırım Faaliyetlerinden Gelirler</v>
-      </c>
-      <c r="B25">
-        <v>3942494</v>
-      </c>
-      <c r="C25">
-        <v>7225568.286729111</v>
-      </c>
-      <c r="D25">
-        <v>285604</v>
-      </c>
-      <c r="E25">
-        <v>155171.00149381388</v>
-      </c>
-      <c r="F25">
-        <v>87825.3571789191</v>
+        <v>Duran Varlıklar</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v xml:space="preserve">    Yatırım Faaliyetlerinden Giderler (-)</v>
+        <v xml:space="preserve">    Finansal Yatırımlar</v>
+      </c>
+      <c r="B26">
+        <v>99511</v>
+      </c>
+      <c r="D26">
+        <v>99511</v>
+      </c>
+      <c r="E26">
+        <v>99511.51323940817</v>
+      </c>
+      <c r="F26">
+        <v>99511.83075071077</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v xml:space="preserve">    TFRS 9 Uyarınca Belirlenen Değer Düşüklüğü Kazançları (Zararları) ve Değer Düşüklüğü Zararlarının İptalleri</v>
+        <v xml:space="preserve">    İştirakler, İş Ortaklıkları ve Bağlı Ortaklıklardaki Yatırımlar</v>
+      </c>
+      <c r="C27">
+        <v>99509.62175889769</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v xml:space="preserve">    Özkaynak Yöntemiyle Değerlenen Yatırımların Karlarından (Zararlarından) Paylar</v>
+        <v xml:space="preserve">    Ticari Alacaklar</v>
+      </c>
+      <c r="B28">
+        <v>10888719</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v xml:space="preserve">    İştirakler, Müşterek Kontrol Edilen İşletmeler ve Bağlı Ortaklıklardan Diğer Gelirler (Giderler)</v>
+        <v xml:space="preserve">    Finans Sektörü Faaliyetlerinden Alacaklar</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v xml:space="preserve">    İtfa Edilmiş Maliyetinden Ölçülen Finansal Varlıkların Gerçeğe Uygun Değer Farkı Kar veya Zarara Yansıtılan Olarak Sınıflandırılmasından Kazançlar (Kayıplar)</v>
+        <v xml:space="preserve">    Diğer Alacaklar</v>
+      </c>
+      <c r="B30">
+        <v>20343</v>
+      </c>
+      <c r="C30">
+        <v>20342.177485427004</v>
+      </c>
+      <c r="D30">
+        <v>20343</v>
+      </c>
+      <c r="E30">
+        <v>20341.752332784912</v>
+      </c>
+      <c r="F30">
+        <v>20343.023717439748</v>
+      </c>
+      <c r="G30">
+        <v>9502.97654741894</v>
+      </c>
+      <c r="H30">
+        <v>15657.23835389431</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v xml:space="preserve">    Gerçeğe Uygun Değer Farkı Diğer Kapsamlı Gelire Yansıtılan Finansal Varlıkların Gerçeğe Uygun Değer Farkı Kar veya Zarara Yansıtılan Olarak Sınıflandırılmasından Kazançlar (Kayıplar)</v>
+        <v xml:space="preserve">    Müşteri Sözleşmelerinden Doğan Varlıklar</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v xml:space="preserve">    Risk Pozisyonlarını Netleştiren Kalemler Grubuna Yönelik Finansal Riskten Korunma Kazançları (Kayıpları)</v>
+        <v xml:space="preserve">    İmtiyaz Sözleşmelerine İlişkin Finansal Varlıklar</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v xml:space="preserve">    Finansman Geliri (Gideri) Öncesi Faaliyet Karı (Zararı)</v>
-      </c>
-      <c r="B33">
-        <v>-595578426</v>
-      </c>
-      <c r="C33">
-        <v>-566845818.1102986</v>
-      </c>
-      <c r="D33">
-        <v>1619070140</v>
-      </c>
-      <c r="E33">
-        <v>1919888066.9748576</v>
-      </c>
-      <c r="F33">
-        <v>1383701862.9532998</v>
-      </c>
-      <c r="G33">
-        <v>-5938278.758112033</v>
-      </c>
-    </row>
-    <row r="34"/>
+        <v xml:space="preserve">    Türev Araçlar</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="str">
+        <v xml:space="preserve">    Stoklar</v>
+      </c>
+    </row>
     <row r="35">
       <c r="A35" t="str">
-        <v xml:space="preserve">    (Esas Faaliyet Dışı) Finansal Gelirler</v>
-      </c>
-      <c r="B35">
-        <v>9690193</v>
-      </c>
-      <c r="C35">
-        <v>10458281.30945706</v>
-      </c>
-      <c r="D35">
-        <v>6991160</v>
-      </c>
-      <c r="E35">
-        <v>4102796.623968734</v>
-      </c>
-      <c r="F35">
-        <v>117244.1385980126</v>
-      </c>
-      <c r="G35">
-        <v>62050.66020931213</v>
+        <v xml:space="preserve">    Özkaynak Yöntemiyle Değerlenen Yatırımlar</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v xml:space="preserve">    (Esas Faaliyet Dışı) Finansal Giderler (-)</v>
-      </c>
-      <c r="B36">
-        <v>-63066868</v>
-      </c>
-      <c r="C36">
-        <v>-43020315.14772721</v>
-      </c>
-      <c r="D36">
-        <v>-6025375</v>
-      </c>
-      <c r="E36">
-        <v>-4979735.319925636</v>
-      </c>
-      <c r="F36">
-        <v>-2003167.4141933108</v>
-      </c>
-      <c r="G36">
-        <v>-218610.6297450122</v>
+        <v xml:space="preserve">    Canlı Varlıklar</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v xml:space="preserve">    Net Parasal Pozisyon Kazançları (Kayıpları)</v>
+        <v xml:space="preserve">    Yatırım Amaçlı Gayrimenkuller</v>
       </c>
       <c r="B37">
-        <v>45286641</v>
+        <v>5373169206</v>
       </c>
       <c r="C37">
-        <v>21144064.3138108</v>
+        <v>3526650237.6174197</v>
       </c>
       <c r="D37">
-        <v>23210954</v>
+        <v>3468153015</v>
       </c>
       <c r="E37">
-        <v>20356213.673252713</v>
+        <v>3475450997.805312</v>
       </c>
       <c r="F37">
-        <v>13636752.573446345</v>
+        <v>4097759523.0964584</v>
       </c>
       <c r="G37">
-        <v>7046409.149714007</v>
+        <v>2047950854.0116153</v>
+      </c>
+      <c r="H37">
+        <v>1503379.983559138</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v xml:space="preserve">    Sürdürülen Faaliyetler Vergi Öncesi Karı (Zararı)</v>
-      </c>
-      <c r="B38">
-        <v>-603668460</v>
-      </c>
-      <c r="C38">
-        <v>-578263787.634758</v>
-      </c>
-      <c r="D38">
-        <v>1643246879</v>
-      </c>
-      <c r="E38">
-        <v>1939367341.9521534</v>
-      </c>
-      <c r="F38">
-        <v>1395452692.2511508</v>
-      </c>
-      <c r="G38">
-        <v>951570.4220662742</v>
-      </c>
-    </row>
-    <row r="39"/>
+        <v xml:space="preserve">    Proje Halindeki Yatırım Amaçlı Gayrimenkuller</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="str">
+        <v xml:space="preserve">    Maddi Duran Varlıklar</v>
+      </c>
+      <c r="B39">
+        <v>964018</v>
+      </c>
+      <c r="C39">
+        <v>1305321.647646338</v>
+      </c>
+      <c r="D39">
+        <v>3111947</v>
+      </c>
+      <c r="E39">
+        <v>3579283.2747251447</v>
+      </c>
+      <c r="F39">
+        <v>5610266.792741337</v>
+      </c>
+      <c r="G39">
+        <v>6981982.983951153</v>
+      </c>
+      <c r="H39">
+        <v>9593561.431712214</v>
+      </c>
+    </row>
     <row r="40">
       <c r="A40" t="str">
-        <v xml:space="preserve">    Sürdürülen Faaliyetler Vergi Geliri (Gideri)</v>
-      </c>
-      <c r="B40">
-        <v>744215290</v>
-      </c>
-      <c r="C40">
-        <v>740861142.0855483</v>
-      </c>
-      <c r="D40">
-        <v>-681766867</v>
-      </c>
-      <c r="E40">
-        <v>-720481649.8923029</v>
-      </c>
-      <c r="F40">
-        <v>-311764035.982487</v>
-      </c>
-      <c r="G40">
-        <v>-1121156.0107596177</v>
+        <v xml:space="preserve">    Kullanım Hakkı Varlıkları</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v xml:space="preserve">    Dönem Vergi Geliri (Gideri)</v>
+        <v xml:space="preserve">    Maddi Olmayan Duran Varlıklar</v>
       </c>
       <c r="B41">
-        <v>-1546967</v>
+        <v>220677</v>
       </c>
       <c r="C41">
-        <v>-1614340.8901972547</v>
+        <v>7918.991708777938</v>
       </c>
       <c r="D41">
-        <v>-283646</v>
+        <v>11763</v>
       </c>
       <c r="E41">
-        <v>-301431.1103432505</v>
+        <v>15692.876052054813</v>
       </c>
       <c r="F41">
-        <v>-311764035.982487</v>
-      </c>
-      <c r="G41">
-        <v>-1121156.0107596177</v>
+        <v>27353.270906436497</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v xml:space="preserve">    Ertelenmiş Vergi Geliri (Gideri)</v>
-      </c>
-      <c r="B42">
-        <v>745762257</v>
-      </c>
-      <c r="C42">
-        <v>742475482.9757456</v>
-      </c>
-      <c r="D42">
-        <v>-681483221</v>
-      </c>
-      <c r="E42">
-        <v>-720180218.7819595</v>
-      </c>
-      <c r="F42">
-        <v>-311764035.982487</v>
-      </c>
-      <c r="G42">
-        <v>-1121156.0107596177</v>
+        <v xml:space="preserve">    Peşin Ödenmiş Giderler</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v xml:space="preserve">    Sürdürülen Faaliyetler Dönem Karı/Zararı</v>
-      </c>
-      <c r="B43">
-        <v>140546830</v>
-      </c>
-      <c r="C43">
-        <v>162597354.45079026</v>
-      </c>
-      <c r="D43">
-        <v>961480012</v>
-      </c>
-      <c r="E43">
-        <v>1218885692.0598505</v>
-      </c>
-      <c r="F43">
-        <v>1083688656.2686636</v>
-      </c>
-      <c r="G43">
-        <v>-169585.58869334348</v>
+        <v xml:space="preserve">    Ertelenmiş Vergi Varlığı</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v xml:space="preserve">    Durdurulan Faaliyetler Dönem Karı/Zararı</v>
-      </c>
-    </row>
-    <row r="45"/>
+        <v xml:space="preserve">    Cari Dönem Vergisiyle İlgili Duran Varlıklar</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="str">
+        <v xml:space="preserve">    Nakit Dışı Serbest Kullanılabilir Teminatlar</v>
+      </c>
+    </row>
     <row r="46">
       <c r="A46" t="str">
-        <v xml:space="preserve">    Dönem Karı (Zararı)</v>
-      </c>
-      <c r="B46">
-        <v>140546830</v>
-      </c>
-      <c r="C46">
-        <v>162597354.45079026</v>
-      </c>
-      <c r="D46">
-        <v>961480012</v>
-      </c>
-      <c r="E46">
-        <v>1218885692.0598505</v>
-      </c>
-      <c r="F46">
-        <v>1083688656.2686636</v>
-      </c>
-      <c r="G46">
-        <v>-169585.58869334348</v>
+        <v xml:space="preserve">    Diğer Duran Varlıklar</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v xml:space="preserve">    Azınlık Payları</v>
+        <v xml:space="preserve">    Toplam Duran Varlıklar</v>
       </c>
       <c r="B47">
-        <v>0</v>
+        <v>5385362474</v>
+      </c>
+      <c r="C47">
+        <v>3528083330.0560193</v>
+      </c>
+      <c r="D47">
+        <v>3471396579</v>
+      </c>
+      <c r="E47">
+        <v>3479165827.221661</v>
+      </c>
+      <c r="F47">
+        <v>4103516998.0145745</v>
+      </c>
+      <c r="G47">
+        <v>2054942339.9721138</v>
+      </c>
+      <c r="H47">
+        <v>11112598.653625248</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v xml:space="preserve">    Ana Ortaklık Payları</v>
+        <v xml:space="preserve">    Toplam Varlıklar</v>
       </c>
       <c r="B48">
-        <v>140546830</v>
+        <v>5812931140</v>
       </c>
       <c r="C48">
-        <v>162597354.45079026</v>
+        <v>3920274173.571283</v>
       </c>
       <c r="D48">
-        <v>961480012</v>
+        <v>3533273303</v>
       </c>
       <c r="E48">
-        <v>1218885692.0598505</v>
+        <v>3568057982.296619</v>
       </c>
       <c r="F48">
-        <v>1083688656.2686636</v>
+        <v>4186617018.1317015</v>
       </c>
       <c r="G48">
-        <v>-169585.58869334348</v>
-      </c>
-    </row>
-    <row r="49"/>
+        <v>2157004685.359439</v>
+      </c>
+      <c r="H48">
+        <v>35170170.884991184</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="str">
+        <v>Kısa Vadeli Yükümlülükler</v>
+      </c>
+    </row>
     <row r="50">
       <c r="A50" t="str">
-        <v xml:space="preserve">    Amortisman</v>
+        <v xml:space="preserve">    Finansal Borçlar</v>
       </c>
       <c r="B50">
-        <v>1843955</v>
+        <v>82675100</v>
       </c>
       <c r="C50">
-        <v>-130651192.79908055</v>
+        <v>87608324.28920746</v>
       </c>
       <c r="D50">
-        <v>2194826</v>
+        <v>108462335</v>
       </c>
       <c r="E50">
-        <v>-1237243047.1461413</v>
+        <v>101320009.67686996</v>
       </c>
       <c r="F50">
-        <v>-1086002733.3782675</v>
+        <v>8678938.026176268</v>
       </c>
       <c r="G50">
-        <v>3747590.2227416085</v>
+        <v>10122263.888329245</v>
+      </c>
+      <c r="H50">
+        <v>3285145.68962824</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="str">
+        <v xml:space="preserve">    Diğer Finansal Yükümlülükler</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="str">
+        <v xml:space="preserve">    Ticari Borçlar</v>
+      </c>
+      <c r="B52">
+        <v>1236260</v>
+      </c>
+      <c r="C52">
+        <v>146463.89192187737</v>
+      </c>
+      <c r="D52">
+        <v>19737299</v>
+      </c>
+      <c r="E52">
+        <v>16750736.882048102</v>
+      </c>
+      <c r="F52">
+        <v>210308.5932689599</v>
+      </c>
+      <c r="G52">
+        <v>7945455.527037141</v>
+      </c>
+      <c r="H52">
+        <v>1031748.2283307893</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="str">
+        <v xml:space="preserve">    Finans Sektörü Faaliyetlerinden Borçlar</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="str">
+        <v xml:space="preserve">    Çalışanlara Sağlanan Faydalar Kapsamında Borçlar</v>
+      </c>
+      <c r="B54">
+        <v>314496</v>
+      </c>
+      <c r="C54">
+        <v>523802.7767111314</v>
+      </c>
+      <c r="D54">
+        <v>338660</v>
+      </c>
+      <c r="E54">
+        <v>362987.16017070465</v>
+      </c>
+      <c r="F54">
+        <v>133144.0598314679</v>
+      </c>
+      <c r="H54">
+        <v>75934.10369087853</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="str">
+        <v xml:space="preserve">    Diğer Borçlar</v>
+      </c>
+      <c r="F55">
+        <v>141525801.29552034</v>
+      </c>
+      <c r="G55">
+        <v>50376605.87490274</v>
+      </c>
+      <c r="H55">
+        <v>20623151.284118652</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="str">
+        <v xml:space="preserve">    Müşteri Sözleşmelerinden Doğan Yükümlülükler</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="str">
+        <v xml:space="preserve">    Özkaynak Yöntemiyle Değerlenen Yatırımlardan Yükümlülükler</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="str">
+        <v xml:space="preserve">    Türev Araçlar</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="str">
+        <v xml:space="preserve">    Devlet Teşvik ve Yardımları</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="str">
+        <v xml:space="preserve">    Ertelenmiş Gelirler</v>
+      </c>
+      <c r="B60">
+        <v>134995449</v>
+      </c>
+      <c r="C60">
+        <v>29648300.447007045</v>
+      </c>
+      <c r="D60">
+        <v>35292852</v>
+      </c>
+      <c r="E60">
+        <v>38673789.18209087</v>
+      </c>
+      <c r="F60">
+        <v>33459868.617114466</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="str">
+        <v xml:space="preserve">    Dönem Karı Vergi Yükümlülüğü</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="str">
+        <v xml:space="preserve">    Kısa Vadeli Karşılıklar</v>
+      </c>
+      <c r="B62">
+        <v>55083</v>
+      </c>
+      <c r="C62">
+        <v>58946.19193170475</v>
+      </c>
+      <c r="D62">
+        <v>235615</v>
+      </c>
+      <c r="E62">
+        <v>367949.4024180185</v>
+      </c>
+      <c r="F62">
+        <v>768865.0230002819</v>
+      </c>
+      <c r="G62">
+        <v>816389.6183468857</v>
+      </c>
+      <c r="H62">
+        <v>422282.14547905995</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="str">
+        <v xml:space="preserve">    Diğer Kısa Vadeli Yükümlülükler</v>
+      </c>
+      <c r="B63">
+        <v>100797</v>
+      </c>
+      <c r="C63">
+        <v>1994352.0460930916</v>
+      </c>
+      <c r="D63">
+        <v>141386</v>
+      </c>
+      <c r="E63">
+        <v>160386.84612826013</v>
+      </c>
+      <c r="F63">
+        <v>5225155.395384576</v>
+      </c>
+      <c r="G63">
+        <v>111947.84101127935</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="str">
+        <v xml:space="preserve">    Satış Amaçlı Sınıflandırılan Varlık Gruplarına İlişkin Yükümlülükler</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="str">
+        <v xml:space="preserve">    Ortaklara Dağıtılmak Üzere Elde Tutulan Varlık Gruplarına İlişkin Yükümlülükler</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="str">
+        <v xml:space="preserve">    Toplam Kısa Vadeli Yükümlülükler</v>
+      </c>
+      <c r="B66">
+        <v>219377185</v>
+      </c>
+      <c r="C66">
+        <v>119980189.6428723</v>
+      </c>
+      <c r="D66">
+        <v>164208147</v>
+      </c>
+      <c r="E66">
+        <v>157635859.14972588</v>
+      </c>
+      <c r="F66">
+        <v>190002081.01029634</v>
+      </c>
+      <c r="G66">
+        <v>69372662.74962729</v>
+      </c>
+      <c r="H66">
+        <v>25438261.45124762</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="str">
+        <v>Uzun Vadeli Yükümlülükler</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="str">
+        <v xml:space="preserve">    Finansal Borçlar</v>
+      </c>
+      <c r="B68">
+        <v>85160778</v>
+      </c>
+      <c r="C68">
+        <v>98227003.00437321</v>
+      </c>
+      <c r="D68">
+        <v>115246708</v>
+      </c>
+      <c r="E68">
+        <v>126722508.08357044</v>
+      </c>
+      <c r="F68">
+        <v>30183952.90315806</v>
+      </c>
+      <c r="G68">
+        <v>48571157.075076774</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="str">
+        <v xml:space="preserve">    Diğer Finansal Yükümlülükler</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="str">
+        <v xml:space="preserve">    Ticari Borçlar</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="str">
+        <v xml:space="preserve">    Finans Sektörü Faaliyetlerinden Borçlar</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="str">
+        <v xml:space="preserve">    Çalışanlara Sağlanan Faydalar Kapsamında Borçlar</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="str">
+        <v xml:space="preserve">    Diğer Borçlar</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="str">
+        <v xml:space="preserve">    Müşteri Sözleşmelerinden Doğan Yükümlülükler</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="str">
+        <v xml:space="preserve">    Devlet Teşvik ve Yardımları</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="str">
+        <v xml:space="preserve">    Özkaynak Yöntemiyle Değerlenen Yatırımlardan Yükümlülükler</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="str">
+        <v xml:space="preserve">    Türev Araçlar</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="str">
+        <v xml:space="preserve">    Devlet Teşvik ve Yardımları</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="str">
+        <v xml:space="preserve">    Ertelenmiş Gelirler</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="str">
+        <v xml:space="preserve">    Uzun vadeli Karşılıklar</v>
+      </c>
+      <c r="B80">
+        <v>368146</v>
+      </c>
+      <c r="C80">
+        <v>318338.11602279963</v>
+      </c>
+      <c r="D80">
+        <v>220379</v>
+      </c>
+      <c r="E80">
+        <v>208659.95161587308</v>
+      </c>
+      <c r="F80">
+        <v>50816.93212611736</v>
+      </c>
+      <c r="G80">
+        <v>30929.83534488391</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="str">
+        <v xml:space="preserve">    Cari Dönem Vergisiyle İlgili Borçlar</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="str">
+        <v xml:space="preserve">    Ertelenmiş Vergi Yükümlülüğü</v>
+      </c>
+      <c r="B82">
+        <v>1438860555</v>
+      </c>
+      <c r="C82">
+        <v>323156079.8045848</v>
+      </c>
+      <c r="D82">
+        <v>880313116</v>
+      </c>
+      <c r="E82">
+        <v>297313391.8708045</v>
+      </c>
+      <c r="F82">
+        <v>1171654345.4588277</v>
+      </c>
+      <c r="G82">
+        <v>369138816.7385559</v>
+      </c>
+      <c r="H82">
+        <v>2006696.1102244584</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="str">
+        <v xml:space="preserve">    Diğer Uzun Vadeli Yükümlülükler</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="str">
+        <v xml:space="preserve">    Toplam Uzun Vadeli Yükümlülükler</v>
+      </c>
+      <c r="B84">
+        <v>1524389479</v>
+      </c>
+      <c r="C84">
+        <v>421701420.9249808</v>
+      </c>
+      <c r="D84">
+        <v>995780203</v>
+      </c>
+      <c r="E84">
+        <v>424244559.9059907</v>
+      </c>
+      <c r="F84">
+        <v>1201889115.294112</v>
+      </c>
+      <c r="G84">
+        <v>417740903.6489775</v>
+      </c>
+      <c r="H84">
+        <v>2006696.1102244584</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="str">
+        <v>Özkaynaklar</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="str">
+        <v xml:space="preserve">    Ana Ortaklığa Ait Özkaynaklar</v>
+      </c>
+      <c r="B86">
+        <v>4069164476</v>
+      </c>
+      <c r="C86">
+        <v>3378592563.00343</v>
+      </c>
+      <c r="D86">
+        <v>2373284953</v>
+      </c>
+      <c r="E86">
+        <v>2986177563.2409024</v>
+      </c>
+      <c r="F86">
+        <v>2794725821.8272934</v>
+      </c>
+      <c r="G86">
+        <v>1669891118.9608345</v>
+      </c>
+      <c r="H86">
+        <v>7725213.323519105</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="str">
+        <v xml:space="preserve">    Ödenmiş Sermaye</v>
+      </c>
+      <c r="B87">
+        <v>210492225</v>
+      </c>
+      <c r="C87">
+        <v>210492225</v>
+      </c>
+      <c r="D87">
+        <v>168242225</v>
+      </c>
+      <c r="E87">
+        <v>168242225</v>
+      </c>
+      <c r="F87">
+        <v>168242225</v>
+      </c>
+      <c r="G87">
+        <v>168242225</v>
+      </c>
+      <c r="H87">
+        <v>50000</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="str">
+        <v xml:space="preserve">    Sermaye Düzeltme Farkları</v>
+      </c>
+      <c r="B88">
+        <v>223661635</v>
+      </c>
+      <c r="C88">
+        <v>223658893.20171005</v>
+      </c>
+      <c r="D88">
+        <v>218455682</v>
+      </c>
+      <c r="E88">
+        <v>218460391.64416048</v>
+      </c>
+      <c r="F88">
+        <v>218460392.48474762</v>
+      </c>
+      <c r="G88">
+        <v>218460391.64416048</v>
+      </c>
+      <c r="H88">
+        <v>634700.9503269761</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="str">
+        <v xml:space="preserve">    Birleşme Denkleştirme Hesabı</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="str">
+        <v xml:space="preserve">    Pay Sahiplerinin İlave Sermaye Katkıları</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="str">
+        <v xml:space="preserve">    Sermaye Avansı</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="str">
+        <v xml:space="preserve">    Geri Alınmış Paylar (-)</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="str">
+        <v xml:space="preserve">    Karşılıklı İştirak Sermaye Düzeltmesi (-)</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="str">
+        <v xml:space="preserve">    Paylara İlişkin Primler (İskontolar)</v>
+      </c>
+      <c r="B94">
+        <v>401845828</v>
+      </c>
+      <c r="C94">
+        <v>401843289.6674848</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="str">
+        <v xml:space="preserve">    Ortak Kontrole Tabi Teşebbüs veya İşletmeleri İçeren Birleşmelerin Etkisi</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="str">
+        <v xml:space="preserve">    Pay Bazlı Ödemeler (-)</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="str">
+        <v xml:space="preserve">    Kar veya Zararda Yeniden Sınıflandırılmayacak Birikmiş Diğer Kapsamlı Gelirler (Giderler)</v>
+      </c>
+      <c r="B97">
+        <v>17601</v>
+      </c>
+      <c r="C97">
+        <v>61703.92728758593</v>
+      </c>
+      <c r="D97">
+        <v>-28107</v>
+      </c>
+      <c r="E97">
+        <v>-21912.26882413386</v>
+      </c>
+      <c r="F97">
+        <v>837.2729298465796</v>
+      </c>
+      <c r="G97">
+        <v>-2750.247189075855</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="str">
+        <v xml:space="preserve">    Kar veya Zararda Yeniden Sınıflandırılacak Birikmiş Diğer Kapsamlı Gelirler (Giderler)</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="str">
+        <v xml:space="preserve">    Kardan Ayrılan Kısıtlanmış Yedekler</v>
+      </c>
+      <c r="B99">
+        <v>27637</v>
+      </c>
+      <c r="C99">
+        <v>27637.281063635004</v>
+      </c>
+      <c r="D99">
+        <v>27637</v>
+      </c>
+      <c r="E99">
+        <v>27637.64936653976</v>
+      </c>
+      <c r="F99">
+        <v>27637.07227928182</v>
+      </c>
+      <c r="G99">
+        <v>7434478.524153457</v>
+      </c>
+      <c r="H99">
+        <v>7434478.524153457</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="str">
+        <v xml:space="preserve">    Diğer Özkaynak Payları</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="str">
+        <v xml:space="preserve">    Diğer Yedekler</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="str">
+        <v xml:space="preserve">    Ödenen Kar Payı Avansları (Net) (-)</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="str">
+        <v xml:space="preserve">    Geçmiş Yıllar Kar/Zararları</v>
+      </c>
+      <c r="B103">
+        <v>1986587516</v>
+      </c>
+      <c r="C103">
+        <v>2573454935.451228</v>
+      </c>
+      <c r="D103">
+        <v>2407965396</v>
+      </c>
+      <c r="E103">
+        <v>2407994729.87117</v>
+      </c>
+      <c r="F103">
+        <v>1275756774.109623</v>
+      </c>
+      <c r="G103">
+        <v>-393966.15096132713</v>
+      </c>
+      <c r="H103">
+        <v>-194262.3215590309</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="str">
+        <v xml:space="preserve">    Dönem Net Kar/Zararı</v>
+      </c>
+      <c r="B104">
+        <v>1246532034</v>
+      </c>
+      <c r="C104">
+        <v>-30946121.52534435</v>
+      </c>
+      <c r="D104">
+        <v>-421377880</v>
+      </c>
+      <c r="E104">
+        <v>191474491.34502944</v>
+      </c>
+      <c r="F104">
+        <v>1132237955.8877137</v>
+      </c>
+      <c r="G104">
+        <v>1276150740.1906705</v>
+      </c>
+      <c r="H104">
+        <v>-199703.82940229628</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="str">
+        <v xml:space="preserve">    Azınlık Payları</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="str">
+        <v xml:space="preserve">    Toplam Özkaynaklar</v>
+      </c>
+      <c r="B106">
+        <v>4069164476</v>
+      </c>
+      <c r="C106">
+        <v>3378592563.00343</v>
+      </c>
+      <c r="D106">
+        <v>2373284953</v>
+      </c>
+      <c r="E106">
+        <v>2986177563.2409024</v>
+      </c>
+      <c r="F106">
+        <v>2794725821.8272934</v>
+      </c>
+      <c r="G106">
+        <v>1669891118.9608345</v>
+      </c>
+      <c r="H106">
+        <v>7725213.323519105</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="str">
+        <v xml:space="preserve">    Toplam Kaynaklar</v>
+      </c>
+      <c r="B107">
+        <v>5812931140</v>
+      </c>
+      <c r="C107">
+        <v>3920274173.571283</v>
+      </c>
+      <c r="D107">
+        <v>3533273303</v>
+      </c>
+      <c r="E107">
+        <v>3568057982.296619</v>
+      </c>
+      <c r="F107">
+        <v>4186617018.1317015</v>
+      </c>
+      <c r="G107">
+        <v>2157004685.359439</v>
+      </c>
+      <c r="H107">
+        <v>35170170.884991184</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="str">
+        <v xml:space="preserve">    Hedge Dahil Net Yabancı Para Pozisyonu</v>
+      </c>
+      <c r="D108">
+        <v>19</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G50"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H108"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G50"/>
+  <dimension ref="A1:K50"/>
   <cols>
     <col min="1" max="1" customWidth="1" width="40" level="2" outlineLevel="2"/>
     <col min="2" max="2" customWidth="1" width="20"/>
@@ -2132,6 +1723,10 @@
     <col min="5" max="5" customWidth="1" width="20"/>
     <col min="6" max="6" customWidth="1" width="20"/>
     <col min="7" max="7" customWidth="1" width="20"/>
+    <col min="8" max="8" customWidth="1" width="20"/>
+    <col min="9" max="9" customWidth="1" width="20"/>
+    <col min="10" max="10" customWidth="1" width="20"/>
+    <col min="11" max="11" customWidth="1" width="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2139,21 +1734,33 @@
         <v>Kalem</v>
       </c>
       <c r="B1" t="str">
+        <v>2026/6</v>
+      </c>
+      <c r="C1" t="str">
+        <v>2026/3</v>
+      </c>
+      <c r="D1" t="str">
         <v>2025/12</v>
       </c>
-      <c r="C1" t="str">
+      <c r="E1" t="str">
         <v>2025/9</v>
       </c>
-      <c r="D1" t="str">
+      <c r="F1" t="str">
+        <v>2025/6</v>
+      </c>
+      <c r="G1" t="str">
+        <v>2025/3</v>
+      </c>
+      <c r="H1" t="str">
         <v>2024/12</v>
       </c>
-      <c r="E1" t="str">
+      <c r="I1" t="str">
         <v>2024/9</v>
       </c>
-      <c r="F1" t="str">
+      <c r="J1" t="str">
         <v>2023/12</v>
       </c>
-      <c r="G1" t="str">
+      <c r="K1" t="str">
         <v>2022/12</v>
       </c>
     </row>
@@ -2167,10 +1774,34 @@
         <v xml:space="preserve">    Satış Gelirleri</v>
       </c>
       <c r="B3">
-        <v>3087005.938070575</v>
+        <v>6827976</v>
+      </c>
+      <c r="C3">
+        <v>3349930</v>
       </c>
       <c r="D3">
-        <v>2945078.8001942257</v>
+        <v>13718967.784135442</v>
+      </c>
+      <c r="E3">
+        <v>10083712.50112259</v>
+      </c>
+      <c r="F3">
+        <v>6242159</v>
+      </c>
+      <c r="G3">
+        <v>3227141</v>
+      </c>
+      <c r="H3">
+        <v>7153692.8853827845</v>
+      </c>
+      <c r="I3">
+        <v>3685570.8661596216</v>
+      </c>
+      <c r="J3">
+        <v>4692748.744937961</v>
+      </c>
+      <c r="K3">
+        <v>1488683.7341694338</v>
       </c>
     </row>
     <row r="4">
@@ -2182,6 +1813,12 @@
       <c r="A5" t="str">
         <v xml:space="preserve">    Yurt İçi Satışlar</v>
       </c>
+      <c r="D5">
+        <v>13718967.784135442</v>
+      </c>
+      <c r="H5">
+        <v>7153692.8853827845</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
@@ -2192,16 +1829,52 @@
       <c r="A7" t="str">
         <v xml:space="preserve">    Satışların Maliyeti (-)</v>
       </c>
+      <c r="B7">
+        <v>-201737</v>
+      </c>
+      <c r="C7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>-2199505.8883619127</v>
+      </c>
+      <c r="K7">
+        <v>-1212083.5832259252</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
         <v xml:space="preserve">    Ticari Faaliyetlerden Brüt Kar (Zarar)</v>
       </c>
       <c r="B8">
-        <v>3087005.938070575</v>
+        <v>6626239</v>
+      </c>
+      <c r="C8">
+        <v>3349930</v>
       </c>
       <c r="D8">
-        <v>2945078.8001942257</v>
+        <v>13718967.784135442</v>
+      </c>
+      <c r="E8">
+        <v>10083712.50112259</v>
+      </c>
+      <c r="F8">
+        <v>6242159</v>
+      </c>
+      <c r="G8">
+        <v>3227141</v>
+      </c>
+      <c r="H8">
+        <v>7153692.8853827845</v>
+      </c>
+      <c r="I8">
+        <v>3685570.8661596216</v>
+      </c>
+      <c r="J8">
+        <v>2493242.8565760483</v>
+      </c>
+      <c r="K8">
+        <v>276600.1509435083</v>
       </c>
     </row>
     <row r="9">
@@ -2229,10 +1902,34 @@
         <v xml:space="preserve">    Brüt Kar (Zarar)</v>
       </c>
       <c r="B13">
-        <v>3087005.938070575</v>
+        <v>6626239</v>
+      </c>
+      <c r="C13">
+        <v>3349930</v>
       </c>
       <c r="D13">
-        <v>2945078.8001942257</v>
+        <v>13718967.784135442</v>
+      </c>
+      <c r="E13">
+        <v>10083712.50112259</v>
+      </c>
+      <c r="F13">
+        <v>6242159</v>
+      </c>
+      <c r="G13">
+        <v>3227141</v>
+      </c>
+      <c r="H13">
+        <v>7153692.8853827845</v>
+      </c>
+      <c r="I13">
+        <v>3685570.8661596216</v>
+      </c>
+      <c r="J13">
+        <v>2493242.8565760483</v>
+      </c>
+      <c r="K13">
+        <v>276600.1509435083</v>
       </c>
     </row>
     <row r="14"/>
@@ -2241,10 +1938,28 @@
         <v xml:space="preserve">    Genel Yönetim Giderleri (-)</v>
       </c>
       <c r="B15">
-        <v>-7486609.2602087185</v>
+        <v>-12367520</v>
       </c>
       <c r="D15">
-        <v>-3318474.1507475013</v>
+        <v>-20625583.900878523</v>
+      </c>
+      <c r="E15">
+        <v>-11809359.892564194</v>
+      </c>
+      <c r="F15">
+        <v>-6075536</v>
+      </c>
+      <c r="H15">
+        <v>-13554720.977998618</v>
+      </c>
+      <c r="I15">
+        <v>-9646888.9459079</v>
+      </c>
+      <c r="J15">
+        <v>-6924569.423328443</v>
+      </c>
+      <c r="K15">
+        <v>-6272462.220184604</v>
       </c>
     </row>
     <row r="16">
@@ -2262,10 +1977,34 @@
         <v xml:space="preserve">    Diğer Faaliyet Gelirleri</v>
       </c>
       <c r="B18">
-        <v>-3708414.3275194466</v>
+        <v>1830171762</v>
+      </c>
+      <c r="C18">
+        <v>759079</v>
       </c>
       <c r="D18">
-        <v>-260051377.57869387</v>
+        <v>212756251.75145355</v>
+      </c>
+      <c r="E18">
+        <v>217123276.9681726</v>
+      </c>
+      <c r="F18">
+        <v>2196985646</v>
+      </c>
+      <c r="G18">
+        <v>1433701</v>
+      </c>
+      <c r="H18">
+        <v>2018709404.6149888</v>
+      </c>
+      <c r="I18">
+        <v>2324945661.7400975</v>
+      </c>
+      <c r="J18">
+        <v>1728681079.990785</v>
+      </c>
+      <c r="K18">
+        <v>96714.56837688063</v>
       </c>
     </row>
     <row r="19">
@@ -2273,10 +2012,34 @@
         <v xml:space="preserve">    Diğer Faaliyet Giderleri (-)</v>
       </c>
       <c r="B19">
-        <v>-17341515.953314662</v>
+        <v>-15734250</v>
+      </c>
+      <c r="C19">
+        <v>-345315</v>
       </c>
       <c r="D19">
-        <v>-40523587.04411651</v>
+        <v>-911844905.9479549</v>
+      </c>
+      <c r="E19">
+        <v>-891423553.1065866</v>
+      </c>
+      <c r="F19">
+        <v>-386913932</v>
+      </c>
+      <c r="G19">
+        <v>-218289</v>
+      </c>
+      <c r="H19">
+        <v>-106029232.71498093</v>
+      </c>
+      <c r="I19">
+        <v>-58308694.80735741</v>
+      </c>
+      <c r="J19">
+        <v>-94907166.8769727</v>
+      </c>
+      <c r="K19">
+        <v>-1093763.9675607772</v>
       </c>
     </row>
     <row r="20">
@@ -2289,10 +2052,34 @@
         <v xml:space="preserve">    Faaliyet Karı (Zararı)</v>
       </c>
       <c r="B21">
-        <v>-25449533.60297215</v>
+        <v>1808696231</v>
+      </c>
+      <c r="C21">
+        <v>-2076061</v>
       </c>
       <c r="D21">
-        <v>-300948359.97336364</v>
+        <v>-705995270.3132445</v>
+      </c>
+      <c r="E21">
+        <v>-676025923.5298556</v>
+      </c>
+      <c r="F21">
+        <v>1810238337</v>
+      </c>
+      <c r="G21">
+        <v>1471697</v>
+      </c>
+      <c r="H21">
+        <v>1906279143.8073921</v>
+      </c>
+      <c r="I21">
+        <v>2260675648.8529916</v>
+      </c>
+      <c r="J21">
+        <v>1629342586.5470598</v>
+      </c>
+      <c r="K21">
+        <v>-6992911.468424992</v>
       </c>
     </row>
     <row r="22"/>
@@ -2311,16 +2098,43 @@
         <v xml:space="preserve">    Yatırım Faaliyetlerinden Gelirler</v>
       </c>
       <c r="B25">
-        <v>-3283074.2867291113</v>
+        <v>28432783</v>
+      </c>
+      <c r="C25">
+        <v>11806199</v>
       </c>
       <c r="D25">
-        <v>130432.99850618612</v>
+        <v>4642677.218400226</v>
+      </c>
+      <c r="E25">
+        <v>8508822.403989047</v>
+      </c>
+      <c r="F25">
+        <v>3911470</v>
+      </c>
+      <c r="G25">
+        <v>997196</v>
+      </c>
+      <c r="H25">
+        <v>336327.001203801</v>
+      </c>
+      <c r="I25">
+        <v>182729.22510260693</v>
+      </c>
+      <c r="J25">
+        <v>103423.05783405897</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
         <v xml:space="preserve">    Yatırım Faaliyetlerinden Giderler (-)</v>
       </c>
+      <c r="B26">
+        <v>-508564</v>
+      </c>
+      <c r="C26">
+        <v>-497886</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
@@ -2357,10 +2171,34 @@
         <v xml:space="preserve">    Finansman Geliri (Gideri) Öncesi Faaliyet Karı (Zararı)</v>
       </c>
       <c r="B33">
-        <v>-28732607.889701366</v>
+        <v>1836620450</v>
+      </c>
+      <c r="C33">
+        <v>9232252</v>
       </c>
       <c r="D33">
-        <v>-300817926.97485757</v>
+        <v>-701352593.0948442</v>
+      </c>
+      <c r="E33">
+        <v>-667517101.1258665</v>
+      </c>
+      <c r="F33">
+        <v>1814149807</v>
+      </c>
+      <c r="G33">
+        <v>2468893</v>
+      </c>
+      <c r="H33">
+        <v>1906615470.808596</v>
+      </c>
+      <c r="I33">
+        <v>2260858378.0780945</v>
+      </c>
+      <c r="J33">
+        <v>1629446009.604894</v>
+      </c>
+      <c r="K33">
+        <v>-6992911.468424992</v>
       </c>
     </row>
     <row r="34"/>
@@ -2369,10 +2207,34 @@
         <v xml:space="preserve">    (Esas Faaliyet Dışı) Finansal Gelirler</v>
       </c>
       <c r="B35">
-        <v>-768088.30945706</v>
+        <v>17080601</v>
+      </c>
+      <c r="C35">
+        <v>12668775</v>
       </c>
       <c r="D35">
-        <v>2888363.376031266</v>
+        <v>11411162.143303538</v>
+      </c>
+      <c r="E35">
+        <v>12315662.212558135</v>
+      </c>
+      <c r="F35">
+        <v>7940053</v>
+      </c>
+      <c r="G35">
+        <v>0</v>
+      </c>
+      <c r="H35">
+        <v>8232783.426478499</v>
+      </c>
+      <c r="I35">
+        <v>4831449.4372924855</v>
+      </c>
+      <c r="J35">
+        <v>138066.5871044957</v>
+      </c>
+      <c r="K35">
+        <v>73070.79897660385</v>
       </c>
     </row>
     <row r="36">
@@ -2380,10 +2242,34 @@
         <v xml:space="preserve">    (Esas Faaliyet Dışı) Finansal Giderler (-)</v>
       </c>
       <c r="B36">
-        <v>-20046552.852272794</v>
+        <v>-40103378</v>
+      </c>
+      <c r="C36">
+        <v>-21798133</v>
       </c>
       <c r="D36">
-        <v>-1045639.680074364</v>
+        <v>-74267484.31309071</v>
+      </c>
+      <c r="E36">
+        <v>-50660682.5691431</v>
+      </c>
+      <c r="F36">
+        <v>-25809130</v>
+      </c>
+      <c r="G36">
+        <v>-2335660</v>
+      </c>
+      <c r="H36">
+        <v>-7095475.920779654</v>
+      </c>
+      <c r="I36">
+        <v>-5864131.619092308</v>
+      </c>
+      <c r="J36">
+        <v>-2358928.058867553</v>
+      </c>
+      <c r="K36">
+        <v>-257435.6715361634</v>
       </c>
     </row>
     <row r="37">
@@ -2391,10 +2277,34 @@
         <v xml:space="preserve">    Net Parasal Pozisyon Kazançları (Kayıpları)</v>
       </c>
       <c r="B37">
-        <v>24142576.6861892</v>
+        <v>124328870</v>
+      </c>
+      <c r="C37">
+        <v>-52641369</v>
       </c>
       <c r="D37">
-        <v>2854740.326747287</v>
+        <v>53329505.75665293</v>
+      </c>
+      <c r="E37">
+        <v>24899230.20659476</v>
+      </c>
+      <c r="F37">
+        <v>21126907</v>
+      </c>
+      <c r="G37">
+        <v>8649311</v>
+      </c>
+      <c r="H37">
+        <v>27333197.552903216</v>
+      </c>
+      <c r="I37">
+        <v>23971458.03486259</v>
+      </c>
+      <c r="J37">
+        <v>16058626.977162171</v>
+      </c>
+      <c r="K37">
+        <v>8297844.773106599</v>
       </c>
     </row>
     <row r="38">
@@ -2402,10 +2312,34 @@
         <v xml:space="preserve">    Sürdürülen Faaliyetler Vergi Öncesi Karı (Zararı)</v>
       </c>
       <c r="B38">
-        <v>-25404672.365242004</v>
+        <v>1937926543</v>
+      </c>
+      <c r="C38">
+        <v>-52538475</v>
       </c>
       <c r="D38">
-        <v>-296120462.95215344</v>
+        <v>-710879409.5079784</v>
+      </c>
+      <c r="E38">
+        <v>-680962891.2758567</v>
+      </c>
+      <c r="F38">
+        <v>1817407637</v>
+      </c>
+      <c r="G38">
+        <v>8782544</v>
+      </c>
+      <c r="H38">
+        <v>1935085975.867198</v>
+      </c>
+      <c r="I38">
+        <v>2283797153.931157</v>
+      </c>
+      <c r="J38">
+        <v>1643283775.1102931</v>
+      </c>
+      <c r="K38">
+        <v>1120568.4321220473</v>
       </c>
     </row>
     <row r="39"/>
@@ -2414,10 +2348,34 @@
         <v xml:space="preserve">    Sürdürülen Faaliyetler Vergi Geliri (Gideri)</v>
       </c>
       <c r="B40">
-        <v>3354147.9144517183</v>
+        <v>-691394509</v>
+      </c>
+      <c r="C40">
+        <v>-91373945</v>
       </c>
       <c r="D40">
-        <v>38714782.89230287</v>
+        <v>876387224.0434905</v>
+      </c>
+      <c r="E40">
+        <v>872437382.6208861</v>
+      </c>
+      <c r="F40">
+        <v>-689326888</v>
+      </c>
+      <c r="G40">
+        <v>-111146562</v>
+      </c>
+      <c r="H40">
+        <v>-802848019.9794843</v>
+      </c>
+      <c r="I40">
+        <v>-848438511.8228214</v>
+      </c>
+      <c r="J40">
+        <v>-367133034.9196221</v>
+      </c>
+      <c r="K40">
+        <v>-1320272.2615243436</v>
       </c>
     </row>
     <row r="41">
@@ -2425,10 +2383,28 @@
         <v xml:space="preserve">    Dönem Vergi Geliri (Gideri)</v>
       </c>
       <c r="B41">
-        <v>67373.89019725472</v>
+        <v>-111750</v>
+      </c>
+      <c r="C41">
+        <v>-2245389</v>
       </c>
       <c r="D41">
-        <v>17785.110343250504</v>
+        <v>-1821706.8811054481</v>
+      </c>
+      <c r="E41">
+        <v>-1901046.31069844</v>
+      </c>
+      <c r="H41">
+        <v>-334021.2622493149</v>
+      </c>
+      <c r="I41">
+        <v>-354964.99142616167</v>
+      </c>
+      <c r="J41">
+        <v>-367133034.9196221</v>
+      </c>
+      <c r="K41">
+        <v>-1320272.2615243436</v>
       </c>
     </row>
     <row r="42">
@@ -2436,10 +2412,34 @@
         <v xml:space="preserve">    Ertelenmiş Vergi Geliri (Gideri)</v>
       </c>
       <c r="B42">
-        <v>3286774.0242544413</v>
+        <v>-691282759</v>
+      </c>
+      <c r="C42">
+        <v>-89128556</v>
       </c>
       <c r="D42">
-        <v>38696997.78195953</v>
+        <v>878208930.9245961</v>
+      </c>
+      <c r="E42">
+        <v>874338428.9315847</v>
+      </c>
+      <c r="F42">
+        <v>-689326888</v>
+      </c>
+      <c r="G42">
+        <v>-110891471</v>
+      </c>
+      <c r="H42">
+        <v>-802513998.717235</v>
+      </c>
+      <c r="I42">
+        <v>-848083546.8313951</v>
+      </c>
+      <c r="J42">
+        <v>-367133034.9196221</v>
+      </c>
+      <c r="K42">
+        <v>-1320272.2615243436</v>
       </c>
     </row>
     <row r="43">
@@ -2447,10 +2447,34 @@
         <v xml:space="preserve">    Sürdürülen Faaliyetler Dönem Karı/Zararı</v>
       </c>
       <c r="B43">
-        <v>-22050524.450790256</v>
+        <v>1246532034</v>
+      </c>
+      <c r="C43">
+        <v>-143912420</v>
       </c>
       <c r="D43">
-        <v>-257405680.05985045</v>
+        <v>165507814.53551215</v>
+      </c>
+      <c r="E43">
+        <v>191474491.34502944</v>
+      </c>
+      <c r="F43">
+        <v>1128080749</v>
+      </c>
+      <c r="G43">
+        <v>-102364018</v>
+      </c>
+      <c r="H43">
+        <v>1132237955.8877137</v>
+      </c>
+      <c r="I43">
+        <v>1435358642.108336</v>
+      </c>
+      <c r="J43">
+        <v>1276150740.1906705</v>
+      </c>
+      <c r="K43">
+        <v>-199703.82940229628</v>
       </c>
     </row>
     <row r="44">
@@ -2464,26 +2488,80 @@
         <v xml:space="preserve">    Dönem Karı (Zararı)</v>
       </c>
       <c r="B46">
-        <v>-22050524.450790256</v>
+        <v>1246532034</v>
+      </c>
+      <c r="C46">
+        <v>-143912420</v>
       </c>
       <c r="D46">
-        <v>-257405680.05985045</v>
+        <v>165507814.53551215</v>
+      </c>
+      <c r="E46">
+        <v>191474491.34502944</v>
+      </c>
+      <c r="F46">
+        <v>1128080749</v>
+      </c>
+      <c r="G46">
+        <v>-102364018</v>
+      </c>
+      <c r="H46">
+        <v>1132237955.8877137</v>
+      </c>
+      <c r="I46">
+        <v>1435358642.108336</v>
+      </c>
+      <c r="J46">
+        <v>1276150740.1906705</v>
+      </c>
+      <c r="K46">
+        <v>-199703.82940229628</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
         <v xml:space="preserve">    Azınlık Payları</v>
       </c>
+      <c r="B47">
+        <v>0</v>
+      </c>
+      <c r="D47">
+        <v>0</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
         <v xml:space="preserve">    Ana Ortaklık Payları</v>
       </c>
       <c r="B48">
-        <v>-22050524.450790256</v>
+        <v>1246532034</v>
+      </c>
+      <c r="C48">
+        <v>-143912420</v>
       </c>
       <c r="D48">
-        <v>-257405680.05985045</v>
+        <v>165507814.53551215</v>
+      </c>
+      <c r="E48">
+        <v>191474491.34502944</v>
+      </c>
+      <c r="F48">
+        <v>1128080749</v>
+      </c>
+      <c r="G48">
+        <v>-102364018</v>
+      </c>
+      <c r="H48">
+        <v>1132237955.8877137</v>
+      </c>
+      <c r="I48">
+        <v>1435358642.108336</v>
+      </c>
+      <c r="J48">
+        <v>1276150740.1906705</v>
+      </c>
+      <c r="K48">
+        <v>-199703.82940229628</v>
       </c>
     </row>
     <row r="49"/>
@@ -2492,22 +2570,46 @@
         <v xml:space="preserve">    Amortisman</v>
       </c>
       <c r="B50">
-        <v>132495147.79908055</v>
+        <v>908431</v>
+      </c>
+      <c r="C50">
+        <v>448966.1647951505</v>
       </c>
       <c r="D50">
-        <v>1239437873.1461413</v>
+        <v>2171439.6699792542</v>
+      </c>
+      <c r="E50">
+        <v>-153854721.4948474</v>
+      </c>
+      <c r="F50">
+        <v>1049250</v>
+      </c>
+      <c r="G50">
+        <v>524770.17786042</v>
+      </c>
+      <c r="H50">
+        <v>2584625.02886561</v>
+      </c>
+      <c r="I50">
+        <v>-1456976246.1552172</v>
+      </c>
+      <c r="J50">
+        <v>-1278875795.2138054</v>
+      </c>
+      <c r="K50">
+        <v>4413158.714007401</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G50"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K50"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G50"/>
+  <dimension ref="A1:K50"/>
   <cols>
     <col min="1" max="1" customWidth="1" width="40" level="2" outlineLevel="2"/>
     <col min="2" max="2" customWidth="1" width="20"/>
@@ -2516,6 +2618,10 @@
     <col min="5" max="5" customWidth="1" width="20"/>
     <col min="6" max="6" customWidth="1" width="20"/>
     <col min="7" max="7" customWidth="1" width="20"/>
+    <col min="8" max="8" customWidth="1" width="20"/>
+    <col min="9" max="9" customWidth="1" width="20"/>
+    <col min="10" max="10" customWidth="1" width="20"/>
+    <col min="11" max="11" customWidth="1" width="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2523,21 +2629,33 @@
         <v>Kalem</v>
       </c>
       <c r="B1" t="str">
+        <v>2026/6</v>
+      </c>
+      <c r="C1" t="str">
+        <v>2026/3</v>
+      </c>
+      <c r="D1" t="str">
         <v>2025/12</v>
       </c>
-      <c r="C1" t="str">
+      <c r="E1" t="str">
         <v>2025/9</v>
       </c>
-      <c r="D1" t="str">
+      <c r="F1" t="str">
+        <v>2025/6</v>
+      </c>
+      <c r="G1" t="str">
+        <v>2025/3</v>
+      </c>
+      <c r="H1" t="str">
         <v>2024/12</v>
       </c>
-      <c r="E1" t="str">
+      <c r="I1" t="str">
         <v>2024/9</v>
       </c>
-      <c r="F1" t="str">
+      <c r="J1" t="str">
         <v>2023/12</v>
       </c>
-      <c r="G1" t="str">
+      <c r="K1" t="str">
         <v>2022/12</v>
       </c>
     </row>
@@ -2551,19 +2669,25 @@
         <v xml:space="preserve">    Satış Gelirleri</v>
       </c>
       <c r="B3">
-        <v>11649948</v>
+        <v>3478046</v>
       </c>
       <c r="C3">
-        <v>11508020.862123651</v>
+        <v>3349930</v>
       </c>
       <c r="D3">
-        <v>6074812</v>
+        <v>3635255.283012852</v>
+      </c>
+      <c r="E3">
+        <v>3841553.50112259</v>
       </c>
       <c r="F3">
-        <v>3985014.0124108316</v>
+        <v>3015018</v>
       </c>
       <c r="G3">
-        <v>1264168.5850137502</v>
+        <v>3227141</v>
+      </c>
+      <c r="H3">
+        <v>3468122.019223163</v>
       </c>
     </row>
     <row r="4">
@@ -2575,12 +2699,6 @@
       <c r="A5" t="str">
         <v xml:space="preserve">    Yurt İçi Satışlar</v>
       </c>
-      <c r="B5">
-        <v>11649948</v>
-      </c>
-      <c r="D5">
-        <v>6074812</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
@@ -2591,11 +2709,11 @@
       <c r="A7" t="str">
         <v xml:space="preserve">    Satışların Maliyeti (-)</v>
       </c>
-      <c r="F7">
-        <v>-1867788.424632189</v>
-      </c>
-      <c r="G7">
-        <v>-1029283.7579635426</v>
+      <c r="B7">
+        <v>-201737</v>
+      </c>
+      <c r="C7">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -2603,19 +2721,25 @@
         <v xml:space="preserve">    Ticari Faaliyetlerden Brüt Kar (Zarar)</v>
       </c>
       <c r="B8">
-        <v>11649948</v>
+        <v>3276309</v>
       </c>
       <c r="C8">
-        <v>11508020.862123651</v>
+        <v>3349930</v>
       </c>
       <c r="D8">
-        <v>6074812</v>
+        <v>3635255.283012852</v>
+      </c>
+      <c r="E8">
+        <v>3841553.50112259</v>
       </c>
       <c r="F8">
-        <v>2117225.5877786423</v>
+        <v>3015018</v>
       </c>
       <c r="G8">
-        <v>234884.8270502076</v>
+        <v>3227141</v>
+      </c>
+      <c r="H8">
+        <v>3468122.019223163</v>
       </c>
     </row>
     <row r="9">
@@ -2643,19 +2767,25 @@
         <v xml:space="preserve">    Brüt Kar (Zarar)</v>
       </c>
       <c r="B13">
-        <v>11649948</v>
+        <v>3276309</v>
       </c>
       <c r="C13">
-        <v>11508020.862123651</v>
+        <v>3349930</v>
       </c>
       <c r="D13">
-        <v>6074812</v>
+        <v>3635255.283012852</v>
+      </c>
+      <c r="E13">
+        <v>3841553.50112259</v>
       </c>
       <c r="F13">
-        <v>2117225.5877786423</v>
+        <v>3015018</v>
       </c>
       <c r="G13">
-        <v>234884.8270502076</v>
+        <v>3227141</v>
+      </c>
+      <c r="H13">
+        <v>3468122.019223163</v>
       </c>
     </row>
     <row r="14"/>
@@ -2663,20 +2793,14 @@
       <c r="A15" t="str">
         <v xml:space="preserve">    Genel Yönetim Giderleri (-)</v>
       </c>
-      <c r="B15">
-        <v>-17514946</v>
-      </c>
-      <c r="C15">
-        <v>-13346810.890538782</v>
-      </c>
       <c r="D15">
-        <v>-11510472</v>
-      </c>
-      <c r="F15">
-        <v>-5880243.686952441</v>
-      </c>
-      <c r="G15">
-        <v>-5326483.73018395</v>
+        <v>-8816224.008314328</v>
+      </c>
+      <c r="E15">
+        <v>-5733823.892564194</v>
+      </c>
+      <c r="H15">
+        <v>-3907832.032090718</v>
       </c>
     </row>
     <row r="16">
@@ -2694,19 +2818,25 @@
         <v xml:space="preserve">    Diğer Faaliyet Gelirleri</v>
       </c>
       <c r="B18">
-        <v>180669516</v>
+        <v>1829412683</v>
       </c>
       <c r="C18">
-        <v>-75673447.25117442</v>
+        <v>759079</v>
       </c>
       <c r="D18">
-        <v>1714258679</v>
+        <v>-4367025.216719061</v>
+      </c>
+      <c r="E18">
+        <v>-1979862369.0318274</v>
       </c>
       <c r="F18">
-        <v>1467970842.074955</v>
+        <v>2195551945</v>
       </c>
       <c r="G18">
-        <v>82128.60545791483</v>
+        <v>1433701</v>
+      </c>
+      <c r="H18">
+        <v>-306236257.1251087</v>
       </c>
     </row>
     <row r="19">
@@ -2714,19 +2844,25 @@
         <v xml:space="preserve">    Diğer Faaliyet Giderleri (-)</v>
       </c>
       <c r="B19">
-        <v>-774325438</v>
+        <v>-15388935</v>
       </c>
       <c r="C19">
-        <v>-797507509.0908018</v>
+        <v>-345315</v>
       </c>
       <c r="D19">
-        <v>-90038483</v>
+        <v>-20421352.841368318</v>
+      </c>
+      <c r="E19">
+        <v>-504509621.1065866</v>
       </c>
       <c r="F19">
-        <v>-80593786.37966037</v>
+        <v>-386695643</v>
       </c>
       <c r="G19">
-        <v>-928808.4604362055</v>
+        <v>-218289</v>
+      </c>
+      <c r="H19">
+        <v>-47720537.90762352</v>
       </c>
     </row>
     <row r="20">
@@ -2739,19 +2875,25 @@
         <v xml:space="preserve">    Faaliyet Karı (Zararı)</v>
       </c>
       <c r="B21">
-        <v>-599520920</v>
+        <v>1810772292</v>
       </c>
       <c r="C21">
-        <v>-875019746.3703915</v>
+        <v>-2076061</v>
       </c>
       <c r="D21">
-        <v>1618784536</v>
+        <v>-29969346.783388853</v>
+      </c>
+      <c r="E21">
+        <v>-2486264260.5298557</v>
       </c>
       <c r="F21">
-        <v>1383614037.5961208</v>
+        <v>1808766640</v>
       </c>
       <c r="G21">
-        <v>-5938278.758112033</v>
+        <v>1471697</v>
+      </c>
+      <c r="H21">
+        <v>-354396505.04559946</v>
       </c>
     </row>
     <row r="22"/>
@@ -2770,22 +2912,37 @@
         <v xml:space="preserve">    Yatırım Faaliyetlerinden Gelirler</v>
       </c>
       <c r="B25">
-        <v>3942494</v>
+        <v>16626584</v>
       </c>
       <c r="C25">
-        <v>7356001.285235298</v>
+        <v>11806199</v>
       </c>
       <c r="D25">
-        <v>285604</v>
+        <v>-3866145.185588821</v>
+      </c>
+      <c r="E25">
+        <v>4597352.403989047</v>
       </c>
       <c r="F25">
-        <v>87825.3571789191</v>
+        <v>2914274</v>
+      </c>
+      <c r="G25">
+        <v>997196</v>
+      </c>
+      <c r="H25">
+        <v>153597.7761011941</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
         <v xml:space="preserve">    Yatırım Faaliyetlerinden Giderler (-)</v>
       </c>
+      <c r="B26">
+        <v>-10678</v>
+      </c>
+      <c r="C26">
+        <v>-497886</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
@@ -2822,19 +2979,25 @@
         <v xml:space="preserve">    Finansman Geliri (Gideri) Öncesi Faaliyet Karı (Zararı)</v>
       </c>
       <c r="B33">
-        <v>-595578426</v>
+        <v>1827388198</v>
       </c>
       <c r="C33">
-        <v>-867663745.0851562</v>
+        <v>9232252</v>
       </c>
       <c r="D33">
-        <v>1619070140</v>
+        <v>-33835491.96897769</v>
+      </c>
+      <c r="E33">
+        <v>-2481666908.1258664</v>
       </c>
       <c r="F33">
-        <v>1383701862.9532998</v>
+        <v>1811680914</v>
       </c>
       <c r="G33">
-        <v>-5938278.758112033</v>
+        <v>2468893</v>
+      </c>
+      <c r="H33">
+        <v>-354242907.2694986</v>
       </c>
     </row>
     <row r="34"/>
@@ -2843,19 +3006,25 @@
         <v xml:space="preserve">    (Esas Faaliyet Dışı) Finansal Gelirler</v>
       </c>
       <c r="B35">
-        <v>9690193</v>
+        <v>4411826</v>
       </c>
       <c r="C35">
-        <v>13346644.685488326</v>
+        <v>12668775</v>
       </c>
       <c r="D35">
-        <v>6991160</v>
+        <v>-904500.0692545976</v>
+      </c>
+      <c r="E35">
+        <v>4375609.212558135</v>
       </c>
       <c r="F35">
-        <v>117244.1385980126</v>
+        <v>7940053</v>
       </c>
       <c r="G35">
-        <v>62050.66020931213</v>
+        <v>0</v>
+      </c>
+      <c r="H35">
+        <v>3401333.989186013</v>
       </c>
     </row>
     <row r="36">
@@ -2863,19 +3032,25 @@
         <v xml:space="preserve">    (Esas Faaliyet Dışı) Finansal Giderler (-)</v>
       </c>
       <c r="B36">
-        <v>-63066868</v>
+        <v>-18305245</v>
       </c>
       <c r="C36">
-        <v>-44065954.82780157</v>
+        <v>-21798133</v>
       </c>
       <c r="D36">
-        <v>-6025375</v>
+        <v>-23606801.74394761</v>
+      </c>
+      <c r="E36">
+        <v>-24851552.5691431</v>
       </c>
       <c r="F36">
-        <v>-2003167.4141933108</v>
+        <v>-23473470</v>
       </c>
       <c r="G36">
-        <v>-218610.6297450122</v>
+        <v>-2335660</v>
+      </c>
+      <c r="H36">
+        <v>-1231344.3016873458</v>
       </c>
     </row>
     <row r="37">
@@ -2883,19 +3058,25 @@
         <v xml:space="preserve">    Net Parasal Pozisyon Kazançları (Kayıpları)</v>
       </c>
       <c r="B37">
-        <v>45286641</v>
+        <v>176970239</v>
       </c>
       <c r="C37">
-        <v>23998804.640558086</v>
+        <v>-52641369</v>
       </c>
       <c r="D37">
-        <v>23210954</v>
+        <v>28430275.550058167</v>
+      </c>
+      <c r="E37">
+        <v>3772323.2065947615</v>
       </c>
       <c r="F37">
-        <v>13636752.573446345</v>
+        <v>12477596</v>
       </c>
       <c r="G37">
-        <v>7046409.149714007</v>
+        <v>8649311</v>
+      </c>
+      <c r="H37">
+        <v>3361739.5180406272</v>
       </c>
     </row>
     <row r="38">
@@ -2903,19 +3084,25 @@
         <v xml:space="preserve">    Sürdürülen Faaliyetler Vergi Öncesi Karı (Zararı)</v>
       </c>
       <c r="B38">
-        <v>-603668460</v>
+        <v>1990465018</v>
       </c>
       <c r="C38">
-        <v>-874384250.5869114</v>
+        <v>-52538475</v>
       </c>
       <c r="D38">
-        <v>1643246879</v>
+        <v>-29916518.232121706</v>
+      </c>
+      <c r="E38">
+        <v>-2498370528.275857</v>
       </c>
       <c r="F38">
-        <v>1395452692.2511508</v>
+        <v>1808625093</v>
       </c>
       <c r="G38">
-        <v>951570.4220662742</v>
+        <v>8782544</v>
+      </c>
+      <c r="H38">
+        <v>-348711178.0639591</v>
       </c>
     </row>
     <row r="39"/>
@@ -2924,19 +3111,25 @@
         <v xml:space="preserve">    Sürdürülen Faaliyetler Vergi Geliri (Gideri)</v>
       </c>
       <c r="B40">
-        <v>744215290</v>
+        <v>-600020564</v>
       </c>
       <c r="C40">
-        <v>779575924.9778512</v>
+        <v>-91373945</v>
       </c>
       <c r="D40">
-        <v>-681766867</v>
+        <v>3949841.4226044416</v>
+      </c>
+      <c r="E40">
+        <v>1561764270.620886</v>
       </c>
       <c r="F40">
-        <v>-311764035.982487</v>
+        <v>-578180326</v>
       </c>
       <c r="G40">
-        <v>-1121156.0107596177</v>
+        <v>-111146562</v>
+      </c>
+      <c r="H40">
+        <v>45590491.84333706</v>
       </c>
     </row>
     <row r="41">
@@ -2944,19 +3137,16 @@
         <v xml:space="preserve">    Dönem Vergi Geliri (Gideri)</v>
       </c>
       <c r="B41">
-        <v>-1546967</v>
+        <v>2133639</v>
       </c>
       <c r="C41">
-        <v>-1596555.7798540043</v>
+        <v>-2245389</v>
       </c>
       <c r="D41">
-        <v>-283646</v>
-      </c>
-      <c r="F41">
-        <v>-311764035.982487</v>
-      </c>
-      <c r="G41">
-        <v>-1121156.0107596177</v>
+        <v>79339.42959299195</v>
+      </c>
+      <c r="H41">
+        <v>20943.72917684674</v>
       </c>
     </row>
     <row r="42">
@@ -2964,19 +3154,25 @@
         <v xml:space="preserve">    Ertelenmiş Vergi Geliri (Gideri)</v>
       </c>
       <c r="B42">
-        <v>745762257</v>
+        <v>-602154203</v>
       </c>
       <c r="C42">
-        <v>781172480.7577051</v>
+        <v>-89128556</v>
       </c>
       <c r="D42">
-        <v>-681483221</v>
+        <v>3870501.9930113554</v>
+      </c>
+      <c r="E42">
+        <v>1563665316.9315848</v>
       </c>
       <c r="F42">
-        <v>-311764035.982487</v>
+        <v>-578435417</v>
       </c>
       <c r="G42">
-        <v>-1121156.0107596177</v>
+        <v>-110891471</v>
+      </c>
+      <c r="H42">
+        <v>45569548.11416018</v>
       </c>
     </row>
     <row r="43">
@@ -2984,19 +3180,25 @@
         <v xml:space="preserve">    Sürdürülen Faaliyetler Dönem Karı/Zararı</v>
       </c>
       <c r="B43">
-        <v>140546830</v>
+        <v>1390444454</v>
       </c>
       <c r="C43">
-        <v>-94808325.6090602</v>
+        <v>-143912420</v>
       </c>
       <c r="D43">
-        <v>961480012</v>
+        <v>-25966676.809517294</v>
+      </c>
+      <c r="E43">
+        <v>-936606257.6549705</v>
       </c>
       <c r="F43">
-        <v>1083688656.2686636</v>
+        <v>1230444767</v>
       </c>
       <c r="G43">
-        <v>-169585.58869334348</v>
+        <v>-102364018</v>
+      </c>
+      <c r="H43">
+        <v>-303120686.2206223</v>
       </c>
     </row>
     <row r="44">
@@ -3010,47 +3212,56 @@
         <v xml:space="preserve">    Dönem Karı (Zararı)</v>
       </c>
       <c r="B46">
-        <v>140546830</v>
+        <v>1390444454</v>
       </c>
       <c r="C46">
-        <v>-94808325.6090602</v>
+        <v>-143912420</v>
       </c>
       <c r="D46">
-        <v>961480012</v>
+        <v>-25966676.809517294</v>
+      </c>
+      <c r="E46">
+        <v>-936606257.6549705</v>
       </c>
       <c r="F46">
-        <v>1083688656.2686636</v>
+        <v>1230444767</v>
       </c>
       <c r="G46">
-        <v>-169585.58869334348</v>
+        <v>-102364018</v>
+      </c>
+      <c r="H46">
+        <v>-303120686.2206223</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
         <v xml:space="preserve">    Azınlık Payları</v>
       </c>
-      <c r="B47">
-        <v>0</v>
-      </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
         <v xml:space="preserve">    Ana Ortaklık Payları</v>
       </c>
       <c r="B48">
-        <v>140546830</v>
+        <v>1390444454</v>
       </c>
       <c r="C48">
-        <v>-94808325.6090602</v>
+        <v>-143912420</v>
       </c>
       <c r="D48">
-        <v>961480012</v>
+        <v>-25966676.809517294</v>
+      </c>
+      <c r="E48">
+        <v>-936606257.6549705</v>
       </c>
       <c r="F48">
-        <v>1083688656.2686636</v>
+        <v>1230444767</v>
       </c>
       <c r="G48">
-        <v>-169585.58869334348</v>
+        <v>-102364018</v>
+      </c>
+      <c r="H48">
+        <v>-303120686.2206223</v>
       </c>
     </row>
     <row r="49"/>
@@ -3059,31 +3270,37 @@
         <v xml:space="preserve">    Amortisman</v>
       </c>
       <c r="B50">
-        <v>1843955</v>
+        <v>459464.8352048495</v>
       </c>
       <c r="C50">
-        <v>1108786680.3470607</v>
+        <v>448966.1647951505</v>
       </c>
       <c r="D50">
-        <v>2194826</v>
+        <v>156026161.16482663</v>
+      </c>
+      <c r="E50">
+        <v>-154903971.4948474</v>
       </c>
       <c r="F50">
-        <v>-1086002733.3782675</v>
+        <v>524479.82213958</v>
       </c>
       <c r="G50">
-        <v>3747590.2227416085</v>
+        <v>524770.17786042</v>
+      </c>
+      <c r="H50">
+        <v>1459560871.1840827</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G50"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K50"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G129"/>
+  <dimension ref="A1:K50"/>
   <cols>
     <col min="1" max="1" customWidth="1" width="40" level="2" outlineLevel="2"/>
     <col min="2" max="2" customWidth="1" width="20"/>
@@ -3092,6 +3309,10 @@
     <col min="5" max="5" customWidth="1" width="20"/>
     <col min="6" max="6" customWidth="1" width="20"/>
     <col min="7" max="7" customWidth="1" width="20"/>
+    <col min="8" max="8" customWidth="1" width="20"/>
+    <col min="9" max="9" customWidth="1" width="20"/>
+    <col min="10" max="10" customWidth="1" width="20"/>
+    <col min="11" max="11" customWidth="1" width="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3099,21 +3320,33 @@
         <v>Kalem</v>
       </c>
       <c r="B1" t="str">
+        <v>2026/6</v>
+      </c>
+      <c r="C1" t="str">
+        <v>2026/3</v>
+      </c>
+      <c r="D1" t="str">
         <v>2025/12</v>
       </c>
-      <c r="C1" t="str">
+      <c r="E1" t="str">
         <v>2025/9</v>
       </c>
-      <c r="D1" t="str">
+      <c r="F1" t="str">
+        <v>2025/6</v>
+      </c>
+      <c r="G1" t="str">
+        <v>2025/3</v>
+      </c>
+      <c r="H1" t="str">
         <v>2024/12</v>
       </c>
-      <c r="E1" t="str">
+      <c r="I1" t="str">
         <v>2024/9</v>
       </c>
-      <c r="F1" t="str">
+      <c r="J1" t="str">
         <v>2023/12</v>
       </c>
-      <c r="G1" t="str">
+      <c r="K1" t="str">
         <v>2022/12</v>
       </c>
     </row>
@@ -3124,1181 +3357,653 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v xml:space="preserve">    İşletme Faaliyetlerinden Nakit Akışları</v>
+        <v xml:space="preserve">    Satış Gelirleri</v>
       </c>
       <c r="B3">
-        <v>114117683</v>
+        <v>14304784.784135442</v>
       </c>
       <c r="C3">
-        <v>-68558858.33075058</v>
+        <v>13841756.784135442</v>
       </c>
       <c r="D3">
-        <v>104396279</v>
+        <v>13718967.784135442</v>
       </c>
       <c r="E3">
-        <v>25911749.816973645</v>
-      </c>
-      <c r="F3">
-        <v>-26803458.951446593</v>
-      </c>
-      <c r="G3">
-        <v>-7214888.5730246315</v>
+        <v>13551834.520345753</v>
+      </c>
+      <c r="H3">
+        <v>7153692.8853827845</v>
+      </c>
+      <c r="J3">
+        <v>4692748.744937961</v>
+      </c>
+      <c r="K3">
+        <v>1488683.7341694338</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v xml:space="preserve">    Dönem Karı (Zararı)</v>
-      </c>
-      <c r="B4">
-        <v>140546830</v>
-      </c>
-      <c r="C4">
-        <v>162597354.45079026</v>
-      </c>
-      <c r="D4">
-        <v>961480012</v>
-      </c>
-      <c r="E4">
-        <v>1218885692.0598505</v>
-      </c>
-      <c r="F4">
-        <v>1083688656.2686636</v>
-      </c>
-      <c r="G4">
-        <v>-169585.58869334348</v>
+        <v xml:space="preserve">    Toplam Hasılat</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v xml:space="preserve">    Dönem Net Karı (Zararı) Mutabakatı İle İlgili Düzeltmeler</v>
-      </c>
-      <c r="B5">
-        <v>-558743191</v>
+        <v xml:space="preserve">    Yurt İçi Satışlar</v>
       </c>
       <c r="D5">
-        <v>-966022089</v>
+        <v>13718967.784135442</v>
+      </c>
+      <c r="H5">
+        <v>7153692.8853827845</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v xml:space="preserve">    Amortisman ve İtfa Gideri İle İlgili Düzeltmeler</v>
-      </c>
-      <c r="B6">
-        <v>1843955</v>
-      </c>
-      <c r="C6">
-        <v>-130651192.79908055</v>
-      </c>
-      <c r="D6">
-        <v>2194826</v>
-      </c>
-      <c r="E6">
-        <v>-1237243047.1461413</v>
-      </c>
-      <c r="F6">
-        <v>-1086002733.3782675</v>
-      </c>
-      <c r="G6">
-        <v>3747590.2227416085</v>
+        <v xml:space="preserve">    Yurt Dışı Satışlar</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v xml:space="preserve">    Değer Düşüklüğü (İptali) İle İlgili Düzeltmeler</v>
-      </c>
-      <c r="C7">
-        <v>1373370.0664375953</v>
-      </c>
-      <c r="E7">
-        <v>3188675.117868746</v>
-      </c>
-      <c r="F7">
-        <v>2352681.237908423</v>
-      </c>
-      <c r="G7">
-        <v>2199489.8550287774</v>
+        <v xml:space="preserve">    Satışların Maliyeti (-)</v>
+      </c>
+      <c r="J7">
+        <v>-2199505.8883619127</v>
+      </c>
+      <c r="K7">
+        <v>-1212083.5832259252</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v xml:space="preserve">    Karşılıklar İle İlgili Düzeltmeler</v>
+        <v xml:space="preserve">    Ticari Faaliyetlerden Brüt Kar (Zarar)</v>
       </c>
       <c r="B8">
-        <v>-176200</v>
+        <v>14103047.784135442</v>
       </c>
       <c r="C8">
-        <v>-353636.8986463611</v>
+        <v>13841756.784135442</v>
       </c>
       <c r="D8">
-        <v>-7353</v>
+        <v>13718967.784135442</v>
       </c>
       <c r="E8">
-        <v>-578661.2005066494</v>
-      </c>
-      <c r="F8">
-        <v>365133.7137609066</v>
-      </c>
-      <c r="G8">
-        <v>176353.02502064017</v>
+        <v>13551834.520345753</v>
+      </c>
+      <c r="H8">
+        <v>7153692.8853827845</v>
+      </c>
+      <c r="J8">
+        <v>2493242.8565760483</v>
+      </c>
+      <c r="K8">
+        <v>276600.1509435083</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v xml:space="preserve">    Kar Payı (Geliri) Gideri ile İlgili Düzeltmeler</v>
+        <v xml:space="preserve">    Faiz, Ücret, Prim, Komisyon ve Diğer Gelirler</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v xml:space="preserve">    Katılım (Kar) Payı ve Diğer Finansal Araçlardan (Gelirler) Giderler ile İlgili Düzeltmeler</v>
+        <v xml:space="preserve">    Faiz, Ücret, Prim, Komisyon ve Diğer Giderler (-)</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v xml:space="preserve">    Pazarlıklı Satın Alım Sonucu Oluşan Kazanç ile İlgili Düzeltmeler</v>
+        <v xml:space="preserve">    Finans Sektörü Faaliyetlerinden Brüt Kar (Zarar)</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v xml:space="preserve">    Faiz (Gelirleri) ve Giderleri İle İlgili Düzeltmeler</v>
-      </c>
-      <c r="B12">
-        <v>-2520607</v>
-      </c>
-      <c r="C12">
-        <v>30395206.125046775</v>
-      </c>
-      <c r="D12">
-        <v>2829808</v>
-      </c>
-      <c r="E12">
-        <v>247581.72724977875</v>
-      </c>
-      <c r="F12">
-        <v>3282402.8065614956</v>
-      </c>
-      <c r="G12">
-        <v>290657.4769364639</v>
+        <v xml:space="preserve">    Canlı Varlıklar Gerçeğe Uygun Değer Farkları</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v xml:space="preserve">    Devlet Teşviklerinden Elde Edilen Gelirler ile İlgili Düzeltmeler</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v xml:space="preserve">    Takas İşlemlerinden Kaynaklanan Kayıplar (Kazançlar) ile İlgili Düzeltmeler</v>
-      </c>
-    </row>
+        <v xml:space="preserve">    Brüt Kar (Zarar)</v>
+      </c>
+      <c r="B13">
+        <v>14103047.784135442</v>
+      </c>
+      <c r="C13">
+        <v>13841756.784135442</v>
+      </c>
+      <c r="D13">
+        <v>13718967.784135442</v>
+      </c>
+      <c r="E13">
+        <v>13551834.520345753</v>
+      </c>
+      <c r="H13">
+        <v>7153692.8853827845</v>
+      </c>
+      <c r="J13">
+        <v>2493242.8565760483</v>
+      </c>
+      <c r="K13">
+        <v>276600.1509435083</v>
+      </c>
+    </row>
+    <row r="14"/>
     <row r="15">
       <c r="A15" t="str">
-        <v xml:space="preserve">    Gerçekleşmemiş Yabancı Para Çevrim Farkları İle İlgili Düzeltmeler</v>
+        <v xml:space="preserve">    Genel Yönetim Giderleri (-)</v>
+      </c>
+      <c r="B15">
+        <v>-26917567.900878523</v>
+      </c>
+      <c r="D15">
+        <v>-20625583.900878523</v>
+      </c>
+      <c r="E15">
+        <v>-15717191.924654912</v>
+      </c>
+      <c r="H15">
+        <v>-13554720.977998618</v>
+      </c>
+      <c r="J15">
+        <v>-6924569.423328443</v>
+      </c>
+      <c r="K15">
+        <v>-6272462.220184604</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v xml:space="preserve">    Pay Bazlı Ödemeler İle İlgili Düzeltmeler</v>
+        <v xml:space="preserve">    Pazarlama, Satış ve Dağıtım Giderleri (-)</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v xml:space="preserve">    Hibe Krediler ile İlgili Düzeltmeler</v>
+        <v xml:space="preserve">    Araştırma ve Geliştirme Giderleri (-)</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v xml:space="preserve">    Gerçeğe Uygun Değer Kayıpları (Kazançları) İle İlgili Düzeltmeler</v>
+        <v xml:space="preserve">    Diğer Faaliyet Gelirleri</v>
       </c>
       <c r="B18">
-        <v>-592570032</v>
+        <v>-154057632.24854636</v>
       </c>
       <c r="C18">
-        <v>570453532.6768432</v>
+        <v>212081629.75145355</v>
       </c>
       <c r="D18">
-        <v>-1633280487</v>
+        <v>212756251.75145355</v>
       </c>
       <c r="E18">
-        <v>-1973989753.8695006</v>
-      </c>
-      <c r="F18">
-        <v>-1402663028.8492703</v>
+        <v>-89112980.15693611</v>
+      </c>
+      <c r="H18">
+        <v>2018709404.6149888</v>
+      </c>
+      <c r="J18">
+        <v>1728681079.990785</v>
+      </c>
+      <c r="K18">
+        <v>96714.56837688063</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v xml:space="preserve">    Özkaynak Yöntemiyle Değerlenen Yatırımların Dağıtılmamış Karları ile İlgili Düzeltmeler</v>
+        <v xml:space="preserve">    Diğer Faaliyet Giderleri (-)</v>
+      </c>
+      <c r="B19">
+        <v>-540665223.9479549</v>
+      </c>
+      <c r="C19">
+        <v>-911971931.9479549</v>
+      </c>
+      <c r="D19">
+        <v>-911844905.9479549</v>
+      </c>
+      <c r="E19">
+        <v>-939144091.0142101</v>
+      </c>
+      <c r="H19">
+        <v>-106029232.71498093</v>
+      </c>
+      <c r="J19">
+        <v>-94907166.8769727</v>
+      </c>
+      <c r="K19">
+        <v>-1093763.9675607772</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v xml:space="preserve">    Vergi (Geliri) Gideri İle İlgili Düzeltmeler</v>
-      </c>
-      <c r="B20">
-        <v>56755381</v>
-      </c>
-      <c r="C20">
-        <v>-805090764.4336218</v>
-      </c>
-      <c r="D20">
-        <v>681483221</v>
-      </c>
-      <c r="E20">
-        <v>720180220.8690641</v>
-      </c>
-      <c r="F20">
-        <v>311764035.982487</v>
-      </c>
-      <c r="G20">
-        <v>1121156.0107596177</v>
+        <v xml:space="preserve">    Diğer Kazançlar (Kayıplar)</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v xml:space="preserve">    Nakit Dışı Kalemlere İlişkin Diğer Düzeltmeler</v>
+        <v xml:space="preserve">    Faaliyet Karı (Zararı)</v>
+      </c>
+      <c r="B21">
+        <v>-707537376.3132443</v>
       </c>
       <c r="C21">
-        <v>9957964.793957626</v>
+        <v>-709543028.3132445</v>
+      </c>
+      <c r="D21">
+        <v>-705995270.3132445</v>
       </c>
       <c r="E21">
-        <v>13708890.209683359</v>
-      </c>
-      <c r="F21">
-        <v>-1103958.2697150765</v>
-      </c>
-      <c r="G21">
-        <v>-40066.14500389045</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="str">
-        <v xml:space="preserve">    Duran Varlıkların Elden Çıkarılmasından Kaynaklanan Kayıplar (Kazançlar) İle İlgili Düzeltmeler</v>
-      </c>
-    </row>
+        <v>-1030422428.5754551</v>
+      </c>
+      <c r="H21">
+        <v>1906279143.8073921</v>
+      </c>
+      <c r="J21">
+        <v>1629342586.5470598</v>
+      </c>
+      <c r="K21">
+        <v>-6992911.468424992</v>
+      </c>
+    </row>
+    <row r="22"/>
     <row r="23">
       <c r="A23" t="str">
-        <v xml:space="preserve">    Satış Amaçlı veya Ortaklara Dağıtılmak Üzere Elde Tutulan Duran Varlıkların Elden Çıkarılmasından Kaynaklanan Kayıplar (Kazançlar) ile İlgili Düzeltmeler</v>
+        <v xml:space="preserve">    Ödenecek Kar Paylarının Defter Değeri ile Dağıtılan Nakit Dışı Varlıkların Değeri Arasındaki Fark</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v xml:space="preserve">    İştirak, İş ortaklığı ve Finansal Yatırımların Elden Çıkarılmasından veya Paylarındaki Değişim Sebebi ile Oluşan Kayıplar (Kazançlar) ile İlgili Düzeltmeler</v>
+        <v xml:space="preserve">    İtfa Edilmiş Maliyetinden Ölçülen Finansal Varlıkların Finansal Tablo Dışı Bırakılmasından Kaynaklanan Kazançlar (Kayıplar)</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v xml:space="preserve">    Bağlı Ortaklıkların veya Müşterek Faaliyetlerin Elden Çıkarılmasından Kaynaklanan Kayıplar (Kazançlar) ile İlgili Düzeltmeler</v>
+        <v xml:space="preserve">    Yatırım Faaliyetlerinden Gelirler</v>
+      </c>
+      <c r="B25">
+        <v>29163990.218400225</v>
+      </c>
+      <c r="C25">
+        <v>15451680.218400225</v>
+      </c>
+      <c r="D25">
+        <v>4642677.218400226</v>
+      </c>
+      <c r="E25">
+        <v>8662420.180090241</v>
+      </c>
+      <c r="H25">
+        <v>336327.001203801</v>
+      </c>
+      <c r="J25">
+        <v>103423.05783405897</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v xml:space="preserve">    Yatırım ya da Finansman Faaliyetlerinden Kaynaklanan Nakit Akışlarına Neden Olan Diğer Kalemlere İlişkin Düzeltmeler</v>
+        <v xml:space="preserve">    Yatırım Faaliyetlerinden Giderler (-)</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v xml:space="preserve">    Kar (Zarar) Mutabakatı İle İlgili Diğer Düzeltmeler</v>
+        <v xml:space="preserve">    TFRS 9 Uyarınca Belirlenen Değer Düşüklüğü Kazançları (Zararları) ve Değer Düşüklüğü Zararlarının İptalleri</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v xml:space="preserve">    İşletme Sermayesinde Gerçekleşen Değişimler</v>
-      </c>
-      <c r="B28">
-        <v>532314044</v>
-      </c>
-      <c r="C28">
-        <v>-100505019.9824603</v>
-      </c>
-      <c r="D28">
-        <v>108938356</v>
-      </c>
-      <c r="E28">
-        <v>44269104.90326441</v>
-      </c>
-      <c r="F28">
-        <v>-24492001.157984924</v>
-      </c>
-      <c r="G28">
-        <v>-10801548.42941655</v>
+        <v xml:space="preserve">    Özkaynak Yöntemiyle Değerlenen Yatırımların Karlarından (Zararlarından) Paylar</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v xml:space="preserve">    Finansal Yatırımlardaki Azalış (Artış)</v>
-      </c>
-      <c r="B29">
-        <v>23234823</v>
-      </c>
-      <c r="D29">
-        <v>-23353528</v>
+        <v xml:space="preserve">    İştirakler, Müşterek Kontrol Edilen İşletmeler ve Bağlı Ortaklıklardan Diğer Gelirler (Giderler)</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v xml:space="preserve">    Türkiye Cumhuriyet Merkez Bankası Hesabındaki Azalış (Artış)</v>
+        <v xml:space="preserve">    İtfa Edilmiş Maliyetinden Ölçülen Finansal Varlıkların Gerçeğe Uygun Değer Farkı Kar veya Zarara Yansıtılan Olarak Sınıflandırılmasından Kazançlar (Kayıplar)</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v xml:space="preserve">    Ticari Alacaklardaki Azalış (Artış) ile İlgili Düzeltmeler</v>
-      </c>
-      <c r="B31">
-        <v>-430774</v>
-      </c>
-      <c r="C31">
-        <v>-21215026.910216738</v>
-      </c>
-      <c r="D31">
-        <v>-5664263</v>
-      </c>
-      <c r="E31">
-        <v>1449206.0518409845</v>
-      </c>
-      <c r="F31">
-        <v>-557092.0190958714</v>
-      </c>
-      <c r="G31">
-        <v>341795.7112900256</v>
+        <v xml:space="preserve">    Gerçeğe Uygun Değer Farkı Diğer Kapsamlı Gelire Yansıtılan Finansal Varlıkların Gerçeğe Uygun Değer Farkı Kar veya Zarara Yansıtılan Olarak Sınıflandırılmasından Kazançlar (Kayıplar)</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v xml:space="preserve">    Finans Sektörü Faaliyetlerinden Alacaklarda Azalış (Artış)</v>
-      </c>
-      <c r="C32">
-        <v>23266758.115368165</v>
-      </c>
-      <c r="E32">
-        <v>1144.7768158896656</v>
-      </c>
-      <c r="F32">
-        <v>-1145.820368137514</v>
+        <v xml:space="preserve">    Risk Pozisyonlarını Netleştiren Kalemler Grubuna Yönelik Finansal Riskten Korunma Kazançları (Kayıpları)</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v xml:space="preserve">    Faaliyetlerle İlgili Diğer Alacaklardaki Azalış (Artış) ile İlgili Düzeltmeler</v>
+        <v xml:space="preserve">    Finansman Geliri (Gideri) Öncesi Faaliyet Karı (Zararı)</v>
       </c>
       <c r="B33">
-        <v>-32788</v>
+        <v>-678881950.0948443</v>
       </c>
       <c r="C33">
-        <v>1105272.1019951175</v>
+        <v>-694589234.0948442</v>
       </c>
       <c r="D33">
-        <v>-7385494</v>
+        <v>-701352593.0948442</v>
       </c>
       <c r="E33">
-        <v>3401387.5903089195</v>
-      </c>
-      <c r="F33">
-        <v>-8734556.316192586</v>
-      </c>
-      <c r="G33">
-        <v>1129961.5046269624</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="str">
-        <v xml:space="preserve">    Müşteri Sözleşmelerinden Doğan Varlıklardaki Azalış (Artış) İle İlgili Düzeltmeler</v>
-      </c>
-    </row>
+        <v>-1021760008.3953651</v>
+      </c>
+      <c r="H33">
+        <v>1906615470.808596</v>
+      </c>
+      <c r="J33">
+        <v>1629446009.604894</v>
+      </c>
+      <c r="K33">
+        <v>-6992911.468424992</v>
+      </c>
+    </row>
+    <row r="34"/>
     <row r="35">
       <c r="A35" t="str">
-        <v xml:space="preserve">    İmtiyaz Sözleşmelerine İlişkin Finansal Varlıklardaki Azalış (Artış)</v>
+        <v xml:space="preserve">    (Esas Faaliyet Dışı) Finansal Gelirler</v>
+      </c>
+      <c r="B35">
+        <v>20551710.143303536</v>
+      </c>
+      <c r="C35">
+        <v>24079937.143303536</v>
+      </c>
+      <c r="D35">
+        <v>11411162.143303538</v>
+      </c>
+      <c r="E35">
+        <v>15716996.201744149</v>
+      </c>
+      <c r="H35">
+        <v>8232783.426478499</v>
+      </c>
+      <c r="J35">
+        <v>138066.5871044957</v>
+      </c>
+      <c r="K35">
+        <v>73070.79897660385</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v xml:space="preserve">    Türev Varlıklardaki Azalış (Artış)</v>
+        <v xml:space="preserve">    (Esas Faaliyet Dışı) Finansal Giderler (-)</v>
+      </c>
+      <c r="B36">
+        <v>-88561732.31309071</v>
+      </c>
+      <c r="C36">
+        <v>-93729957.31309071</v>
+      </c>
+      <c r="D36">
+        <v>-74267484.31309071</v>
+      </c>
+      <c r="E36">
+        <v>-51892026.87083045</v>
+      </c>
+      <c r="H36">
+        <v>-7095475.920779654</v>
+      </c>
+      <c r="J36">
+        <v>-2358928.058867553</v>
+      </c>
+      <c r="K36">
+        <v>-257435.6715361634</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v xml:space="preserve">    Stoklardaki Azalışlar (Artışlar) İle İlgili Düzeltmeler</v>
+        <v xml:space="preserve">    Net Parasal Pozisyon Kazançları (Kayıpları)</v>
       </c>
       <c r="B37">
-        <v>-54253036</v>
+        <v>156531468.75665292</v>
       </c>
       <c r="C37">
-        <v>3012682.118373614</v>
+        <v>-7961174.243347071</v>
       </c>
       <c r="D37">
-        <v>7280493</v>
+        <v>53329505.75665293</v>
       </c>
       <c r="E37">
-        <v>-9815480.257140905</v>
-      </c>
-      <c r="F37">
-        <v>-19024186.016218126</v>
-      </c>
-      <c r="G37">
-        <v>-221052.54200497738</v>
+        <v>28260969.72463539</v>
+      </c>
+      <c r="H37">
+        <v>27333197.552903216</v>
+      </c>
+      <c r="J37">
+        <v>16058626.977162171</v>
+      </c>
+      <c r="K37">
+        <v>8297844.773106599</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v xml:space="preserve">    Canlı Varlıklardaki Azalış (Artış)</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="str">
-        <v xml:space="preserve">    Peşin Ödenmiş Giderlerdeki Azalış (Artış)</v>
-      </c>
-      <c r="B39">
-        <v>-5535746</v>
-      </c>
-      <c r="C39">
-        <v>-860782.4200557136</v>
-      </c>
-      <c r="D39">
-        <v>34358390</v>
-      </c>
-      <c r="E39">
-        <v>-31496538.817306265</v>
-      </c>
-      <c r="F39">
-        <v>-27342827.279165007</v>
-      </c>
-      <c r="G39">
-        <v>-5155621.877091488</v>
-      </c>
-    </row>
+        <v xml:space="preserve">    Sürdürülen Faaliyetler Vergi Öncesi Karı (Zararı)</v>
+      </c>
+      <c r="B38">
+        <v>-590360503.5079784</v>
+      </c>
+      <c r="C38">
+        <v>-772200428.5079784</v>
+      </c>
+      <c r="D38">
+        <v>-710879409.5079784</v>
+      </c>
+      <c r="E38">
+        <v>-1029674069.3398159</v>
+      </c>
+      <c r="H38">
+        <v>1935085975.867198</v>
+      </c>
+      <c r="J38">
+        <v>1643283775.1102931</v>
+      </c>
+      <c r="K38">
+        <v>1120568.4321220473</v>
+      </c>
+    </row>
+    <row r="39"/>
     <row r="40">
       <c r="A40" t="str">
-        <v xml:space="preserve">    Ticari Borçlardaki Artış (Azalış) ile İlgili Düzeltmeler</v>
+        <v xml:space="preserve">    Sürdürülen Faaliyetler Vergi Geliri (Gideri)</v>
       </c>
       <c r="B40">
-        <v>16760080</v>
+        <v>874319603.0434904</v>
       </c>
       <c r="C40">
-        <v>14045891.84194677</v>
+        <v>896159841.0434905</v>
       </c>
       <c r="D40">
-        <v>-6568573</v>
+        <v>876387224.0434905</v>
       </c>
       <c r="E40">
-        <v>5767646.486514098</v>
-      </c>
-      <c r="F40">
-        <v>5871021.815738205</v>
-      </c>
-      <c r="G40">
-        <v>-6870624.860668444</v>
+        <v>918027874.4642231</v>
+      </c>
+      <c r="H40">
+        <v>-802848019.9794843</v>
+      </c>
+      <c r="J40">
+        <v>-367133034.9196221</v>
+      </c>
+      <c r="K40">
+        <v>-1320272.2615243436</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v xml:space="preserve">    Finans Sektörü Faaliyetlerinden Borçlardaki Artış (Azalış)</v>
+        <v xml:space="preserve">    Dönem Vergi Geliri (Gideri)</v>
+      </c>
+      <c r="D41">
+        <v>-1821706.8811054481</v>
+      </c>
+      <c r="E41">
+        <v>-1880102.5815215933</v>
+      </c>
+      <c r="H41">
+        <v>-334021.2622493149</v>
+      </c>
+      <c r="J41">
+        <v>-367133034.9196221</v>
+      </c>
+      <c r="K41">
+        <v>-1320272.2615243436</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v xml:space="preserve">    Çalışanlara Sağlanan Faydalar Kapsamında Borçlardaki Artış (Azalış)</v>
+        <v xml:space="preserve">    Ertelenmiş Vergi Geliri (Gideri)</v>
       </c>
       <c r="B42">
-        <v>174525</v>
+        <v>876253059.9245961</v>
       </c>
       <c r="C42">
-        <v>195179.75112407267</v>
+        <v>899971845.9245961</v>
       </c>
       <c r="D42">
-        <v>113064</v>
+        <v>878208930.9245961</v>
       </c>
       <c r="E42">
-        <v>145612.06290352278</v>
-      </c>
-      <c r="F42">
-        <v>-64482.13694679884</v>
-      </c>
-      <c r="G42">
-        <v>-16270.02309620399</v>
+        <v>919907977.0457449</v>
+      </c>
+      <c r="H42">
+        <v>-802513998.717235</v>
+      </c>
+      <c r="J42">
+        <v>-367133034.9196221</v>
+      </c>
+      <c r="K42">
+        <v>-1320272.2615243436</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v xml:space="preserve">    Müşteri Sözleşmelerinden Doğan Yükümlülüklerdeki Artış (Azalış) İle İlgili Düzeltmeler</v>
+        <v xml:space="preserve">    Sürdürülen Faaliyetler Dönem Karı/Zararı</v>
+      </c>
+      <c r="B43">
+        <v>283959099.5355122</v>
+      </c>
+      <c r="C43">
+        <v>123959412.53551215</v>
+      </c>
+      <c r="D43">
+        <v>165507814.53551215</v>
+      </c>
+      <c r="E43">
+        <v>-111646194.87559286</v>
+      </c>
+      <c r="H43">
+        <v>1132237955.8877137</v>
+      </c>
+      <c r="J43">
+        <v>1276150740.1906705</v>
+      </c>
+      <c r="K43">
+        <v>-199703.82940229628</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v xml:space="preserve">    Faaliyetler ile İlgili Diğer Borçlardaki Artış (Azalış) ile İlgili Düzeltmeler</v>
-      </c>
-      <c r="B44">
-        <v>550840052</v>
-      </c>
-      <c r="C44">
-        <v>-124482580.14527117</v>
-      </c>
-      <c r="D44">
-        <v>81744632</v>
-      </c>
-      <c r="E44">
-        <v>86351419.98235637</v>
-      </c>
-      <c r="F44">
-        <v>25361266.614263397</v>
-      </c>
-      <c r="G44">
-        <v>-9736.342472425324</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="str">
-        <v xml:space="preserve">    Türev Yükümlülüklerdeki Artış (Azalış)</v>
-      </c>
-    </row>
+        <v xml:space="preserve">    Durdurulan Faaliyetler Dönem Karı/Zararı</v>
+      </c>
+    </row>
+    <row r="45"/>
     <row r="46">
       <c r="A46" t="str">
-        <v xml:space="preserve">    Devlet Teşvik ve Yardımlarındaki Artış (Azalış)</v>
+        <v xml:space="preserve">    Dönem Karı (Zararı)</v>
+      </c>
+      <c r="B46">
+        <v>283959099.5355122</v>
+      </c>
+      <c r="C46">
+        <v>123959412.53551215</v>
+      </c>
+      <c r="D46">
+        <v>165507814.53551215</v>
+      </c>
+      <c r="E46">
+        <v>-111646194.87559286</v>
+      </c>
+      <c r="H46">
+        <v>1132237955.8877137</v>
+      </c>
+      <c r="J46">
+        <v>1276150740.1906705</v>
+      </c>
+      <c r="K46">
+        <v>-199703.82940229628</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v xml:space="preserve">    Ertelenmiş Gelirlerdeki Artış (Azalış)</v>
-      </c>
-      <c r="B47">
-        <v>1556908</v>
-      </c>
-      <c r="C47">
-        <v>4427585.564275575</v>
+        <v xml:space="preserve">    Azınlık Payları</v>
       </c>
       <c r="D47">
-        <v>28413635</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v xml:space="preserve">    İşletme Sermayesinde Gerçekleşen Diğer Artış (Azalış) ile İlgili Düzeltmeler</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="str">
-        <v xml:space="preserve">    Faaliyetlerden Elde Edilen Nakit Akışları</v>
-      </c>
-      <c r="B49">
-        <v>114117683</v>
-      </c>
-      <c r="D49">
-        <v>104396279</v>
-      </c>
-    </row>
+        <v xml:space="preserve">    Ana Ortaklık Payları</v>
+      </c>
+      <c r="B48">
+        <v>283959099.5355122</v>
+      </c>
+      <c r="C48">
+        <v>123959412.53551215</v>
+      </c>
+      <c r="D48">
+        <v>165507814.53551215</v>
+      </c>
+      <c r="E48">
+        <v>-111646194.87559286</v>
+      </c>
+      <c r="H48">
+        <v>1132237955.8877137</v>
+      </c>
+      <c r="J48">
+        <v>1276150740.1906705</v>
+      </c>
+      <c r="K48">
+        <v>-199703.82940229628</v>
+      </c>
+    </row>
+    <row r="49"/>
     <row r="50">
       <c r="A50" t="str">
-        <v xml:space="preserve">    Ödenen Temettüler</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="str">
-        <v xml:space="preserve">    Alınan Temettüler</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="str">
-        <v xml:space="preserve">    Ödenen Faiz</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="str">
-        <v xml:space="preserve">    Alınan Faiz</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="str">
-        <v xml:space="preserve">    Vergi İadeleri (Ödemeleri)</v>
-      </c>
-      <c r="F54">
-        <v>2619.3161420994174</v>
-      </c>
-      <c r="G54">
-        <v>8655.22234365441</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="str">
-        <v xml:space="preserve">    Katılım (Kar) Payı ve Diğer Finansal Araçlardan Nakit Çıkışları</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="str">
-        <v xml:space="preserve">    Katılım (Kar) Payı ve Diğer Finansal Araçlardan Nakit Girişleri</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="str">
-        <v xml:space="preserve">    Kira Ödemeleri</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="str">
-        <v xml:space="preserve">    Alınan Kira</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="str">
-        <v xml:space="preserve">    Başka İşletmelerin veya Fonların Paylarının veya Borçlanma Araçlarının Edinimi İçin Yapılan Nakit Çıkışları</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="str">
-        <v xml:space="preserve">    Başka İşletmelerin veya Fonların Paylarının veya Borçlanma Araçlarının Satılması Sonucu Elde Edilen Nakit Girişleri</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="str">
-        <v xml:space="preserve">    İştirakler, İş Ortaklıkları ve/veya Müşterek Faaliyetlerin Sermaye Artırımına Katılımdan Kaynaklanan Nakit Çıkışları</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="str">
-        <v xml:space="preserve">    Çalışanlara Sağlanan Faydalara İlişkin Karşılıklar Kapsamında Yapılan Ödemeler</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="str">
-        <v xml:space="preserve">    Diğer Karşılıklara İlişkin Ödemeler</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="str">
-        <v xml:space="preserve">    Diğer Nakit Girişleri (Çıkışları)</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="str">
-        <v xml:space="preserve">    Durdurulan Faaliyetlere İlişkin Net Nakit Akışları</v>
-      </c>
-    </row>
-    <row r="66"/>
-    <row r="67">
-      <c r="A67" t="str">
-        <v xml:space="preserve">    Yatırım Faaliyetlerinden Kaynaklanan Nakit Akışları</v>
-      </c>
-      <c r="B67">
-        <v>-55971204</v>
-      </c>
-      <c r="C67">
-        <v>-39047609.83407974</v>
-      </c>
-      <c r="D67">
-        <v>-108440453</v>
-      </c>
-      <c r="E67">
-        <v>996077.9254370073</v>
-      </c>
-      <c r="F67">
-        <v>-335285381.1913448</v>
-      </c>
-      <c r="G67">
-        <v>-2951242.9797815406</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="str">
-        <v xml:space="preserve">    Bağlı Ortaklıkların Kontrolünün Kaybı Sonucunu Doğuracak Satışlara İlişkin Nakit Girişleri</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="str">
-        <v xml:space="preserve">    Bağlı Ortaklıkların Kontrolünün Kaybı Sonucunu Doğurmayan Satışlara İlişkin Nakit Girişleri</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="str">
-        <v xml:space="preserve">    Bağlı Ortaklıkların Kontrolünün Elde Edilmesine Yönelik Alışlara İlişkin Nakit Çıkışları</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="str">
-        <v xml:space="preserve">    Bağlı Ortaklıklarda İlave Pay Alımlarına ilişkin Nakit Çıkışları</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="str">
-        <v xml:space="preserve">    İştiraklerin ve/veya İş Ortaklıklarının Pay Satışı veya Sermaye Azaltımı Sebebiyle Oluşan Nakit Girişleri</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="str">
-        <v xml:space="preserve">    İştiraklar ve/veya İş Ortaklıkları Pay Alımı veya Sermaye Artırımı Sebebiyle Oluşan Nakit Çıkışları</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="str">
-        <v xml:space="preserve">    İştirakler ve/veya İş Ortaklıkları Sermaye Avansı Ödemelerinden Nakit Çıkışları</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="str">
-        <v xml:space="preserve">    Başka İşletmelerin veya Fonların Paylarının veya Borçlanma Araçlarının Satılması Sonucu Elde Edilen Nakit Girişleri</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="str">
-        <v xml:space="preserve">    Başka İşletmelerin veya Fonların Paylarının veya Borçlanma Araçlarının Edinimi İçin Yapılan Nakit Çıkışları</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="str">
-        <v xml:space="preserve">    Maddi ve Maddi Olmayan Duran Varlıkların Satışından Kaynaklanan Nakit Girişleri</v>
-      </c>
-      <c r="B77">
-        <v>2243435</v>
-      </c>
-      <c r="C77">
-        <v>3223378.4478709437</v>
-      </c>
-      <c r="D77">
-        <v>445898</v>
-      </c>
-      <c r="E77">
-        <v>2224279.4386764155</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="str">
-        <v xml:space="preserve">    Maddi ve Maddi Olmayan Duran Varlıkların Alımından Kaynaklanan Nakit Çıkışları</v>
-      </c>
-      <c r="B78">
-        <v>-261422</v>
-      </c>
-      <c r="C78">
-        <v>-272807.5157370175</v>
-      </c>
-      <c r="D78">
-        <v>-1499116</v>
-      </c>
-      <c r="E78">
-        <v>-1228201.5132394081</v>
-      </c>
-      <c r="F78">
-        <v>-134965.74287097369</v>
-      </c>
-      <c r="G78">
-        <v>-1674594.553435772</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="str">
-        <v xml:space="preserve">    Yatırım Amaçlı Gayrimenkul Satımından Kaynaklanan Nakit Girişleri</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="str">
-        <v xml:space="preserve">    Yatırım Amaçlı Gayrimenkul Alımından Kaynaklanan Nakit Çıkışları</v>
-      </c>
-      <c r="B80">
-        <v>-57953217</v>
-      </c>
-      <c r="D80">
-        <v>-107387235</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="str">
-        <v xml:space="preserve">    Satış Amacıyla Elde Tutulan Duran Varlık Satışlarından Kaynaklanan Nakit Girişleri</v>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="str">
-        <v xml:space="preserve">    Satış Amacıyla Elde Tutulan Duran Varlık Alımlarından Nakit Çıkışları</v>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="str">
-        <v xml:space="preserve">    Canlı Varlık Satışından Kaynaklanan Nakit Girişleri</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="str">
-        <v xml:space="preserve">    Canlı Varlık Alımından Kaynaklanan Nakit Çıkışları</v>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="str">
-        <v xml:space="preserve">    Diğer Uzun Vadeli Varlıkların Satışından Kaynaklanan Nakit Girişleri</v>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="str">
-        <v xml:space="preserve">    Diğer Uzun Vadeli Varlık Alımından Kaynaklanan Nakit Çıkışları</v>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="str">
-        <v xml:space="preserve">    Verilen Nakit Avans ve Borçlar</v>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="str">
-        <v xml:space="preserve">    Verilen Nakit Avans ve Borçlardan Geri Ödemeler</v>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="str">
-        <v xml:space="preserve">    Türev Araçlardan Nakit Girişleri</v>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="str">
-        <v xml:space="preserve">    Türev Araçlardan Nakit Çıkışları</v>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="str">
-        <v xml:space="preserve">    Devlet Teşviklerinden Elde Edilen Nakit Girişleri</v>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="str">
-        <v xml:space="preserve">    Alınan Temettüler</v>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="str">
-        <v xml:space="preserve">    Ödenen Faiz</v>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="str">
-        <v xml:space="preserve">    Alınan Faiz</v>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="str">
-        <v xml:space="preserve">    Katılım (Kar) Payı ve Diğer Finansal Araçlardan Nakit Çıkışları</v>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="str">
-        <v xml:space="preserve">    Katılım (Kar) Payı ve Diğer Finansal Araçlardan Nakit Girişleri</v>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="str">
-        <v xml:space="preserve">    Vergi İadeleri (Ödemeleri)</v>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="str">
-        <v xml:space="preserve">    Diğer Nakit Girişleri (Çıkışları)</v>
-      </c>
-      <c r="C98">
-        <v>-41998180.76621367</v>
-      </c>
-      <c r="F98">
-        <v>-335150415.4484738</v>
-      </c>
-      <c r="G98">
-        <v>-1276648.4263457689</v>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="str">
-        <v xml:space="preserve">    Durdurulan Faaliyetlere İlişkin Net Nakit Akışları</v>
-      </c>
-    </row>
-    <row r="100"/>
-    <row r="101">
-      <c r="A101" t="str">
-        <v xml:space="preserve">    Finansman Faaliyetlerinden Nakit Akışları</v>
-      </c>
-      <c r="B101">
-        <v>-54478702</v>
-      </c>
-      <c r="C101">
-        <v>117833967.89467573</v>
-      </c>
-      <c r="D101">
-        <v>-6729045</v>
-      </c>
-      <c r="E101">
-        <v>-2659871.7131075487</v>
-      </c>
-      <c r="F101">
-        <v>372666941.07779413</v>
-      </c>
-      <c r="G101">
-        <v>8726475.047585249</v>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="str">
-        <v xml:space="preserve">    Bağlı Ortaklıklardaki Kontrolün Kaybına Yol Açmayan Şekilde Ortaklık Payları Değişmelerinden Kaynaklanan Nakit Girişleri</v>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="str">
-        <v xml:space="preserve">    Bağlı Ortaklıklardaki Kontrolün Kaybına Yol Açmayan Şekilde Ortaklık Payları Değişmelerinden Kaynaklanan Nakit Çıkışları</v>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="str">
-        <v xml:space="preserve">    Pay ve Diğer Özkaynağa Dayalı Araçların İhracından Kaynaklanan Nakit Girişleri</v>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="str">
-        <v xml:space="preserve">    Sermaye Avanslarından Nakit Girişleri</v>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="str">
-        <v xml:space="preserve">    İşletmenin Kendi Paylarını ve Diğer Özkaynağa Dayalı Araçlarını Almasıyla İlgili Nakit Çıkışları</v>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="str">
-        <v xml:space="preserve">    İşletmenin Kendi Paylarını ve Diğer Özkaynağa Dayalı Araçlarını Satmasından Kaynaklanan Nakit Girişleri</v>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="str">
-        <v xml:space="preserve">    Ortak Kontrole Tabi İşletmelerin Birleşme Etkisinden Kaynaklanan Nakit Girişleri (Çıkışları)</v>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="str">
-        <v xml:space="preserve">    Borçlanmadan Kaynaklanan Nakit Girişleri</v>
-      </c>
-      <c r="B109">
-        <v>12549625</v>
-      </c>
-      <c r="C109">
-        <v>156802861.53914803</v>
-      </c>
-      <c r="D109">
-        <v>2432337</v>
-      </c>
-      <c r="E109">
-        <v>2299187.7061314676</v>
-      </c>
-      <c r="F109">
-        <v>58095008.62649901</v>
-      </c>
-      <c r="G109">
-        <v>6134348.65930352</v>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="str">
-        <v xml:space="preserve">    Borç Ödemelerine İlişkin Nakit Çıkışları</v>
-      </c>
-      <c r="B110">
-        <v>-13651649</v>
-      </c>
-      <c r="C110">
-        <v>-6451545.757007264</v>
-      </c>
-      <c r="D110">
-        <v>-7470216</v>
-      </c>
-      <c r="E110">
-        <v>-3281958.2533039125</v>
-      </c>
-      <c r="F110">
-        <v>-11259075.12854521</v>
-      </c>
-      <c r="G110">
-        <v>-3541081.668414894</v>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="str">
-        <v xml:space="preserve">    İlişkili Taraflardan Alınan Diğer Borçlardaki Artış</v>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="str">
-        <v xml:space="preserve">    İlişkili Taraflardan Alınan Diğer Borçlardaki Azalış</v>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="str">
-        <v xml:space="preserve">    Kira Sözleşmelerinden Kaynaklanan Borç Ödemelerine İlişkin Nakit Çıkışları</v>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="str">
-        <v xml:space="preserve">    Türev Araçlardan Nakit Girişleri</v>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="str">
-        <v xml:space="preserve">    Türev Araçlardan Nakit Çıkışları</v>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="str">
-        <v xml:space="preserve">    Devlet Teşviklerinden Elde Edilen Nakit Girişleri</v>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="str">
-        <v xml:space="preserve">    Ödenen Temettüler</v>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="str">
-        <v xml:space="preserve">    Ödenen Faiz</v>
-      </c>
-      <c r="B118">
-        <v>-63066868</v>
-      </c>
-      <c r="C118">
-        <v>-42975627.109817594</v>
-      </c>
-      <c r="D118">
-        <v>-6025375</v>
-      </c>
-      <c r="E118">
-        <v>-2610670.3117259936</v>
-      </c>
-      <c r="F118">
-        <v>-2003142.3689393625</v>
-      </c>
-      <c r="G118">
-        <v>-218610.6297450122</v>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="str">
-        <v xml:space="preserve">    Alınan Faiz</v>
-      </c>
-      <c r="B119">
-        <v>9690190</v>
-      </c>
-      <c r="C119">
-        <v>10458279.222352564</v>
-      </c>
-      <c r="D119">
-        <v>6713829</v>
-      </c>
-      <c r="E119">
-        <v>933005.6275770516</v>
-      </c>
-      <c r="F119">
-        <v>33347.755632242624</v>
-      </c>
-      <c r="G119">
-        <v>62035.0069255944</v>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="str">
-        <v xml:space="preserve">    Katılım (Kar) Payı ve Diğer Finansal Araçlardan Nakit Çıkışları</v>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="str">
-        <v xml:space="preserve">    Katılım (Kar) Payı ve Diğer Finansal Araçlardan Nakit Girişleri</v>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="str">
-        <v xml:space="preserve">    Vergi İadeleri (Ödemeleri)</v>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="str">
-        <v xml:space="preserve">    Diğer Nakit Girişleri (Çıkışları)</v>
-      </c>
-      <c r="D123">
-        <v>-2379620</v>
-      </c>
-      <c r="G123">
-        <v>6289783.67951604</v>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="str">
-        <v xml:space="preserve">    Durdurulan Faaliyetlere İlişkin Net Nakit Akışları</v>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="str">
-        <v xml:space="preserve">    Yabancı Para Çevrim Farklarının Etkisinden Önce Nakit ve Nakit Benzerlerindeki Net Artış (Azalış)</v>
-      </c>
-      <c r="B125">
-        <v>3667777</v>
-      </c>
-      <c r="C125">
-        <v>10227499.729845392</v>
-      </c>
-      <c r="D125">
-        <v>-10773219</v>
-      </c>
-      <c r="E125">
-        <v>24247956.029303104</v>
-      </c>
-      <c r="F125">
-        <v>10578100.935002761</v>
-      </c>
-      <c r="G125">
-        <v>-1439656.505220924</v>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="str">
-        <v xml:space="preserve">    Yabancı Para Çevrim Farklarının Nakit ve Nakit Benzerleri Üzerindeki Etkisi</v>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="str">
-        <v xml:space="preserve">    Nakit ve Nakit Benzerlerindeki Net Artış (Azalış)</v>
-      </c>
-      <c r="B127">
-        <v>3667777</v>
-      </c>
-      <c r="C127">
-        <v>10227499.729845392</v>
-      </c>
-      <c r="D127">
-        <v>-10773219</v>
-      </c>
-      <c r="E127">
-        <v>24247956.029303104</v>
-      </c>
-      <c r="F127">
-        <v>10578100.935002761</v>
-      </c>
-      <c r="G127">
-        <v>-1439656.505220924</v>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="str">
-        <v xml:space="preserve">    Dönem Başı Nakit ve Nakit Benzerleri</v>
-      </c>
-      <c r="B128">
-        <v>44711</v>
-      </c>
-      <c r="D128">
-        <v>10817930</v>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="str">
-        <v xml:space="preserve">    Dönem Sonu Nakit ve Nakit Benzerleri</v>
-      </c>
-      <c r="B129">
-        <v>3712488</v>
-      </c>
-      <c r="D129">
-        <v>44711</v>
+        <v xml:space="preserve">    Amortisman</v>
+      </c>
+      <c r="B50">
+        <v>2030620.6699792542</v>
+      </c>
+      <c r="C50">
+        <v>2095635.6569139848</v>
+      </c>
+      <c r="D50">
+        <v>2171439.6699792542</v>
+      </c>
+      <c r="E50">
+        <v>1305706149.6892354</v>
+      </c>
+      <c r="H50">
+        <v>2584625.02886561</v>
+      </c>
+      <c r="J50">
+        <v>-1278875795.2138054</v>
+      </c>
+      <c r="K50">
+        <v>4413158.714007401</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G129"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K50"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G129"/>
+  <dimension ref="A1:K129"/>
   <cols>
     <col min="1" max="1" customWidth="1" width="40" level="2" outlineLevel="2"/>
     <col min="2" max="2" customWidth="1" width="20"/>
@@ -4307,6 +4012,10 @@
     <col min="5" max="5" customWidth="1" width="20"/>
     <col min="6" max="6" customWidth="1" width="20"/>
     <col min="7" max="7" customWidth="1" width="20"/>
+    <col min="8" max="8" customWidth="1" width="20"/>
+    <col min="9" max="9" customWidth="1" width="20"/>
+    <col min="10" max="10" customWidth="1" width="20"/>
+    <col min="11" max="11" customWidth="1" width="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4314,21 +4023,33 @@
         <v>Kalem</v>
       </c>
       <c r="B1" t="str">
+        <v>2026/6</v>
+      </c>
+      <c r="C1" t="str">
+        <v>2026/3</v>
+      </c>
+      <c r="D1" t="str">
         <v>2025/12</v>
       </c>
-      <c r="C1" t="str">
+      <c r="E1" t="str">
         <v>2025/9</v>
       </c>
-      <c r="D1" t="str">
+      <c r="F1" t="str">
+        <v>2025/6</v>
+      </c>
+      <c r="G1" t="str">
+        <v>2025/3</v>
+      </c>
+      <c r="H1" t="str">
         <v>2024/12</v>
       </c>
-      <c r="E1" t="str">
+      <c r="I1" t="str">
         <v>2024/9</v>
       </c>
-      <c r="F1" t="str">
+      <c r="J1" t="str">
         <v>2023/12</v>
       </c>
-      <c r="G1" t="str">
+      <c r="K1" t="str">
         <v>2022/12</v>
       </c>
     </row>
@@ -4342,10 +4063,34 @@
         <v xml:space="preserve">    İşletme Faaliyetlerinden Nakit Akışları</v>
       </c>
       <c r="B3">
-        <v>182676541.33075058</v>
+        <v>-310141642</v>
+      </c>
+      <c r="C3">
+        <v>-281536746.6048196</v>
       </c>
       <c r="D3">
-        <v>78484529.18302636</v>
+        <v>134384875.93911842</v>
+      </c>
+      <c r="E3">
+        <v>-80734846.95010425</v>
+      </c>
+      <c r="F3">
+        <v>-67640163</v>
+      </c>
+      <c r="G3">
+        <v>3780896.9081396735</v>
+      </c>
+      <c r="H3">
+        <v>122936959.75163282</v>
+      </c>
+      <c r="I3">
+        <v>30513652.161334872</v>
+      </c>
+      <c r="J3">
+        <v>-31563727.997609306</v>
+      </c>
+      <c r="K3">
+        <v>-8496245.983196823</v>
       </c>
     </row>
     <row r="4">
@@ -4353,42 +4098,144 @@
         <v xml:space="preserve">    Dönem Karı (Zararı)</v>
       </c>
       <c r="B4">
-        <v>-22050524.450790256</v>
+        <v>1246532034</v>
+      </c>
+      <c r="C4">
+        <v>-30946121.52534435</v>
       </c>
       <c r="D4">
-        <v>-257405680.05985045</v>
+        <v>165507814.53551215</v>
+      </c>
+      <c r="E4">
+        <v>191474491.34502944</v>
+      </c>
+      <c r="F4">
+        <v>1128080749</v>
+      </c>
+      <c r="G4">
+        <v>752652261.650711</v>
+      </c>
+      <c r="H4">
+        <v>1132237955.8877137</v>
+      </c>
+      <c r="I4">
+        <v>1435358642.108336</v>
+      </c>
+      <c r="J4">
+        <v>1276150740.1906705</v>
+      </c>
+      <c r="K4">
+        <v>-199703.82940229628</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
         <v xml:space="preserve">    Dönem Net Karı (Zararı) Mutabakatı İle İlgili Düzeltmeler</v>
       </c>
+      <c r="B5">
+        <v>-1144028236</v>
+      </c>
+      <c r="C5">
+        <v>-43523347.742739365</v>
+      </c>
+      <c r="D5">
+        <v>-657975455.0779142</v>
+      </c>
+      <c r="F5">
+        <v>-1086933628</v>
+      </c>
+      <c r="G5">
+        <v>-744528146.6539955</v>
+      </c>
+      <c r="H5">
+        <v>-1137586701.4817767</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
         <v xml:space="preserve">    Amortisman ve İtfa Gideri İle İlgili Düzeltmeler</v>
       </c>
       <c r="B6">
-        <v>132495147.79908055</v>
+        <v>908431</v>
+      </c>
+      <c r="C6">
+        <v>448966.1647951505</v>
       </c>
       <c r="D6">
-        <v>1239437873.1461413</v>
+        <v>2171439.6699792542</v>
+      </c>
+      <c r="E6">
+        <v>-153854721.4948474</v>
+      </c>
+      <c r="F6">
+        <v>1049250</v>
+      </c>
+      <c r="G6">
+        <v>524770.17786042</v>
+      </c>
+      <c r="H6">
+        <v>2584625.02886561</v>
+      </c>
+      <c r="I6">
+        <v>-1456976246.1552172</v>
+      </c>
+      <c r="J6">
+        <v>-1278875795.2138054</v>
+      </c>
+      <c r="K6">
+        <v>4413158.714007401</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
         <v xml:space="preserve">    Değer Düşüklüğü (İptali) İle İlgili Düzeltmeler</v>
       </c>
+      <c r="E7">
+        <v>1617279.2957662405</v>
+      </c>
+      <c r="I7">
+        <v>3754980.8133148416</v>
+      </c>
+      <c r="J7">
+        <v>2770515.208240032</v>
+      </c>
+      <c r="K7">
+        <v>2590117.1801515794</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
         <v xml:space="preserve">    Karşılıklar İle İlgili Düzeltmeler</v>
       </c>
       <c r="B8">
-        <v>177436.89864636108</v>
+        <v>-13750</v>
+      </c>
+      <c r="C8">
+        <v>154859.09326719667</v>
       </c>
       <c r="D8">
-        <v>571308.2005066494</v>
+        <v>-207492.9539225982</v>
+      </c>
+      <c r="E8">
+        <v>-416442.47852531174</v>
+      </c>
+      <c r="F8">
+        <v>-402569</v>
+      </c>
+      <c r="G8">
+        <v>-579803.9598343825</v>
+      </c>
+      <c r="H8">
+        <v>-8658.885869426018</v>
+      </c>
+      <c r="I8">
+        <v>-681430.8842992143</v>
+      </c>
+      <c r="J8">
+        <v>429981.11716787145</v>
+      </c>
+      <c r="K8">
+        <v>207673.15604267022</v>
       </c>
     </row>
     <row r="9">
@@ -4411,10 +4258,34 @@
         <v xml:space="preserve">    Faiz (Gelirleri) ve Giderleri İle İlgili Düzeltmeler</v>
       </c>
       <c r="B12">
-        <v>-32915813.125046775</v>
+        <v>21561186</v>
+      </c>
+      <c r="C12">
+        <v>8261648.620284789</v>
       </c>
       <c r="D12">
-        <v>2582226.272750221</v>
+        <v>-2968264.4274005587</v>
+      </c>
+      <c r="E12">
+        <v>35793366.08383771</v>
+      </c>
+      <c r="F12">
+        <v>19937067</v>
+      </c>
+      <c r="G12">
+        <v>2957863.258238206</v>
+      </c>
+      <c r="H12">
+        <v>3332379.233562995</v>
+      </c>
+      <c r="I12">
+        <v>291552.0086510534</v>
+      </c>
+      <c r="J12">
+        <v>3865354.4511763416</v>
+      </c>
+      <c r="K12">
+        <v>342277.97088102356</v>
       </c>
     </row>
     <row r="13">
@@ -4447,10 +4318,25 @@
         <v xml:space="preserve">    Gerçeğe Uygun Değer Kayıpları (Kazançları) İle İlgili Düzeltmeler</v>
       </c>
       <c r="B18">
-        <v>-1163023564.6768432</v>
+        <v>-1829305377</v>
       </c>
       <c r="D18">
-        <v>340709266.86950064</v>
+        <v>-697809911.1560075</v>
+      </c>
+      <c r="E18">
+        <v>671765542.398976</v>
+      </c>
+      <c r="F18">
+        <v>-1810748442</v>
+      </c>
+      <c r="H18">
+        <v>-1923349562.041826</v>
+      </c>
+      <c r="I18">
+        <v>-2324568473.571653</v>
+      </c>
+      <c r="J18">
+        <v>-1651774660.6921322</v>
       </c>
     </row>
     <row r="19">
@@ -4463,16 +4349,52 @@
         <v xml:space="preserve">    Vergi (Geliri) Gideri İle İlgili Düzeltmeler</v>
       </c>
       <c r="B20">
-        <v>861846145.4336218</v>
+        <v>691394509</v>
+      </c>
+      <c r="C20">
+        <v>-31954703.571786575</v>
       </c>
       <c r="D20">
-        <v>-38696999.86906409</v>
+        <v>66835083.17078606</v>
+      </c>
+      <c r="E20">
+        <v>-948074125.3583134</v>
+      </c>
+      <c r="F20">
+        <v>689326671</v>
+      </c>
+      <c r="G20">
+        <v>-743869773.4548018</v>
+      </c>
+      <c r="H20">
+        <v>802513998.717235</v>
+      </c>
+      <c r="I20">
+        <v>848083549.2891674</v>
+      </c>
+      <c r="J20">
+        <v>367133034.9196221</v>
+      </c>
+      <c r="K20">
+        <v>1320272.2615243436</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
         <v xml:space="preserve">    Nakit Dışı Kalemlere İlişkin Diğer Düzeltmeler</v>
       </c>
+      <c r="E21">
+        <v>11726489.955479596</v>
+      </c>
+      <c r="I21">
+        <v>16143576.189601513</v>
+      </c>
+      <c r="J21">
+        <v>-1300020.2178800318</v>
+      </c>
+      <c r="K21">
+        <v>-47181.85459221554</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
@@ -4509,16 +4431,58 @@
         <v xml:space="preserve">    İşletme Sermayesinde Gerçekleşen Değişimler</v>
       </c>
       <c r="B28">
-        <v>632819063.9824603</v>
+        <v>-412533690</v>
+      </c>
+      <c r="C28">
+        <v>-204821902.88468066</v>
       </c>
       <c r="D28">
-        <v>64669251.09673559</v>
+        <v>626852516.4815204</v>
+      </c>
+      <c r="E28">
+        <v>-118354616.80028631</v>
+      </c>
+      <c r="F28">
+        <v>-108787284</v>
+      </c>
+      <c r="G28">
+        <v>-4088129.17335792</v>
+      </c>
+      <c r="H28">
+        <v>128285705.3456958</v>
+      </c>
+      <c r="I28">
+        <v>52131256.20821627</v>
+      </c>
+      <c r="J28">
+        <v>-28841757.47869459</v>
+      </c>
+      <c r="K28">
+        <v>-12719893.24947583</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
         <v xml:space="preserve">    Finansal Yatırımlardaki Azalış (Artış)</v>
       </c>
+      <c r="B29">
+        <v>-142397680</v>
+      </c>
+      <c r="C29">
+        <v>-229798321.40398115</v>
+      </c>
+      <c r="D29">
+        <v>27361305.664805476</v>
+      </c>
+      <c r="F29">
+        <v>27402279</v>
+      </c>
+      <c r="G29">
+        <v>25407785.260089897</v>
+      </c>
+      <c r="H29">
+        <v>-27501092.560920015</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
@@ -4530,26 +4494,83 @@
         <v xml:space="preserve">    Ticari Alacaklardaki Azalış (Artış) ile İlgili Düzeltmeler</v>
       </c>
       <c r="B31">
-        <v>20784252.910216738</v>
+        <v>-49189315</v>
+      </c>
+      <c r="C31">
+        <v>4248602.189666231</v>
       </c>
       <c r="D31">
-        <v>-7113469.051840984</v>
+        <v>-507279.0563737418</v>
+      </c>
+      <c r="E31">
+        <v>-24982795.69323656</v>
+      </c>
+      <c r="F31">
+        <v>7550219</v>
+      </c>
+      <c r="G31">
+        <v>3895957.7174001876</v>
+      </c>
+      <c r="H31">
+        <v>-6670230.769945958</v>
+      </c>
+      <c r="I31">
+        <v>1706583.680698024</v>
+      </c>
+      <c r="J31">
+        <v>-656031.0365999253</v>
+      </c>
+      <c r="K31">
+        <v>402498.3074554084</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
         <v xml:space="preserve">    Finans Sektörü Faaliyetlerinden Alacaklarda Azalış (Artış)</v>
       </c>
+      <c r="E32">
+        <v>27398912.426562566</v>
+      </c>
+      <c r="I32">
+        <v>1348.0880993816859</v>
+      </c>
+      <c r="J32">
+        <v>-1349.3169855251515</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
         <v xml:space="preserve">    Faaliyetlerle İlgili Diğer Alacaklardaki Azalış (Artış) ile İlgili Düzeltmeler</v>
       </c>
       <c r="B33">
-        <v>-1138060.1019951175</v>
+        <v>-4125352</v>
+      </c>
+      <c r="C33">
+        <v>-719729.3329264446</v>
       </c>
       <c r="D33">
-        <v>-10786881.59030892</v>
+        <v>-38611.117895653515</v>
+      </c>
+      <c r="E33">
+        <v>1301567.3855346548</v>
+      </c>
+      <c r="F33">
+        <v>-480839</v>
+      </c>
+      <c r="G33">
+        <v>1960567.9152490215</v>
+      </c>
+      <c r="H33">
+        <v>-8697150.773198782</v>
+      </c>
+      <c r="I33">
+        <v>4005470.820368138</v>
+      </c>
+      <c r="J33">
+        <v>-10285805.285187783</v>
+      </c>
+      <c r="K33">
+        <v>1330641.6028029057</v>
       </c>
     </row>
     <row r="34">
@@ -4571,11 +4592,29 @@
       <c r="A37" t="str">
         <v xml:space="preserve">    Stoklardaki Azalışlar (Artışlar) İle İlgili Düzeltmeler</v>
       </c>
-      <c r="B37">
-        <v>-57265718.11837362</v>
-      </c>
       <c r="D37">
-        <v>17095973.257140905</v>
+        <v>-63888324.057372645</v>
+      </c>
+      <c r="E37">
+        <v>3547731.622991667</v>
+      </c>
+      <c r="F37">
+        <v>-4158317</v>
+      </c>
+      <c r="G37">
+        <v>842576.4372779138</v>
+      </c>
+      <c r="H37">
+        <v>8573501.69456753</v>
+      </c>
+      <c r="I37">
+        <v>-11558700.299223099</v>
+      </c>
+      <c r="J37">
+        <v>-22402863.521442026</v>
+      </c>
+      <c r="K37">
+        <v>-260311.26511187272</v>
       </c>
     </row>
     <row r="38">
@@ -4588,10 +4627,34 @@
         <v xml:space="preserve">    Peşin Ödenmiş Giderlerdeki Azalış (Artış)</v>
       </c>
       <c r="B39">
-        <v>-4674963.5799442865</v>
+        <v>-166154278</v>
+      </c>
+      <c r="C39">
+        <v>-21330759.797268502</v>
       </c>
       <c r="D39">
-        <v>65854928.817306265</v>
+        <v>-6518889.271879723</v>
+      </c>
+      <c r="E39">
+        <v>-1013656.5665266898</v>
+      </c>
+      <c r="F39">
+        <v>1739</v>
+      </c>
+      <c r="G39">
+        <v>-9805.637976693546</v>
+      </c>
+      <c r="H39">
+        <v>40460407.679481596</v>
+      </c>
+      <c r="I39">
+        <v>-37090294.42418078</v>
+      </c>
+      <c r="J39">
+        <v>-32198887.631948616</v>
+      </c>
+      <c r="K39">
+        <v>-6071255.46302885</v>
       </c>
     </row>
     <row r="40">
@@ -4599,10 +4662,34 @@
         <v xml:space="preserve">    Ticari Borçlardaki Artış (Azalış) ile İlgili Düzeltmeler</v>
       </c>
       <c r="B40">
-        <v>2714188.1580532305</v>
+        <v>-18501039</v>
+      </c>
+      <c r="C40">
+        <v>-19590709.04775858</v>
       </c>
       <c r="D40">
-        <v>-12336219.486514099</v>
+        <v>19736654.410777863</v>
+      </c>
+      <c r="E40">
+        <v>16540428.99411384</v>
+      </c>
+      <c r="F40">
+        <v>14475935</v>
+      </c>
+      <c r="G40">
+        <v>1648307.0902957015</v>
+      </c>
+      <c r="H40">
+        <v>-7735145.373588096</v>
+      </c>
+      <c r="I40">
+        <v>6791975.0662208</v>
+      </c>
+      <c r="J40">
+        <v>6913709.756478638</v>
+      </c>
+      <c r="K40">
+        <v>-8090841.360012117</v>
       </c>
     </row>
     <row r="41">
@@ -4615,10 +4702,34 @@
         <v xml:space="preserve">    Çalışanlara Sağlanan Faydalar Kapsamında Borçlardaki Artış (Azalış)</v>
       </c>
       <c r="B42">
-        <v>-20654.751124072674</v>
+        <v>-24164</v>
+      </c>
+      <c r="C42">
+        <v>185144.9560172135</v>
       </c>
       <c r="D42">
-        <v>-32548.062903522776</v>
+        <v>205520.47550137033</v>
+      </c>
+      <c r="E42">
+        <v>229843.49095693184</v>
+      </c>
+      <c r="F42">
+        <v>51355</v>
+      </c>
+      <c r="G42">
+        <v>395015.35844406404</v>
+      </c>
+      <c r="H42">
+        <v>133144.0598314679</v>
+      </c>
+      <c r="I42">
+        <v>171472.62802846267</v>
+      </c>
+      <c r="J42">
+        <v>-75934.10369087853</v>
+      </c>
+      <c r="K42">
+        <v>-19159.563862771072</v>
       </c>
     </row>
     <row r="43">
@@ -4631,10 +4742,34 @@
         <v xml:space="preserve">    Faaliyetler ile İlgili Diğer Borçlardaki Artış (Azalış) ile İlgili Düzeltmeler</v>
       </c>
       <c r="B44">
-        <v>675322632.1452712</v>
+        <v>-131844459</v>
+      </c>
+      <c r="C44">
+        <v>1676299.6558522168</v>
       </c>
       <c r="D44">
-        <v>-4606787.9823563695</v>
+        <v>648668726.0406219</v>
+      </c>
+      <c r="E44">
+        <v>-146590569.04795054</v>
+      </c>
+      <c r="F44">
+        <v>-145306267</v>
+      </c>
+      <c r="G44">
+        <v>-34066867.74169197</v>
+      </c>
+      <c r="H44">
+        <v>96262401.59475452</v>
+      </c>
+      <c r="I44">
+        <v>101687350.78064696</v>
+      </c>
+      <c r="J44">
+        <v>29865403.660681516</v>
+      </c>
+      <c r="K44">
+        <v>-11465.50771853339</v>
       </c>
     </row>
     <row r="45">
@@ -4652,18 +4787,57 @@
         <v xml:space="preserve">    Ertelenmiş Gelirlerdeki Artış (Azalış)</v>
       </c>
       <c r="B47">
-        <v>-2870677.564275575</v>
+        <v>99702597</v>
+      </c>
+      <c r="C47">
+        <v>-5644328.758874401</v>
+      </c>
+      <c r="D47">
+        <v>1833413.3933355534</v>
+      </c>
+      <c r="E47">
+        <v>5213920.587267837</v>
+      </c>
+      <c r="F47">
+        <v>-8323388</v>
+      </c>
+      <c r="G47">
+        <v>-4161665.5724460403</v>
+      </c>
+      <c r="H47">
+        <v>33459869.794713527</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
         <v xml:space="preserve">    İşletme Sermayesinde Gerçekleşen Diğer Artış (Azalış) ile İlgili Düzeltmeler</v>
       </c>
+      <c r="C48">
+        <v>66151898.65459277</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
         <v xml:space="preserve">    Faaliyetlerden Elde Edilen Nakit Akışları</v>
       </c>
+      <c r="B49">
+        <v>-310029892</v>
+      </c>
+      <c r="C49">
+        <v>-279291372.1527644</v>
+      </c>
+      <c r="D49">
+        <v>134384875.93911842</v>
+      </c>
+      <c r="F49">
+        <v>-67640163</v>
+      </c>
+      <c r="G49">
+        <v>4035985.823357661</v>
+      </c>
+      <c r="H49">
+        <v>122936959.75163282</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
@@ -4688,6 +4862,21 @@
     <row r="54">
       <c r="A54" t="str">
         <v xml:space="preserve">    Vergi İadeleri (Ödemeleri)</v>
+      </c>
+      <c r="B54">
+        <v>-111750</v>
+      </c>
+      <c r="C54">
+        <v>-2245374.45205522</v>
+      </c>
+      <c r="G54">
+        <v>-255088.9152179873</v>
+      </c>
+      <c r="J54">
+        <v>3084.5042200984794</v>
+      </c>
+      <c r="K54">
+        <v>10192.381673903104</v>
       </c>
     </row>
     <row r="55">
@@ -4751,10 +4940,34 @@
         <v xml:space="preserve">    Yatırım Faaliyetlerinden Kaynaklanan Nakit Akışları</v>
       </c>
       <c r="B67">
-        <v>-16923594.165920258</v>
+        <v>-74680230</v>
+      </c>
+      <c r="C67">
+        <v>-57157649.12945273</v>
       </c>
       <c r="D67">
-        <v>-109436530.925437</v>
+        <v>-65911637.0747125</v>
+      </c>
+      <c r="E67">
+        <v>-45982428.53626731</v>
+      </c>
+      <c r="F67">
+        <v>-40950165</v>
+      </c>
+      <c r="G67">
+        <v>-536382.2020539267</v>
+      </c>
+      <c r="H67">
+        <v>-127699375.24219453</v>
+      </c>
+      <c r="I67">
+        <v>1172980.4261408523</v>
+      </c>
+      <c r="J67">
+        <v>-394831748.8675169</v>
+      </c>
+      <c r="K67">
+        <v>-3475380.9512951337</v>
       </c>
     </row>
     <row r="68">
@@ -4807,10 +5020,22 @@
         <v xml:space="preserve">    Maddi ve Maddi Olmayan Duran Varlıkların Satışından Kaynaklanan Nakit Girişleri</v>
       </c>
       <c r="B77">
-        <v>-979943.4478709437</v>
+        <v>1315565</v>
+      </c>
+      <c r="C77">
+        <v>1361483.350871794</v>
       </c>
       <c r="D77">
-        <v>-1778381.4386764155</v>
+        <v>2641866.941449172</v>
+      </c>
+      <c r="E77">
+        <v>3795847.4220157876</v>
+      </c>
+      <c r="H77">
+        <v>525089.0645186078</v>
+      </c>
+      <c r="I77">
+        <v>2619309.370489603</v>
       </c>
     </row>
     <row r="78">
@@ -4818,10 +5043,31 @@
         <v xml:space="preserve">    Maddi ve Maddi Olmayan Duran Varlıkların Alımından Kaynaklanan Nakit Çıkışları</v>
       </c>
       <c r="B78">
-        <v>11385.5157370175</v>
+        <v>-284981</v>
       </c>
       <c r="D78">
-        <v>-270914.48676059186</v>
+        <v>-307850.3007965577</v>
+      </c>
+      <c r="E78">
+        <v>-321257.8733970457</v>
+      </c>
+      <c r="F78">
+        <v>-223909</v>
+      </c>
+      <c r="G78">
+        <v>-142631.74201523766</v>
+      </c>
+      <c r="H78">
+        <v>-1765357.5886074333</v>
+      </c>
+      <c r="I78">
+        <v>-1446328.9443487509</v>
+      </c>
+      <c r="J78">
+        <v>-158935.53159282735</v>
+      </c>
+      <c r="K78">
+        <v>-1972000.967735996</v>
       </c>
     </row>
     <row r="79">
@@ -4833,6 +5079,24 @@
       <c r="A80" t="str">
         <v xml:space="preserve">    Yatırım Amaçlı Gayrimenkul Alımından Kaynaklanan Nakit Çıkışları</v>
       </c>
+      <c r="B80">
+        <v>-75710814</v>
+      </c>
+      <c r="C80">
+        <v>-58519132.48032452</v>
+      </c>
+      <c r="D80">
+        <v>-68245653.71536511</v>
+      </c>
+      <c r="F80">
+        <v>-40726256</v>
+      </c>
+      <c r="G80">
+        <v>-393750.46003868897</v>
+      </c>
+      <c r="H80">
+        <v>-126459106.7181057</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
@@ -4922,6 +5186,15 @@
     <row r="98">
       <c r="A98" t="str">
         <v xml:space="preserve">    Diğer Nakit Girişleri (Çıkışları)</v>
+      </c>
+      <c r="E98">
+        <v>-49457018.08488606</v>
+      </c>
+      <c r="J98">
+        <v>-394672813.3359241</v>
+      </c>
+      <c r="K98">
+        <v>-1503379.983559138</v>
       </c>
     </row>
     <row r="99">
@@ -4935,10 +5208,34 @@
         <v xml:space="preserve">    Finansman Faaliyetlerinden Nakit Akışları</v>
       </c>
       <c r="B101">
-        <v>-172312669.89467573</v>
+        <v>399535908</v>
+      </c>
+      <c r="C101">
+        <v>421408696.4665998</v>
       </c>
       <c r="D101">
-        <v>-4069173.2868924513</v>
+        <v>-64154068.12627104</v>
+      </c>
+      <c r="E101">
+        <v>138761169.5283023</v>
+      </c>
+      <c r="F101">
+        <v>178385631</v>
+      </c>
+      <c r="G101">
+        <v>-3253368.9949233728</v>
+      </c>
+      <c r="H101">
+        <v>-7924117.049535129</v>
+      </c>
+      <c r="I101">
+        <v>-3132262.42229198</v>
+      </c>
+      <c r="J101">
+        <v>438852238.5557909</v>
+      </c>
+      <c r="K101">
+        <v>10276288.790892785</v>
       </c>
     </row>
     <row r="102">
@@ -4955,11 +5252,20 @@
       <c r="A104" t="str">
         <v xml:space="preserve">    Pay ve Diğer Özkaynağa Dayalı Araçların İhracından Kaynaklanan Nakit Girişleri</v>
       </c>
+      <c r="B104">
+        <v>401845828</v>
+      </c>
+      <c r="C104">
+        <v>401843289.6674848</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
         <v xml:space="preserve">    Sermaye Avanslarından Nakit Girişleri</v>
       </c>
+      <c r="C105">
+        <v>45213162.121063225</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
@@ -4980,11 +5286,26 @@
       <c r="A109" t="str">
         <v xml:space="preserve">    Borçlanmadan Kaynaklanan Nakit Girişleri</v>
       </c>
-      <c r="B109">
-        <v>-144253236.53914803</v>
-      </c>
       <c r="D109">
-        <v>133149.2938685324</v>
+        <v>14778426.571344417</v>
+      </c>
+      <c r="E109">
+        <v>184650901.9538819</v>
+      </c>
+      <c r="F109">
+        <v>198257740</v>
+      </c>
+      <c r="H109">
+        <v>2864317.758599493</v>
+      </c>
+      <c r="I109">
+        <v>2707521.2756398455</v>
+      </c>
+      <c r="J109">
+        <v>68412627.40108459</v>
+      </c>
+      <c r="K109">
+        <v>7223803.1992623</v>
       </c>
     </row>
     <row r="110">
@@ -4992,10 +5313,34 @@
         <v xml:space="preserve">    Borç Ödemelerine İlişkin Nakit Çıkışları</v>
       </c>
       <c r="B110">
-        <v>-7200103.242992736</v>
+        <v>-21627531</v>
+      </c>
+      <c r="C110">
+        <v>-16593355.704109924</v>
       </c>
       <c r="D110">
-        <v>-4188257.7466960875</v>
+        <v>-16076168.995031122</v>
+      </c>
+      <c r="E110">
+        <v>-7597334.2025439385</v>
+      </c>
+      <c r="F110">
+        <v>-2003032</v>
+      </c>
+      <c r="G110">
+        <v>-962555.5824699878</v>
+      </c>
+      <c r="H110">
+        <v>-8796919.320544017</v>
+      </c>
+      <c r="I110">
+        <v>-3864830.9456792255</v>
+      </c>
+      <c r="J110">
+        <v>-13258676.25912771</v>
+      </c>
+      <c r="K110">
+        <v>-4169974.4350770074</v>
       </c>
     </row>
     <row r="111">
@@ -5038,10 +5383,34 @@
         <v xml:space="preserve">    Ödenen Faiz</v>
       </c>
       <c r="B118">
-        <v>-20091240.890182406</v>
+        <v>-40012990</v>
+      </c>
+      <c r="C118">
+        <v>-21723094.470005743</v>
       </c>
       <c r="D118">
-        <v>-3414704.6882740064</v>
+        <v>-74267484.31309071</v>
+      </c>
+      <c r="E118">
+        <v>-50608057.97782147</v>
+      </c>
+      <c r="F118">
+        <v>-25809130</v>
+      </c>
+      <c r="G118">
+        <v>-2290813.4124533846</v>
+      </c>
+      <c r="H118">
+        <v>-7095475.920779654</v>
+      </c>
+      <c r="I118">
+        <v>-3074322.8983998676</v>
+      </c>
+      <c r="J118">
+        <v>-2358898.5656001098</v>
+      </c>
+      <c r="K118">
+        <v>-257435.6715361634</v>
       </c>
     </row>
     <row r="119">
@@ -5049,10 +5418,31 @@
         <v xml:space="preserve">    Alınan Faiz</v>
       </c>
       <c r="B119">
-        <v>-768089.2223525643</v>
+        <v>17080601</v>
+      </c>
+      <c r="C119">
+        <v>12668694.852167461</v>
       </c>
       <c r="D119">
-        <v>5780823.3724229485</v>
+        <v>11411158.610506367</v>
+      </c>
+      <c r="E119">
+        <v>12315659.75478585</v>
+      </c>
+      <c r="F119">
+        <v>7940053</v>
+      </c>
+      <c r="H119">
+        <v>7906198.702276978</v>
+      </c>
+      <c r="I119">
+        <v>1098706.5476297957</v>
+      </c>
+      <c r="J119">
+        <v>39270.285600584466</v>
+      </c>
+      <c r="K119">
+        <v>73052.36568445187</v>
       </c>
     </row>
     <row r="120">
@@ -5074,6 +5464,15 @@
       <c r="A123" t="str">
         <v xml:space="preserve">    Diğer Nakit Girişleri (Çıkışları)</v>
       </c>
+      <c r="B123">
+        <v>42250000</v>
+      </c>
+      <c r="H123">
+        <v>-2802238.2690879293</v>
+      </c>
+      <c r="K123">
+        <v>7406843.332559204</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
@@ -5085,10 +5484,34 @@
         <v xml:space="preserve">    Yabancı Para Çevrim Farklarının Etkisinden Önce Nakit ve Nakit Benzerlerindeki Net Artış (Azalış)</v>
       </c>
       <c r="B125">
-        <v>-6559722.729845392</v>
+        <v>14714036</v>
+      </c>
+      <c r="C125">
+        <v>82714300.7323275</v>
       </c>
       <c r="D125">
-        <v>-35021175.0293031</v>
+        <v>4319170.738134878</v>
+      </c>
+      <c r="E125">
+        <v>12043894.041930735</v>
+      </c>
+      <c r="F125">
+        <v>69795303</v>
+      </c>
+      <c r="G125">
+        <v>-8854.288837625494</v>
+      </c>
+      <c r="H125">
+        <v>-12686532.540096818</v>
+      </c>
+      <c r="I125">
+        <v>28554370.165183745</v>
+      </c>
+      <c r="J125">
+        <v>12456761.690664703</v>
+      </c>
+      <c r="K125">
+        <v>-1695338.143599171</v>
       </c>
     </row>
     <row r="126">
@@ -5101,32 +5524,92 @@
         <v xml:space="preserve">    Nakit ve Nakit Benzerlerindeki Net Artış (Azalış)</v>
       </c>
       <c r="B127">
-        <v>-6559722.729845392</v>
+        <v>14714036</v>
+      </c>
+      <c r="C127">
+        <v>82714300.7323275</v>
       </c>
       <c r="D127">
-        <v>-35021175.0293031</v>
+        <v>4319170.738134878</v>
+      </c>
+      <c r="E127">
+        <v>12043894.041930735</v>
+      </c>
+      <c r="F127">
+        <v>69795303</v>
+      </c>
+      <c r="G127">
+        <v>-8854.288837625494</v>
+      </c>
+      <c r="H127">
+        <v>-12686532.540096818</v>
+      </c>
+      <c r="I127">
+        <v>28554370.165183745</v>
+      </c>
+      <c r="J127">
+        <v>12456761.690664703</v>
+      </c>
+      <c r="K127">
+        <v>-1695338.143599171</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
         <v xml:space="preserve">    Dönem Başı Nakit ve Nakit Benzerleri</v>
       </c>
+      <c r="B128">
+        <v>4371768</v>
+      </c>
+      <c r="C128">
+        <v>4371740.370469699</v>
+      </c>
+      <c r="D128">
+        <v>52651.631457623655</v>
+      </c>
+      <c r="F128">
+        <v>52652</v>
+      </c>
+      <c r="G128">
+        <v>52650.59352322629</v>
+      </c>
+      <c r="H128">
+        <v>12739184.17155444</v>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
         <v xml:space="preserve">    Dönem Sonu Nakit ve Nakit Benzerleri</v>
       </c>
+      <c r="B129">
+        <v>19085804</v>
+      </c>
+      <c r="C129">
+        <v>87086041.1027972</v>
+      </c>
+      <c r="D129">
+        <v>4371822.369592501</v>
+      </c>
+      <c r="F129">
+        <v>69847955</v>
+      </c>
+      <c r="G129">
+        <v>43796.30468560079</v>
+      </c>
+      <c r="H129">
+        <v>52651.631457623655</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G129"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K129"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G129"/>
+  <dimension ref="A1:K129"/>
   <cols>
     <col min="1" max="1" customWidth="1" width="40" level="2" outlineLevel="2"/>
     <col min="2" max="2" customWidth="1" width="20"/>
@@ -5135,6 +5618,10 @@
     <col min="5" max="5" customWidth="1" width="20"/>
     <col min="6" max="6" customWidth="1" width="20"/>
     <col min="7" max="7" customWidth="1" width="20"/>
+    <col min="8" max="8" customWidth="1" width="20"/>
+    <col min="9" max="9" customWidth="1" width="20"/>
+    <col min="10" max="10" customWidth="1" width="20"/>
+    <col min="11" max="11" customWidth="1" width="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5142,21 +5629,33 @@
         <v>Kalem</v>
       </c>
       <c r="B1" t="str">
+        <v>2026/6</v>
+      </c>
+      <c r="C1" t="str">
+        <v>2026/3</v>
+      </c>
+      <c r="D1" t="str">
         <v>2025/12</v>
       </c>
-      <c r="C1" t="str">
+      <c r="E1" t="str">
         <v>2025/9</v>
       </c>
-      <c r="D1" t="str">
+      <c r="F1" t="str">
+        <v>2025/6</v>
+      </c>
+      <c r="G1" t="str">
+        <v>2025/3</v>
+      </c>
+      <c r="H1" t="str">
         <v>2024/12</v>
       </c>
-      <c r="E1" t="str">
+      <c r="I1" t="str">
         <v>2024/9</v>
       </c>
-      <c r="F1" t="str">
+      <c r="J1" t="str">
         <v>2023/12</v>
       </c>
-      <c r="G1" t="str">
+      <c r="K1" t="str">
         <v>2022/12</v>
       </c>
     </row>
@@ -5170,19 +5669,25 @@
         <v xml:space="preserve">    İşletme Faaliyetlerinden Nakit Akışları</v>
       </c>
       <c r="B3">
-        <v>114117683</v>
+        <v>-28604895.395180404</v>
       </c>
       <c r="C3">
-        <v>9925670.852275774</v>
+        <v>-281536746.6048196</v>
       </c>
       <c r="D3">
-        <v>104396279</v>
+        <v>215119722.88922268</v>
+      </c>
+      <c r="E3">
+        <v>-13094683.950104252</v>
       </c>
       <c r="F3">
-        <v>-26803458.951446593</v>
+        <v>-71421059.90813968</v>
       </c>
       <c r="G3">
-        <v>-7214888.5730246315</v>
+        <v>3780896.9081396735</v>
+      </c>
+      <c r="H3">
+        <v>92423307.59029795</v>
       </c>
     </row>
     <row r="4">
@@ -5190,19 +5695,25 @@
         <v xml:space="preserve">    Dönem Karı (Zararı)</v>
       </c>
       <c r="B4">
-        <v>140546830</v>
+        <v>1277478155.5253444</v>
       </c>
       <c r="C4">
-        <v>-94808325.6090602</v>
+        <v>-30946121.52534435</v>
       </c>
       <c r="D4">
-        <v>961480012</v>
+        <v>-25966676.809517294</v>
+      </c>
+      <c r="E4">
+        <v>-936606257.6549705</v>
       </c>
       <c r="F4">
-        <v>1083688656.2686636</v>
+        <v>375428487.34928894</v>
       </c>
       <c r="G4">
-        <v>-169585.58869334348</v>
+        <v>752652261.650711</v>
+      </c>
+      <c r="H4">
+        <v>-303120686.2206223</v>
       </c>
     </row>
     <row r="5">
@@ -5210,10 +5721,16 @@
         <v xml:space="preserve">    Dönem Net Karı (Zararı) Mutabakatı İle İlgili Düzeltmeler</v>
       </c>
       <c r="B5">
-        <v>-558743191</v>
-      </c>
-      <c r="D5">
-        <v>-966022089</v>
+        <v>-1100504888.2572606</v>
+      </c>
+      <c r="C5">
+        <v>-43523347.742739365</v>
+      </c>
+      <c r="F5">
+        <v>-342405481.3460045</v>
+      </c>
+      <c r="G5">
+        <v>-744528146.6539955</v>
       </c>
     </row>
     <row r="6">
@@ -5221,50 +5738,56 @@
         <v xml:space="preserve">    Amortisman ve İtfa Gideri İle İlgili Düzeltmeler</v>
       </c>
       <c r="B6">
-        <v>1843955</v>
+        <v>459464.8352048495</v>
       </c>
       <c r="C6">
-        <v>1108786680.3470607</v>
+        <v>448966.1647951505</v>
       </c>
       <c r="D6">
-        <v>2194826</v>
+        <v>156026161.16482663</v>
+      </c>
+      <c r="E6">
+        <v>-154903971.4948474</v>
       </c>
       <c r="F6">
-        <v>-1086002733.3782675</v>
+        <v>524479.82213958</v>
       </c>
       <c r="G6">
-        <v>3747590.2227416085</v>
+        <v>524770.17786042</v>
+      </c>
+      <c r="H6">
+        <v>1459560871.1840827</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
         <v xml:space="preserve">    Değer Düşüklüğü (İptali) İle İlgili Düzeltmeler</v>
       </c>
-      <c r="F7">
-        <v>2352681.237908423</v>
-      </c>
-      <c r="G7">
-        <v>2199489.8550287774</v>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
         <v xml:space="preserve">    Karşılıklar İle İlgili Düzeltmeler</v>
       </c>
       <c r="B8">
-        <v>-176200</v>
+        <v>-168609.09326719667</v>
       </c>
       <c r="C8">
-        <v>217671.30186028837</v>
+        <v>154859.09326719667</v>
       </c>
       <c r="D8">
-        <v>-7353</v>
+        <v>208949.52460271356</v>
+      </c>
+      <c r="E8">
+        <v>-13873.478525311744</v>
       </c>
       <c r="F8">
-        <v>365133.7137609066</v>
+        <v>177234.95983438252</v>
       </c>
       <c r="G8">
-        <v>176353.02502064017</v>
+        <v>-579803.9598343825</v>
+      </c>
+      <c r="H8">
+        <v>672771.9984297883</v>
       </c>
     </row>
     <row r="9">
@@ -5287,19 +5810,25 @@
         <v xml:space="preserve">    Faiz (Gelirleri) ve Giderleri İle İlgili Düzeltmeler</v>
       </c>
       <c r="B12">
-        <v>-2520607</v>
+        <v>13299537.379715212</v>
       </c>
       <c r="C12">
-        <v>32977432.397796996</v>
+        <v>8261648.620284789</v>
       </c>
       <c r="D12">
-        <v>2829808</v>
+        <v>-38761630.51123827</v>
+      </c>
+      <c r="E12">
+        <v>15856299.08383771</v>
       </c>
       <c r="F12">
-        <v>3282402.8065614956</v>
+        <v>16979203.741761792</v>
       </c>
       <c r="G12">
-        <v>290657.4769364639</v>
+        <v>2957863.258238206</v>
+      </c>
+      <c r="H12">
+        <v>3040827.2249119417</v>
       </c>
     </row>
     <row r="13">
@@ -5331,17 +5860,14 @@
       <c r="A18" t="str">
         <v xml:space="preserve">    Gerçeğe Uygun Değer Kayıpları (Kazançları) İle İlgili Düzeltmeler</v>
       </c>
-      <c r="B18">
-        <v>-592570032</v>
-      </c>
-      <c r="C18">
-        <v>911162799.5463438</v>
-      </c>
       <c r="D18">
-        <v>-1633280487</v>
-      </c>
-      <c r="F18">
-        <v>-1402663028.8492703</v>
+        <v>-1369575453.5549836</v>
+      </c>
+      <c r="E18">
+        <v>2482513984.398976</v>
+      </c>
+      <c r="H18">
+        <v>401218911.5298269</v>
       </c>
     </row>
     <row r="19">
@@ -5354,31 +5880,31 @@
         <v xml:space="preserve">    Vergi (Geliri) Gideri İle İlgili Düzeltmeler</v>
       </c>
       <c r="B20">
-        <v>56755381</v>
+        <v>723349212.5717865</v>
       </c>
       <c r="C20">
-        <v>-843787764.3026859</v>
+        <v>-31954703.571786575</v>
       </c>
       <c r="D20">
-        <v>681483221</v>
+        <v>1014909208.5290995</v>
+      </c>
+      <c r="E20">
+        <v>-1637400796.3583136</v>
       </c>
       <c r="F20">
-        <v>311764035.982487</v>
+        <v>1433196444.4548018</v>
       </c>
       <c r="G20">
-        <v>1121156.0107596177</v>
+        <v>-743869773.4548018</v>
+      </c>
+      <c r="H20">
+        <v>-45569550.571932435</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
         <v xml:space="preserve">    Nakit Dışı Kalemlere İlişkin Diğer Düzeltmeler</v>
       </c>
-      <c r="F21">
-        <v>-1103958.2697150765</v>
-      </c>
-      <c r="G21">
-        <v>-40066.14500389045</v>
-      </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
@@ -5415,19 +5941,25 @@
         <v xml:space="preserve">    İşletme Sermayesinde Gerçekleşen Değişimler</v>
       </c>
       <c r="B28">
-        <v>532314044</v>
+        <v>-207711787.11531934</v>
       </c>
       <c r="C28">
-        <v>-35835768.885724716</v>
+        <v>-204821902.88468066</v>
       </c>
       <c r="D28">
-        <v>108938356</v>
+        <v>745207133.2818067</v>
+      </c>
+      <c r="E28">
+        <v>-9567332.800286308</v>
       </c>
       <c r="F28">
-        <v>-24492001.157984924</v>
+        <v>-104699154.82664208</v>
       </c>
       <c r="G28">
-        <v>-10801548.42941655</v>
+        <v>-4088129.17335792</v>
+      </c>
+      <c r="H28">
+        <v>76154449.13747951</v>
       </c>
     </row>
     <row r="29">
@@ -5435,10 +5967,16 @@
         <v xml:space="preserve">    Finansal Yatırımlardaki Azalış (Artış)</v>
       </c>
       <c r="B29">
-        <v>23234823</v>
-      </c>
-      <c r="D29">
-        <v>-23353528</v>
+        <v>87400641.40398115</v>
+      </c>
+      <c r="C29">
+        <v>-229798321.40398115</v>
+      </c>
+      <c r="F29">
+        <v>1994493.7399101034</v>
+      </c>
+      <c r="G29">
+        <v>25407785.260089897</v>
       </c>
     </row>
     <row r="30">
@@ -5451,47 +5989,56 @@
         <v xml:space="preserve">    Ticari Alacaklardaki Azalış (Artış) ile İlgili Düzeltmeler</v>
       </c>
       <c r="B31">
-        <v>-430774</v>
+        <v>-53437917.189666234</v>
       </c>
       <c r="C31">
-        <v>-28328495.96205772</v>
+        <v>4248602.189666231</v>
       </c>
       <c r="D31">
-        <v>-5664263</v>
+        <v>24475516.63686282</v>
+      </c>
+      <c r="E31">
+        <v>-32533014.69323656</v>
       </c>
       <c r="F31">
-        <v>-557092.0190958714</v>
+        <v>3654261.2825998124</v>
       </c>
       <c r="G31">
-        <v>341795.7112900256</v>
+        <v>3895957.7174001876</v>
+      </c>
+      <c r="H31">
+        <v>-8376814.450643982</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
         <v xml:space="preserve">    Finans Sektörü Faaliyetlerinden Alacaklarda Azalış (Artış)</v>
       </c>
-      <c r="F32">
-        <v>-1145.820368137514</v>
-      </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
         <v xml:space="preserve">    Faaliyetlerle İlgili Diğer Alacaklardaki Azalış (Artış) ile İlgili Düzeltmeler</v>
       </c>
       <c r="B33">
-        <v>-32788</v>
+        <v>-3405622.6670735553</v>
       </c>
       <c r="C33">
-        <v>-9681609.488313802</v>
+        <v>-719729.3329264446</v>
       </c>
       <c r="D33">
-        <v>-7385494</v>
+        <v>-1340178.5034303083</v>
+      </c>
+      <c r="E33">
+        <v>1782406.3855346548</v>
       </c>
       <c r="F33">
-        <v>-8734556.316192586</v>
+        <v>-2441406.9152490217</v>
       </c>
       <c r="G33">
-        <v>1129961.5046269624</v>
+        <v>1960567.9152490215</v>
+      </c>
+      <c r="H33">
+        <v>-12702621.59356692</v>
       </c>
     </row>
     <row r="34">
@@ -5513,20 +6060,20 @@
       <c r="A37" t="str">
         <v xml:space="preserve">    Stoklardaki Azalışlar (Artışlar) İle İlgili Düzeltmeler</v>
       </c>
-      <c r="B37">
-        <v>-54253036</v>
-      </c>
-      <c r="C37">
-        <v>20108655.37551452</v>
-      </c>
       <c r="D37">
-        <v>7280493</v>
+        <v>-67436055.68036431</v>
+      </c>
+      <c r="E37">
+        <v>7706048.622991667</v>
       </c>
       <c r="F37">
-        <v>-19024186.016218126</v>
+        <v>-5000893.437277914</v>
       </c>
       <c r="G37">
-        <v>-221052.54200497738</v>
+        <v>842576.4372779138</v>
+      </c>
+      <c r="H37">
+        <v>20132201.993790627</v>
       </c>
     </row>
     <row r="38">
@@ -5539,19 +6086,25 @@
         <v xml:space="preserve">    Peşin Ödenmiş Giderlerdeki Azalış (Artış)</v>
       </c>
       <c r="B39">
-        <v>-5535746</v>
+        <v>-144823518.2027315</v>
       </c>
       <c r="C39">
-        <v>64994146.39725055</v>
+        <v>-21330759.797268502</v>
       </c>
       <c r="D39">
-        <v>34358390</v>
+        <v>-5505232.705353034</v>
+      </c>
+      <c r="E39">
+        <v>-1015395.5665266898</v>
       </c>
       <c r="F39">
-        <v>-27342827.279165007</v>
+        <v>11544.637976693546</v>
       </c>
       <c r="G39">
-        <v>-5155621.877091488</v>
+        <v>-9805.637976693546</v>
+      </c>
+      <c r="H39">
+        <v>77550702.10366237</v>
       </c>
     </row>
     <row r="40">
@@ -5559,19 +6112,25 @@
         <v xml:space="preserve">    Ticari Borçlardaki Artış (Azalış) ile İlgili Düzeltmeler</v>
       </c>
       <c r="B40">
-        <v>16760080</v>
+        <v>1089670.0477585793</v>
       </c>
       <c r="C40">
-        <v>1709672.3554326706</v>
+        <v>-19590709.04775858</v>
       </c>
       <c r="D40">
-        <v>-6568573</v>
+        <v>3196225.416664023</v>
+      </c>
+      <c r="E40">
+        <v>2064493.9941138402</v>
       </c>
       <c r="F40">
-        <v>5871021.815738205</v>
+        <v>12827627.909704298</v>
       </c>
       <c r="G40">
-        <v>-6870624.860668444</v>
+        <v>1648307.0902957015</v>
+      </c>
+      <c r="H40">
+        <v>-14527120.439808898</v>
       </c>
     </row>
     <row r="41">
@@ -5584,19 +6143,25 @@
         <v xml:space="preserve">    Çalışanlara Sağlanan Faydalar Kapsamında Borçlardaki Artış (Azalış)</v>
       </c>
       <c r="B42">
-        <v>174525</v>
+        <v>-209308.9560172135</v>
       </c>
       <c r="C42">
-        <v>162631.6882205499</v>
+        <v>185144.9560172135</v>
       </c>
       <c r="D42">
-        <v>113064</v>
+        <v>-24323.015455561515</v>
+      </c>
+      <c r="E42">
+        <v>178488.49095693184</v>
       </c>
       <c r="F42">
-        <v>-64482.13694679884</v>
+        <v>-343660.35844406404</v>
       </c>
       <c r="G42">
-        <v>-16270.02309620399</v>
+        <v>395015.35844406404</v>
+      </c>
+      <c r="H42">
+        <v>-38328.56819699478</v>
       </c>
     </row>
     <row r="43">
@@ -5609,19 +6174,25 @@
         <v xml:space="preserve">    Faaliyetler ile İlgili Diğer Borçlardaki Artış (Azalış) ile İlgili Düzeltmeler</v>
       </c>
       <c r="B44">
-        <v>550840052</v>
+        <v>-133520758.65585221</v>
       </c>
       <c r="C44">
-        <v>-129089368.12762754</v>
+        <v>1676299.6558522168</v>
       </c>
       <c r="D44">
-        <v>81744632</v>
+        <v>795259295.0885724</v>
+      </c>
+      <c r="E44">
+        <v>-1284302.047950536</v>
       </c>
       <c r="F44">
-        <v>25361266.614263397</v>
+        <v>-111239399.25830802</v>
       </c>
       <c r="G44">
-        <v>-9736.342472425324</v>
+        <v>-34066867.74169197</v>
+      </c>
+      <c r="H44">
+        <v>-5424949.185892448</v>
       </c>
     </row>
     <row r="45">
@@ -5639,26 +6210,47 @@
         <v xml:space="preserve">    Ertelenmiş Gelirlerdeki Artış (Azalış)</v>
       </c>
       <c r="B47">
-        <v>1556908</v>
+        <v>105346925.7588744</v>
+      </c>
+      <c r="C47">
+        <v>-5644328.758874401</v>
       </c>
       <c r="D47">
-        <v>28413635</v>
+        <v>-3380507.193932283</v>
+      </c>
+      <c r="E47">
+        <v>13537308.587267837</v>
+      </c>
+      <c r="F47">
+        <v>-4161722.4275539597</v>
+      </c>
+      <c r="G47">
+        <v>-4161665.5724460403</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
         <v xml:space="preserve">    İşletme Sermayesinde Gerçekleşen Diğer Artış (Azalış) ile İlgili Düzeltmeler</v>
       </c>
+      <c r="C48">
+        <v>66151898.65459277</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
         <v xml:space="preserve">    Faaliyetlerden Elde Edilen Nakit Akışları</v>
       </c>
       <c r="B49">
-        <v>114117683</v>
-      </c>
-      <c r="D49">
-        <v>104396279</v>
+        <v>-30738519.84723562</v>
+      </c>
+      <c r="C49">
+        <v>-279291372.1527644</v>
+      </c>
+      <c r="F49">
+        <v>-71676148.82335766</v>
+      </c>
+      <c r="G49">
+        <v>4035985.823357661</v>
       </c>
     </row>
     <row r="50">
@@ -5685,11 +6277,14 @@
       <c r="A54" t="str">
         <v xml:space="preserve">    Vergi İadeleri (Ödemeleri)</v>
       </c>
-      <c r="F54">
-        <v>2619.3161420994174</v>
+      <c r="B54">
+        <v>2133624.45205522</v>
+      </c>
+      <c r="C54">
+        <v>-2245374.45205522</v>
       </c>
       <c r="G54">
-        <v>8655.22234365441</v>
+        <v>-255088.9152179873</v>
       </c>
     </row>
     <row r="55">
@@ -5753,19 +6348,25 @@
         <v xml:space="preserve">    Yatırım Faaliyetlerinden Kaynaklanan Nakit Akışları</v>
       </c>
       <c r="B67">
-        <v>-55971204</v>
+        <v>-17522580.870547272</v>
       </c>
       <c r="C67">
-        <v>-148484140.75951675</v>
+        <v>-57157649.12945273</v>
       </c>
       <c r="D67">
-        <v>-108440453</v>
+        <v>-19929208.53844519</v>
+      </c>
+      <c r="E67">
+        <v>-5032263.53626731</v>
       </c>
       <c r="F67">
-        <v>-335285381.1913448</v>
+        <v>-40413782.79794607</v>
       </c>
       <c r="G67">
-        <v>-2951242.9797815406</v>
+        <v>-536382.2020539267</v>
+      </c>
+      <c r="H67">
+        <v>-128872355.66833538</v>
       </c>
     </row>
     <row r="68">
@@ -5818,33 +6419,36 @@
         <v xml:space="preserve">    Maddi ve Maddi Olmayan Duran Varlıkların Satışından Kaynaklanan Nakit Girişleri</v>
       </c>
       <c r="B77">
-        <v>2243435</v>
+        <v>-45918.350871793926</v>
       </c>
       <c r="C77">
-        <v>1444997.0091945282</v>
+        <v>1361483.350871794</v>
       </c>
       <c r="D77">
-        <v>445898</v>
+        <v>-1153980.4805666157</v>
+      </c>
+      <c r="H77">
+        <v>-2094220.3059709952</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
         <v xml:space="preserve">    Maddi ve Maddi Olmayan Duran Varlıkların Alımından Kaynaklanan Nakit Çıkışları</v>
       </c>
-      <c r="B78">
-        <v>-261422</v>
-      </c>
-      <c r="C78">
-        <v>-543722.0024976094</v>
-      </c>
       <c r="D78">
-        <v>-1499116</v>
+        <v>13407.572600488027</v>
+      </c>
+      <c r="E78">
+        <v>-97348.87339704571</v>
       </c>
       <c r="F78">
-        <v>-134965.74287097369</v>
+        <v>-81277.25798476234</v>
       </c>
       <c r="G78">
-        <v>-1674594.553435772</v>
+        <v>-142631.74201523766</v>
+      </c>
+      <c r="H78">
+        <v>-319028.6442586824</v>
       </c>
     </row>
     <row r="79">
@@ -5857,10 +6461,16 @@
         <v xml:space="preserve">    Yatırım Amaçlı Gayrimenkul Alımından Kaynaklanan Nakit Çıkışları</v>
       </c>
       <c r="B80">
-        <v>-57953217</v>
-      </c>
-      <c r="D80">
-        <v>-107387235</v>
+        <v>-17191681.51967548</v>
+      </c>
+      <c r="C80">
+        <v>-58519132.48032452</v>
+      </c>
+      <c r="F80">
+        <v>-40332505.53996131</v>
+      </c>
+      <c r="G80">
+        <v>-393750.46003868897</v>
       </c>
     </row>
     <row r="81">
@@ -5951,12 +6561,6 @@
     <row r="98">
       <c r="A98" t="str">
         <v xml:space="preserve">    Diğer Nakit Girişleri (Çıkışları)</v>
-      </c>
-      <c r="F98">
-        <v>-335150415.4484738</v>
-      </c>
-      <c r="G98">
-        <v>-1276648.4263457689</v>
       </c>
     </row>
     <row r="99">
@@ -5970,19 +6574,25 @@
         <v xml:space="preserve">    Finansman Faaliyetlerinden Nakit Akışları</v>
       </c>
       <c r="B101">
-        <v>-54478702</v>
+        <v>-21872788.466599822</v>
       </c>
       <c r="C101">
-        <v>113764794.60778329</v>
+        <v>421408696.4665998</v>
       </c>
       <c r="D101">
-        <v>-6729045</v>
+        <v>-202915237.65457335</v>
+      </c>
+      <c r="E101">
+        <v>-39624461.47169769</v>
       </c>
       <c r="F101">
-        <v>372666941.07779413</v>
+        <v>181638999.99492338</v>
       </c>
       <c r="G101">
-        <v>8726475.047585249</v>
+        <v>-3253368.9949233728</v>
+      </c>
+      <c r="H101">
+        <v>-4791854.627243149</v>
       </c>
     </row>
     <row r="102">
@@ -5999,11 +6609,20 @@
       <c r="A104" t="str">
         <v xml:space="preserve">    Pay ve Diğer Özkaynağa Dayalı Araçların İhracından Kaynaklanan Nakit Girişleri</v>
       </c>
+      <c r="B104">
+        <v>2538.332515180111</v>
+      </c>
+      <c r="C104">
+        <v>401843289.6674848</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
         <v xml:space="preserve">    Sermaye Avanslarından Nakit Girişleri</v>
       </c>
+      <c r="C105">
+        <v>45213162.121063225</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
@@ -6024,20 +6643,14 @@
       <c r="A109" t="str">
         <v xml:space="preserve">    Borçlanmadan Kaynaklanan Nakit Girişleri</v>
       </c>
-      <c r="B109">
-        <v>12549625</v>
-      </c>
-      <c r="C109">
-        <v>156936010.83301657</v>
-      </c>
       <c r="D109">
-        <v>2432337</v>
-      </c>
-      <c r="F109">
-        <v>58095008.62649901</v>
-      </c>
-      <c r="G109">
-        <v>6134348.65930352</v>
+        <v>-169872475.38253748</v>
+      </c>
+      <c r="E109">
+        <v>-13606838.04611811</v>
+      </c>
+      <c r="H109">
+        <v>156796.48295964766</v>
       </c>
     </row>
     <row r="110">
@@ -6045,19 +6658,25 @@
         <v xml:space="preserve">    Borç Ödemelerine İlişkin Nakit Çıkışları</v>
       </c>
       <c r="B110">
-        <v>-13651649</v>
+        <v>-5034175.295890076</v>
       </c>
       <c r="C110">
-        <v>-10639803.503703352</v>
+        <v>-16593355.704109924</v>
       </c>
       <c r="D110">
-        <v>-7470216</v>
+        <v>-8478834.792487184</v>
+      </c>
+      <c r="E110">
+        <v>-5594302.2025439385</v>
       </c>
       <c r="F110">
-        <v>-11259075.12854521</v>
+        <v>-1040476.4175300122</v>
       </c>
       <c r="G110">
-        <v>-3541081.668414894</v>
+        <v>-962555.5824699878</v>
+      </c>
+      <c r="H110">
+        <v>-4932088.374864792</v>
       </c>
     </row>
     <row r="111">
@@ -6100,19 +6719,25 @@
         <v xml:space="preserve">    Ödenen Faiz</v>
       </c>
       <c r="B118">
-        <v>-63066868</v>
+        <v>-18289895.529994257</v>
       </c>
       <c r="C118">
-        <v>-46390331.7980916</v>
+        <v>-21723094.470005743</v>
       </c>
       <c r="D118">
-        <v>-6025375</v>
+        <v>-23659426.335269243</v>
+      </c>
+      <c r="E118">
+        <v>-24798927.97782147</v>
       </c>
       <c r="F118">
-        <v>-2003142.3689393625</v>
+        <v>-23518316.587546617</v>
       </c>
       <c r="G118">
-        <v>-218610.6297450122</v>
+        <v>-2290813.4124533846</v>
+      </c>
+      <c r="H118">
+        <v>-4021153.0223797862</v>
       </c>
     </row>
     <row r="119">
@@ -6120,19 +6745,19 @@
         <v xml:space="preserve">    Alınan Faiz</v>
       </c>
       <c r="B119">
-        <v>9690190</v>
+        <v>4411906.147832539</v>
       </c>
       <c r="C119">
-        <v>16239102.594775513</v>
+        <v>12668694.852167461</v>
       </c>
       <c r="D119">
-        <v>6713829</v>
-      </c>
-      <c r="F119">
-        <v>33347.755632242624</v>
-      </c>
-      <c r="G119">
-        <v>62035.0069255944</v>
+        <v>-904501.1442794837</v>
+      </c>
+      <c r="E119">
+        <v>4375606.754785851</v>
+      </c>
+      <c r="H119">
+        <v>6807492.154647182</v>
       </c>
     </row>
     <row r="120">
@@ -6154,12 +6779,6 @@
       <c r="A123" t="str">
         <v xml:space="preserve">    Diğer Nakit Girişleri (Çıkışları)</v>
       </c>
-      <c r="D123">
-        <v>-2379620</v>
-      </c>
-      <c r="G123">
-        <v>6289783.67951604</v>
-      </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
@@ -6171,19 +6790,25 @@
         <v xml:space="preserve">    Yabancı Para Çevrim Farklarının Etkisinden Önce Nakit ve Nakit Benzerlerindeki Net Artış (Azalış)</v>
       </c>
       <c r="B125">
-        <v>3667777</v>
+        <v>-68000264.7323275</v>
       </c>
       <c r="C125">
-        <v>-24793675.299457714</v>
+        <v>82714300.7323275</v>
       </c>
       <c r="D125">
-        <v>-10773219</v>
+        <v>-7724723.303795857</v>
+      </c>
+      <c r="E125">
+        <v>-57751408.958069265</v>
       </c>
       <c r="F125">
-        <v>10578100.935002761</v>
+        <v>69804157.28883763</v>
       </c>
       <c r="G125">
-        <v>-1439656.505220924</v>
+        <v>-8854.288837625494</v>
+      </c>
+      <c r="H125">
+        <v>-41240902.705280565</v>
       </c>
     </row>
     <row r="126">
@@ -6196,19 +6821,25 @@
         <v xml:space="preserve">    Nakit ve Nakit Benzerlerindeki Net Artış (Azalış)</v>
       </c>
       <c r="B127">
-        <v>3667777</v>
+        <v>-68000264.7323275</v>
       </c>
       <c r="C127">
-        <v>-24793675.299457714</v>
+        <v>82714300.7323275</v>
       </c>
       <c r="D127">
-        <v>-10773219</v>
+        <v>-7724723.303795857</v>
+      </c>
+      <c r="E127">
+        <v>-57751408.958069265</v>
       </c>
       <c r="F127">
-        <v>10578100.935002761</v>
+        <v>69804157.28883763</v>
       </c>
       <c r="G127">
-        <v>-1439656.505220924</v>
+        <v>-8854.288837625494</v>
+      </c>
+      <c r="H127">
+        <v>-41240902.705280565</v>
       </c>
     </row>
     <row r="128">
@@ -6216,10 +6847,16 @@
         <v xml:space="preserve">    Dönem Başı Nakit ve Nakit Benzerleri</v>
       </c>
       <c r="B128">
-        <v>44711</v>
-      </c>
-      <c r="D128">
-        <v>10817930</v>
+        <v>27.629530301317573</v>
+      </c>
+      <c r="C128">
+        <v>4371740.370469699</v>
+      </c>
+      <c r="F128">
+        <v>1.4064767737072543</v>
+      </c>
+      <c r="G128">
+        <v>52650.59352322629</v>
       </c>
     </row>
     <row r="129">
@@ -6227,15 +6864,1318 @@
         <v xml:space="preserve">    Dönem Sonu Nakit ve Nakit Benzerleri</v>
       </c>
       <c r="B129">
-        <v>3712488</v>
-      </c>
-      <c r="D129">
-        <v>44711</v>
+        <v>-68000237.1027972</v>
+      </c>
+      <c r="C129">
+        <v>87086041.1027972</v>
+      </c>
+      <c r="F129">
+        <v>69804158.69531439</v>
+      </c>
+      <c r="G129">
+        <v>43796.30468560079</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G129"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K129"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:K129"/>
+  <cols>
+    <col min="1" max="1" customWidth="1" width="40" level="2" outlineLevel="2"/>
+    <col min="2" max="2" customWidth="1" width="20"/>
+    <col min="3" max="3" customWidth="1" width="20"/>
+    <col min="4" max="4" customWidth="1" width="20"/>
+    <col min="5" max="5" customWidth="1" width="20"/>
+    <col min="6" max="6" customWidth="1" width="20"/>
+    <col min="7" max="7" customWidth="1" width="20"/>
+    <col min="8" max="8" customWidth="1" width="20"/>
+    <col min="9" max="9" customWidth="1" width="20"/>
+    <col min="10" max="10" customWidth="1" width="20"/>
+    <col min="11" max="11" customWidth="1" width="20"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Kalem</v>
+      </c>
+      <c r="B1" t="str">
+        <v>2026/6</v>
+      </c>
+      <c r="C1" t="str">
+        <v>2026/3</v>
+      </c>
+      <c r="D1" t="str">
+        <v>2025/12</v>
+      </c>
+      <c r="E1" t="str">
+        <v>2025/9</v>
+      </c>
+      <c r="F1" t="str">
+        <v>2025/6</v>
+      </c>
+      <c r="G1" t="str">
+        <v>2025/3</v>
+      </c>
+      <c r="H1" t="str">
+        <v>2024/12</v>
+      </c>
+      <c r="I1" t="str">
+        <v>2024/9</v>
+      </c>
+      <c r="J1" t="str">
+        <v>2023/12</v>
+      </c>
+      <c r="K1" t="str">
+        <v>2022/12</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v xml:space="preserve">    İşletme Faaliyetlerinden Nakit Akışları</v>
+      </c>
+      <c r="B3">
+        <v>-108116603.06088158</v>
+      </c>
+      <c r="C3">
+        <v>-150932767.57384086</v>
+      </c>
+      <c r="D3">
+        <v>134384875.93911842</v>
+      </c>
+      <c r="E3">
+        <v>11688460.6401937</v>
+      </c>
+      <c r="H3">
+        <v>122936959.75163282</v>
+      </c>
+      <c r="J3">
+        <v>-31563727.997609306</v>
+      </c>
+      <c r="K3">
+        <v>-8496245.983196823</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v xml:space="preserve">    Dönem Karı (Zararı)</v>
+      </c>
+      <c r="B4">
+        <v>283959099.5355122</v>
+      </c>
+      <c r="C4">
+        <v>-618090568.6405432</v>
+      </c>
+      <c r="D4">
+        <v>165507814.53551215</v>
+      </c>
+      <c r="E4">
+        <v>-111646194.87559286</v>
+      </c>
+      <c r="H4">
+        <v>1132237955.8877137</v>
+      </c>
+      <c r="J4">
+        <v>1276150740.1906705</v>
+      </c>
+      <c r="K4">
+        <v>-199703.82940229628</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v xml:space="preserve">    Dönem Net Karı (Zararı) Mutabakatı İle İlgili Düzeltmeler</v>
+      </c>
+      <c r="B5">
+        <v>-715070063.0779142</v>
+      </c>
+      <c r="C5">
+        <v>43029343.83334191</v>
+      </c>
+      <c r="D5">
+        <v>-657975455.0779142</v>
+      </c>
+      <c r="H5">
+        <v>-1137586701.4817767</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v xml:space="preserve">    Amortisman ve İtfa Gideri İle İlgili Düzeltmeler</v>
+      </c>
+      <c r="B6">
+        <v>2030620.6699792542</v>
+      </c>
+      <c r="C6">
+        <v>2095635.6569139848</v>
+      </c>
+      <c r="D6">
+        <v>2171439.6699792542</v>
+      </c>
+      <c r="E6">
+        <v>1305706149.6892354</v>
+      </c>
+      <c r="H6">
+        <v>2584625.02886561</v>
+      </c>
+      <c r="J6">
+        <v>-1278875795.2138054</v>
+      </c>
+      <c r="K6">
+        <v>4413158.714007401</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v xml:space="preserve">    Değer Düşüklüğü (İptali) İle İlgili Düzeltmeler</v>
+      </c>
+      <c r="J7">
+        <v>2770515.208240032</v>
+      </c>
+      <c r="K7">
+        <v>2590117.1801515794</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v xml:space="preserve">    Karşılıklar İle İlgili Düzeltmeler</v>
+      </c>
+      <c r="B8">
+        <v>181326.0460774018</v>
+      </c>
+      <c r="C8">
+        <v>527170.099178981</v>
+      </c>
+      <c r="D8">
+        <v>-207492.9539225982</v>
+      </c>
+      <c r="E8">
+        <v>256329.51990447653</v>
+      </c>
+      <c r="H8">
+        <v>-8658.885869426018</v>
+      </c>
+      <c r="J8">
+        <v>429981.11716787145</v>
+      </c>
+      <c r="K8">
+        <v>207673.15604267022</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v xml:space="preserve">    Kar Payı (Geliri) Gideri ile İlgili Düzeltmeler</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v xml:space="preserve">    Katılım (Kar) Payı ve Diğer Finansal Araçlardan (Gelirler) Giderler ile İlgili Düzeltmeler</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v xml:space="preserve">    Pazarlıklı Satın Alım Sonucu Oluşan Kazanç ile İlgili Düzeltmeler</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v xml:space="preserve">    Faiz (Gelirleri) ve Giderleri İle İlgili Düzeltmeler</v>
+      </c>
+      <c r="B12">
+        <v>-1344145.4274005592</v>
+      </c>
+      <c r="C12">
+        <v>2335520.9346460244</v>
+      </c>
+      <c r="D12">
+        <v>-2968264.4274005587</v>
+      </c>
+      <c r="E12">
+        <v>38834193.30874965</v>
+      </c>
+      <c r="H12">
+        <v>3332379.233562995</v>
+      </c>
+      <c r="J12">
+        <v>3865354.4511763416</v>
+      </c>
+      <c r="K12">
+        <v>342277.97088102356</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v xml:space="preserve">    Devlet Teşviklerinden Elde Edilen Gelirler ile İlgili Düzeltmeler</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v xml:space="preserve">    Takas İşlemlerinden Kaynaklanan Kayıplar (Kazançlar) ile İlgili Düzeltmeler</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v xml:space="preserve">    Gerçekleşmemiş Yabancı Para Çevrim Farkları İle İlgili Düzeltmeler</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v xml:space="preserve">    Pay Bazlı Ödemeler İle İlgili Düzeltmeler</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v xml:space="preserve">    Hibe Krediler ile İlgili Düzeltmeler</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v xml:space="preserve">    Gerçeğe Uygun Değer Kayıpları (Kazançları) İle İlgili Düzeltmeler</v>
+      </c>
+      <c r="B18">
+        <v>-716366846.1560075</v>
+      </c>
+      <c r="D18">
+        <v>-697809911.1560075</v>
+      </c>
+      <c r="E18">
+        <v>1072984453.9288028</v>
+      </c>
+      <c r="H18">
+        <v>-1923349562.041826</v>
+      </c>
+      <c r="J18">
+        <v>-1651774660.6921322</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v xml:space="preserve">    Özkaynak Yöntemiyle Değerlenen Yatırımların Dağıtılmamış Karları ile İlgili Düzeltmeler</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v xml:space="preserve">    Vergi (Geliri) Gideri İle İlgili Düzeltmeler</v>
+      </c>
+      <c r="B20">
+        <v>68902921.17078602</v>
+      </c>
+      <c r="C20">
+        <v>778750153.0538013</v>
+      </c>
+      <c r="D20">
+        <v>66835083.17078606</v>
+      </c>
+      <c r="E20">
+        <v>-993643675.9302459</v>
+      </c>
+      <c r="H20">
+        <v>802513998.717235</v>
+      </c>
+      <c r="J20">
+        <v>367133034.9196221</v>
+      </c>
+      <c r="K20">
+        <v>1320272.2615243436</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v xml:space="preserve">    Nakit Dışı Kalemlere İlişkin Diğer Düzeltmeler</v>
+      </c>
+      <c r="J21">
+        <v>-1300020.2178800318</v>
+      </c>
+      <c r="K21">
+        <v>-47181.85459221554</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v xml:space="preserve">    Duran Varlıkların Elden Çıkarılmasından Kaynaklanan Kayıplar (Kazançlar) İle İlgili Düzeltmeler</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v xml:space="preserve">    Satış Amaçlı veya Ortaklara Dağıtılmak Üzere Elde Tutulan Duran Varlıkların Elden Çıkarılmasından Kaynaklanan Kayıplar (Kazançlar) ile İlgili Düzeltmeler</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v xml:space="preserve">    İştirak, İş ortaklığı ve Finansal Yatırımların Elden Çıkarılmasından veya Paylarındaki Değişim Sebebi ile Oluşan Kayıplar (Kazançlar) ile İlgili Düzeltmeler</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v xml:space="preserve">    Bağlı Ortaklıkların veya Müşterek Faaliyetlerin Elden Çıkarılmasından Kaynaklanan Kayıplar (Kazançlar) ile İlgili Düzeltmeler</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v xml:space="preserve">    Yatırım ya da Finansman Faaliyetlerinden Kaynaklanan Nakit Akışlarına Neden Olan Diğer Kalemlere İlişkin Düzeltmeler</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v xml:space="preserve">    Kar (Zarar) Mutabakatı İle İlgili Diğer Düzeltmeler</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v xml:space="preserve">    İşletme Sermayesinde Gerçekleşen Değişimler</v>
+      </c>
+      <c r="B28">
+        <v>323106110.4815204</v>
+      </c>
+      <c r="C28">
+        <v>426118742.77019775</v>
+      </c>
+      <c r="D28">
+        <v>626852516.4815204</v>
+      </c>
+      <c r="E28">
+        <v>-42200167.662806794</v>
+      </c>
+      <c r="H28">
+        <v>128285705.3456958</v>
+      </c>
+      <c r="J28">
+        <v>-28841757.47869459</v>
+      </c>
+      <c r="K28">
+        <v>-12719893.24947583</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v xml:space="preserve">    Finansal Yatırımlardaki Azalış (Artış)</v>
+      </c>
+      <c r="B29">
+        <v>-142438653.33519453</v>
+      </c>
+      <c r="C29">
+        <v>-227844800.99926558</v>
+      </c>
+      <c r="D29">
+        <v>27361305.664805476</v>
+      </c>
+      <c r="H29">
+        <v>-27501092.560920015</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
+        <v xml:space="preserve">    Türkiye Cumhuriyet Merkez Bankası Hesabındaki Azalış (Artış)</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v xml:space="preserve">    Ticari Alacaklardaki Azalış (Artış) ile İlgili Düzeltmeler</v>
+      </c>
+      <c r="B31">
+        <v>-57246813.056373745</v>
+      </c>
+      <c r="C31">
+        <v>-154634.58410769794</v>
+      </c>
+      <c r="D31">
+        <v>-507279.0563737418</v>
+      </c>
+      <c r="E31">
+        <v>-33359610.143880542</v>
+      </c>
+      <c r="H31">
+        <v>-6670230.769945958</v>
+      </c>
+      <c r="J31">
+        <v>-656031.0365999253</v>
+      </c>
+      <c r="K31">
+        <v>402498.3074554084</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v xml:space="preserve">    Finans Sektörü Faaliyetlerinden Alacaklarda Azalış (Artış)</v>
+      </c>
+      <c r="J32">
+        <v>-1349.3169855251515</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="str">
+        <v xml:space="preserve">    Faaliyetlerle İlgili Diğer Alacaklardaki Azalış (Artış) ile İlgili Düzeltmeler</v>
+      </c>
+      <c r="B33">
+        <v>-3683124.1178956535</v>
+      </c>
+      <c r="C33">
+        <v>-2718908.3660711194</v>
+      </c>
+      <c r="D33">
+        <v>-38611.117895653515</v>
+      </c>
+      <c r="E33">
+        <v>-11401054.208032265</v>
+      </c>
+      <c r="H33">
+        <v>-8697150.773198782</v>
+      </c>
+      <c r="J33">
+        <v>-10285805.285187783</v>
+      </c>
+      <c r="K33">
+        <v>1330641.6028029057</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="str">
+        <v xml:space="preserve">    Müşteri Sözleşmelerinden Doğan Varlıklardaki Azalış (Artış) İle İlgili Düzeltmeler</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="str">
+        <v xml:space="preserve">    İmtiyaz Sözleşmelerine İlişkin Finansal Varlıklardaki Azalış (Artış)</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="str">
+        <v xml:space="preserve">    Türev Varlıklardaki Azalış (Artış)</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="str">
+        <v xml:space="preserve">    Stoklardaki Azalışlar (Artışlar) İle İlgili Düzeltmeler</v>
+      </c>
+      <c r="D37">
+        <v>-63888324.057372645</v>
+      </c>
+      <c r="E37">
+        <v>23679933.616782293</v>
+      </c>
+      <c r="H37">
+        <v>8573501.69456753</v>
+      </c>
+      <c r="J37">
+        <v>-22402863.521442026</v>
+      </c>
+      <c r="K37">
+        <v>-260311.26511187272</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="str">
+        <v xml:space="preserve">    Canlı Varlıklardaki Azalış (Artış)</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="str">
+        <v xml:space="preserve">    Peşin Ödenmiş Giderlerdeki Azalış (Artış)</v>
+      </c>
+      <c r="B39">
+        <v>-172674906.27187973</v>
+      </c>
+      <c r="C39">
+        <v>-27839843.431171533</v>
+      </c>
+      <c r="D39">
+        <v>-6518889.271879723</v>
+      </c>
+      <c r="E39">
+        <v>76537045.53713568</v>
+      </c>
+      <c r="H39">
+        <v>40460407.679481596</v>
+      </c>
+      <c r="J39">
+        <v>-32198887.631948616</v>
+      </c>
+      <c r="K39">
+        <v>-6071255.46302885</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="str">
+        <v xml:space="preserve">    Ticari Borçlardaki Artış (Azalış) ile İlgili Düzeltmeler</v>
+      </c>
+      <c r="B40">
+        <v>-13240319.589222137</v>
+      </c>
+      <c r="C40">
+        <v>-1502361.7272764184</v>
+      </c>
+      <c r="D40">
+        <v>19736654.410777863</v>
+      </c>
+      <c r="E40">
+        <v>2013308.5543049425</v>
+      </c>
+      <c r="H40">
+        <v>-7735145.373588096</v>
+      </c>
+      <c r="J40">
+        <v>6913709.756478638</v>
+      </c>
+      <c r="K40">
+        <v>-8090841.360012117</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="str">
+        <v xml:space="preserve">    Finans Sektörü Faaliyetlerinden Borçlardaki Artış (Azalış)</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="str">
+        <v xml:space="preserve">    Çalışanlara Sağlanan Faydalar Kapsamında Borçlardaki Artış (Azalış)</v>
+      </c>
+      <c r="B42">
+        <v>130001.47550137033</v>
+      </c>
+      <c r="C42">
+        <v>-4349.92692548022</v>
+      </c>
+      <c r="D42">
+        <v>205520.47550137033</v>
+      </c>
+      <c r="E42">
+        <v>191514.92275993706</v>
+      </c>
+      <c r="H42">
+        <v>133144.0598314679</v>
+      </c>
+      <c r="J42">
+        <v>-75934.10369087853</v>
+      </c>
+      <c r="K42">
+        <v>-19159.563862771072</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="str">
+        <v xml:space="preserve">    Müşteri Sözleşmelerinden Doğan Yükümlülüklerdeki Artış (Azalış) İle İlgili Düzeltmeler</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="str">
+        <v xml:space="preserve">    Faaliyetler ile İlgili Diğer Borçlardaki Artış (Azalış) ile İlgili Düzeltmeler</v>
+      </c>
+      <c r="B44">
+        <v>662130534.0406219</v>
+      </c>
+      <c r="C44">
+        <v>684411893.438166</v>
+      </c>
+      <c r="D44">
+        <v>648668726.0406219</v>
+      </c>
+      <c r="E44">
+        <v>-152015518.23384297</v>
+      </c>
+      <c r="H44">
+        <v>96262401.59475452</v>
+      </c>
+      <c r="J44">
+        <v>29865403.660681516</v>
+      </c>
+      <c r="K44">
+        <v>-11465.50771853339</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="str">
+        <v xml:space="preserve">    Türev Yükümlülüklerdeki Artış (Azalış)</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="str">
+        <v xml:space="preserve">    Devlet Teşvik ve Yardımlarındaki Artış (Azalış)</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="str">
+        <v xml:space="preserve">    Ertelenmiş Gelirlerdeki Artış (Azalış)</v>
+      </c>
+      <c r="B47">
+        <v>109859398.39333555</v>
+      </c>
+      <c r="C47">
+        <v>350750.20690719225</v>
+      </c>
+      <c r="D47">
+        <v>1833413.3933355534</v>
+      </c>
+      <c r="H47">
+        <v>33459869.794713527</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="str">
+        <v xml:space="preserve">    İşletme Sermayesinde Gerçekleşen Diğer Artış (Azalış) ile İlgili Düzeltmeler</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="str">
+        <v xml:space="preserve">    Faaliyetlerden Elde Edilen Nakit Akışları</v>
+      </c>
+      <c r="B49">
+        <v>-108004853.06088158</v>
+      </c>
+      <c r="C49">
+        <v>-148942482.03700364</v>
+      </c>
+      <c r="D49">
+        <v>134384875.93911842</v>
+      </c>
+      <c r="H49">
+        <v>122936959.75163282</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="str">
+        <v xml:space="preserve">    Ödenen Temettüler</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="str">
+        <v xml:space="preserve">    Alınan Temettüler</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="str">
+        <v xml:space="preserve">    Ödenen Faiz</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="str">
+        <v xml:space="preserve">    Alınan Faiz</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="str">
+        <v xml:space="preserve">    Vergi İadeleri (Ödemeleri)</v>
+      </c>
+      <c r="J54">
+        <v>3084.5042200984794</v>
+      </c>
+      <c r="K54">
+        <v>10192.381673903104</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="str">
+        <v xml:space="preserve">    Katılım (Kar) Payı ve Diğer Finansal Araçlardan Nakit Çıkışları</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="str">
+        <v xml:space="preserve">    Katılım (Kar) Payı ve Diğer Finansal Araçlardan Nakit Girişleri</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="str">
+        <v xml:space="preserve">    Kira Ödemeleri</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="str">
+        <v xml:space="preserve">    Alınan Kira</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="str">
+        <v xml:space="preserve">    Başka İşletmelerin veya Fonların Paylarının veya Borçlanma Araçlarının Edinimi İçin Yapılan Nakit Çıkışları</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="str">
+        <v xml:space="preserve">    Başka İşletmelerin veya Fonların Paylarının veya Borçlanma Araçlarının Satılması Sonucu Elde Edilen Nakit Girişleri</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="str">
+        <v xml:space="preserve">    İştirakler, İş Ortaklıkları ve/veya Müşterek Faaliyetlerin Sermaye Artırımına Katılımdan Kaynaklanan Nakit Çıkışları</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="str">
+        <v xml:space="preserve">    Çalışanlara Sağlanan Faydalara İlişkin Karşılıklar Kapsamında Yapılan Ödemeler</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="str">
+        <v xml:space="preserve">    Diğer Karşılıklara İlişkin Ödemeler</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="str">
+        <v xml:space="preserve">    Diğer Nakit Girişleri (Çıkışları)</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="str">
+        <v xml:space="preserve">    Durdurulan Faaliyetlere İlişkin Net Nakit Akışları</v>
+      </c>
+    </row>
+    <row r="66"/>
+    <row r="67">
+      <c r="A67" t="str">
+        <v xml:space="preserve">    Yatırım Faaliyetlerinden Kaynaklanan Nakit Akışları</v>
+      </c>
+      <c r="B67">
+        <v>-99641702.0747125</v>
+      </c>
+      <c r="C67">
+        <v>-122532904.0021113</v>
+      </c>
+      <c r="D67">
+        <v>-65911637.0747125</v>
+      </c>
+      <c r="E67">
+        <v>-174854784.2046027</v>
+      </c>
+      <c r="H67">
+        <v>-127699375.24219453</v>
+      </c>
+      <c r="J67">
+        <v>-394831748.8675169</v>
+      </c>
+      <c r="K67">
+        <v>-3475380.9512951337</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="str">
+        <v xml:space="preserve">    Bağlı Ortaklıkların Kontrolünün Kaybı Sonucunu Doğuracak Satışlara İlişkin Nakit Girişleri</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="str">
+        <v xml:space="preserve">    Bağlı Ortaklıkların Kontrolünün Kaybı Sonucunu Doğurmayan Satışlara İlişkin Nakit Girişleri</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="str">
+        <v xml:space="preserve">    Bağlı Ortaklıkların Kontrolünün Elde Edilmesine Yönelik Alışlara İlişkin Nakit Çıkışları</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="str">
+        <v xml:space="preserve">    Bağlı Ortaklıklarda İlave Pay Alımlarına ilişkin Nakit Çıkışları</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="str">
+        <v xml:space="preserve">    İştiraklerin ve/veya İş Ortaklıklarının Pay Satışı veya Sermaye Azaltımı Sebebiyle Oluşan Nakit Girişleri</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="str">
+        <v xml:space="preserve">    İştiraklar ve/veya İş Ortaklıkları Pay Alımı veya Sermaye Artırımı Sebebiyle Oluşan Nakit Çıkışları</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="str">
+        <v xml:space="preserve">    İştirakler ve/veya İş Ortaklıkları Sermaye Avansı Ödemelerinden Nakit Çıkışları</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="str">
+        <v xml:space="preserve">    Başka İşletmelerin veya Fonların Paylarının veya Borçlanma Araçlarının Satılması Sonucu Elde Edilen Nakit Girişleri</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="str">
+        <v xml:space="preserve">    Başka İşletmelerin veya Fonların Paylarının veya Borçlanma Araçlarının Edinimi İçin Yapılan Nakit Çıkışları</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="str">
+        <v xml:space="preserve">    Maddi ve Maddi Olmayan Duran Varlıkların Satışından Kaynaklanan Nakit Girişleri</v>
+      </c>
+      <c r="D77">
+        <v>2641866.941449172</v>
+      </c>
+      <c r="E77">
+        <v>1701627.1160447923</v>
+      </c>
+      <c r="H77">
+        <v>525089.0645186078</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="str">
+        <v xml:space="preserve">    Maddi ve Maddi Olmayan Duran Varlıkların Alımından Kaynaklanan Nakit Çıkışları</v>
+      </c>
+      <c r="B78">
+        <v>-368922.3007965577</v>
+      </c>
+      <c r="D78">
+        <v>-307850.3007965577</v>
+      </c>
+      <c r="E78">
+        <v>-640286.5176557282</v>
+      </c>
+      <c r="H78">
+        <v>-1765357.5886074333</v>
+      </c>
+      <c r="J78">
+        <v>-158935.53159282735</v>
+      </c>
+      <c r="K78">
+        <v>-1972000.967735996</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="str">
+        <v xml:space="preserve">    Yatırım Amaçlı Gayrimenkul Satımından Kaynaklanan Nakit Girişleri</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="str">
+        <v xml:space="preserve">    Yatırım Amaçlı Gayrimenkul Alımından Kaynaklanan Nakit Çıkışları</v>
+      </c>
+      <c r="B80">
+        <v>-103230211.71536511</v>
+      </c>
+      <c r="C80">
+        <v>-126371035.73565094</v>
+      </c>
+      <c r="D80">
+        <v>-68245653.71536511</v>
+      </c>
+      <c r="H80">
+        <v>-126459106.7181057</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="str">
+        <v xml:space="preserve">    Satış Amacıyla Elde Tutulan Duran Varlık Satışlarından Kaynaklanan Nakit Girişleri</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="str">
+        <v xml:space="preserve">    Satış Amacıyla Elde Tutulan Duran Varlık Alımlarından Nakit Çıkışları</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="str">
+        <v xml:space="preserve">    Canlı Varlık Satışından Kaynaklanan Nakit Girişleri</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="str">
+        <v xml:space="preserve">    Canlı Varlık Alımından Kaynaklanan Nakit Çıkışları</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="str">
+        <v xml:space="preserve">    Diğer Uzun Vadeli Varlıkların Satışından Kaynaklanan Nakit Girişleri</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="str">
+        <v xml:space="preserve">    Diğer Uzun Vadeli Varlık Alımından Kaynaklanan Nakit Çıkışları</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="str">
+        <v xml:space="preserve">    Verilen Nakit Avans ve Borçlar</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="str">
+        <v xml:space="preserve">    Verilen Nakit Avans ve Borçlardan Geri Ödemeler</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="str">
+        <v xml:space="preserve">    Türev Araçlardan Nakit Girişleri</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="str">
+        <v xml:space="preserve">    Türev Araçlardan Nakit Çıkışları</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="str">
+        <v xml:space="preserve">    Devlet Teşviklerinden Elde Edilen Nakit Girişleri</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="str">
+        <v xml:space="preserve">    Alınan Temettüler</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="str">
+        <v xml:space="preserve">    Ödenen Faiz</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="str">
+        <v xml:space="preserve">    Alınan Faiz</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="str">
+        <v xml:space="preserve">    Katılım (Kar) Payı ve Diğer Finansal Araçlardan Nakit Çıkışları</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="str">
+        <v xml:space="preserve">    Katılım (Kar) Payı ve Diğer Finansal Araçlardan Nakit Girişleri</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="str">
+        <v xml:space="preserve">    Vergi İadeleri (Ödemeleri)</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="str">
+        <v xml:space="preserve">    Diğer Nakit Girişleri (Çıkışları)</v>
+      </c>
+      <c r="J98">
+        <v>-394672813.3359241</v>
+      </c>
+      <c r="K98">
+        <v>-1503379.983559138</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="str">
+        <v xml:space="preserve">    Durdurulan Faaliyetlere İlişkin Net Nakit Akışları</v>
+      </c>
+    </row>
+    <row r="100"/>
+    <row r="101">
+      <c r="A101" t="str">
+        <v xml:space="preserve">    Finansman Faaliyetlerinden Nakit Akışları</v>
+      </c>
+      <c r="B101">
+        <v>156996208.87372896</v>
+      </c>
+      <c r="C101">
+        <v>360507997.33525217</v>
+      </c>
+      <c r="D101">
+        <v>-64154068.12627104</v>
+      </c>
+      <c r="E101">
+        <v>133969314.90105917</v>
+      </c>
+      <c r="H101">
+        <v>-7924117.049535129</v>
+      </c>
+      <c r="J101">
+        <v>438852238.5557909</v>
+      </c>
+      <c r="K101">
+        <v>10276288.790892785</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="str">
+        <v xml:space="preserve">    Bağlı Ortaklıklardaki Kontrolün Kaybına Yol Açmayan Şekilde Ortaklık Payları Değişmelerinden Kaynaklanan Nakit Girişleri</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="str">
+        <v xml:space="preserve">    Bağlı Ortaklıklardaki Kontrolün Kaybına Yol Açmayan Şekilde Ortaklık Payları Değişmelerinden Kaynaklanan Nakit Çıkışları</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="str">
+        <v xml:space="preserve">    Pay ve Diğer Özkaynağa Dayalı Araçların İhracından Kaynaklanan Nakit Girişleri</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="str">
+        <v xml:space="preserve">    Sermaye Avanslarından Nakit Girişleri</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="str">
+        <v xml:space="preserve">    İşletmenin Kendi Paylarını ve Diğer Özkaynağa Dayalı Araçlarını Almasıyla İlgili Nakit Çıkışları</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="str">
+        <v xml:space="preserve">    İşletmenin Kendi Paylarını ve Diğer Özkaynağa Dayalı Araçlarını Satmasından Kaynaklanan Nakit Girişleri</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="str">
+        <v xml:space="preserve">    Ortak Kontrole Tabi İşletmelerin Birleşme Etkisinden Kaynaklanan Nakit Girişleri (Çıkışları)</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="str">
+        <v xml:space="preserve">    Borçlanmadan Kaynaklanan Nakit Girişleri</v>
+      </c>
+      <c r="D109">
+        <v>14778426.571344417</v>
+      </c>
+      <c r="E109">
+        <v>184807698.43684155</v>
+      </c>
+      <c r="H109">
+        <v>2864317.758599493</v>
+      </c>
+      <c r="J109">
+        <v>68412627.40108459</v>
+      </c>
+      <c r="K109">
+        <v>7223803.1992623</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="str">
+        <v xml:space="preserve">    Borç Ödemelerine İlişkin Nakit Çıkışları</v>
+      </c>
+      <c r="B110">
+        <v>-35700667.99503112</v>
+      </c>
+      <c r="C110">
+        <v>-31706969.116671056</v>
+      </c>
+      <c r="D110">
+        <v>-16076168.995031122</v>
+      </c>
+      <c r="E110">
+        <v>-12529422.577408731</v>
+      </c>
+      <c r="H110">
+        <v>-8796919.320544017</v>
+      </c>
+      <c r="J110">
+        <v>-13258676.25912771</v>
+      </c>
+      <c r="K110">
+        <v>-4169974.4350770074</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="str">
+        <v xml:space="preserve">    İlişkili Taraflardan Alınan Diğer Borçlardaki Artış</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="str">
+        <v xml:space="preserve">    İlişkili Taraflardan Alınan Diğer Borçlardaki Azalış</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="str">
+        <v xml:space="preserve">    Kira Sözleşmelerinden Kaynaklanan Borç Ödemelerine İlişkin Nakit Çıkışları</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="str">
+        <v xml:space="preserve">    Türev Araçlardan Nakit Girişleri</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="str">
+        <v xml:space="preserve">    Türev Araçlardan Nakit Çıkışları</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="str">
+        <v xml:space="preserve">    Devlet Teşviklerinden Elde Edilen Nakit Girişleri</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="str">
+        <v xml:space="preserve">    Ödenen Temettüler</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="str">
+        <v xml:space="preserve">    Ödenen Faiz</v>
+      </c>
+      <c r="B118">
+        <v>-88471344.31309071</v>
+      </c>
+      <c r="C118">
+        <v>-93699765.37064308</v>
+      </c>
+      <c r="D118">
+        <v>-74267484.31309071</v>
+      </c>
+      <c r="E118">
+        <v>-54629211.000201255</v>
+      </c>
+      <c r="H118">
+        <v>-7095475.920779654</v>
+      </c>
+      <c r="J118">
+        <v>-2358898.5656001098</v>
+      </c>
+      <c r="K118">
+        <v>-257435.6715361634</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="str">
+        <v xml:space="preserve">    Alınan Faiz</v>
+      </c>
+      <c r="B119">
+        <v>20551706.610506367</v>
+      </c>
+      <c r="D119">
+        <v>11411158.610506367</v>
+      </c>
+      <c r="E119">
+        <v>19123151.909433033</v>
+      </c>
+      <c r="H119">
+        <v>7906198.702276978</v>
+      </c>
+      <c r="J119">
+        <v>39270.285600584466</v>
+      </c>
+      <c r="K119">
+        <v>73052.36568445187</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="str">
+        <v xml:space="preserve">    Katılım (Kar) Payı ve Diğer Finansal Araçlardan Nakit Çıkışları</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="str">
+        <v xml:space="preserve">    Katılım (Kar) Payı ve Diğer Finansal Araçlardan Nakit Girişleri</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="str">
+        <v xml:space="preserve">    Vergi İadeleri (Ödemeleri)</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="str">
+        <v xml:space="preserve">    Diğer Nakit Girişleri (Çıkışları)</v>
+      </c>
+      <c r="H123">
+        <v>-2802238.2690879293</v>
+      </c>
+      <c r="K123">
+        <v>7406843.332559204</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="str">
+        <v xml:space="preserve">    Durdurulan Faaliyetlere İlişkin Net Nakit Akışları</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="str">
+        <v xml:space="preserve">    Yabancı Para Çevrim Farklarının Etkisinden Önce Nakit ve Nakit Benzerlerindeki Net Artış (Azalış)</v>
+      </c>
+      <c r="B125">
+        <v>-50762096.261865124</v>
+      </c>
+      <c r="C125">
+        <v>87042325.75930001</v>
+      </c>
+      <c r="D125">
+        <v>4319170.738134878</v>
+      </c>
+      <c r="E125">
+        <v>-29197008.66334983</v>
+      </c>
+      <c r="H125">
+        <v>-12686532.540096818</v>
+      </c>
+      <c r="J125">
+        <v>12456761.690664703</v>
+      </c>
+      <c r="K125">
+        <v>-1695338.143599171</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="str">
+        <v xml:space="preserve">    Yabancı Para Çevrim Farklarının Nakit ve Nakit Benzerleri Üzerindeki Etkisi</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="str">
+        <v xml:space="preserve">    Nakit ve Nakit Benzerlerindeki Net Artış (Azalış)</v>
+      </c>
+      <c r="B127">
+        <v>-50762096.261865124</v>
+      </c>
+      <c r="C127">
+        <v>87042325.75930001</v>
+      </c>
+      <c r="D127">
+        <v>4319170.738134878</v>
+      </c>
+      <c r="E127">
+        <v>-29197008.66334983</v>
+      </c>
+      <c r="H127">
+        <v>-12686532.540096818</v>
+      </c>
+      <c r="J127">
+        <v>12456761.690664703</v>
+      </c>
+      <c r="K127">
+        <v>-1695338.143599171</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="str">
+        <v xml:space="preserve">    Dönem Başı Nakit ve Nakit Benzerleri</v>
+      </c>
+      <c r="B128">
+        <v>4371767.631457624</v>
+      </c>
+      <c r="C128">
+        <v>4371741.408404096</v>
+      </c>
+      <c r="D128">
+        <v>52651.631457623655</v>
+      </c>
+      <c r="H128">
+        <v>12739184.17155444</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="str">
+        <v xml:space="preserve">    Dönem Sonu Nakit ve Nakit Benzerleri</v>
+      </c>
+      <c r="B129">
+        <v>-46390328.6304075</v>
+      </c>
+      <c r="C129">
+        <v>91414067.16770409</v>
+      </c>
+      <c r="D129">
+        <v>4371822.369592501</v>
+      </c>
+      <c r="H129">
+        <v>52651.631457623655</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:K129"/>
   </ignoredErrors>
 </worksheet>
 </file>